--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_Menu.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_Menu.xlsx
@@ -10,12 +10,12 @@
     <sheet name="MainOLD" sheetId="1" r:id="rId1"/>
     <sheet name="Main" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511" iterateDelta="1E-4"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="307">
   <si>
     <t>System</t>
   </si>
@@ -374,9 +374,6 @@
     <t>Debit Note</t>
   </si>
   <si>
-    <t>Module.Budgeting.Data.Budget.Transaction</t>
-  </si>
-  <si>
     <t>Module.Finance.Data.Advance.Transaction</t>
   </si>
   <si>
@@ -701,12 +698,6 @@
     <t>Module.General.MasterData.MenuManagement.Transaction</t>
   </si>
   <si>
-    <t>Workflow Route</t>
-  </si>
-  <si>
-    <t>Module.General.MasterData.WorkflowRoute.Transaction</t>
-  </si>
-  <si>
     <t>Report Advance Summary</t>
   </si>
   <si>
@@ -731,7 +722,220 @@
     <t>Cash &amp; Bank</t>
   </si>
   <si>
-    <t>Cash &amp; Bank Report</t>
+    <t>Dashboard.Home</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.PrivilegeMenu.Transaction</t>
+  </si>
+  <si>
+    <t>Privilege Menu</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.Workflow.Transaction</t>
+  </si>
+  <si>
+    <t>Workflow</t>
+  </si>
+  <si>
+    <t>Module.Budgeting.Data.ModifyBudget.Transaction</t>
+  </si>
+  <si>
+    <t>Modify Budget</t>
+  </si>
+  <si>
+    <t>Module.Budgeting.Data.Work.Transaction</t>
+  </si>
+  <si>
+    <t>Work</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.CurrencyExchangeRate.Transaction</t>
+  </si>
+  <si>
+    <t>Exchange Rate</t>
+  </si>
+  <si>
+    <t>Module.Accounting.Data.GeneralJournal.Transaction</t>
+  </si>
+  <si>
+    <t>General Journal</t>
+  </si>
+  <si>
+    <t>Module.Finance.Data.SalesInvoice.Transaction</t>
+  </si>
+  <si>
+    <t>Sales Invoice</t>
+  </si>
+  <si>
+    <t>Module.Finance.Data.TaxReconciliation.Transaction</t>
+  </si>
+  <si>
+    <t>Tax Reconciliation</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</t>
+  </si>
+  <si>
+    <t>Exchange Rate Summary</t>
+  </si>
+  <si>
+    <t>Module.Accounting.Data.GeneralJournal.Report.DataList</t>
+  </si>
+  <si>
+    <t>General Journal Summary</t>
+  </si>
+  <si>
+    <t>Module.Finance.Data.SalesInvoice.Report.DataList</t>
+  </si>
+  <si>
+    <t>Sales Invoice Summary</t>
+  </si>
+  <si>
+    <t>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</t>
+  </si>
+  <si>
+    <t>Sales Invoice to Credit Note</t>
+  </si>
+  <si>
+    <t>Module.Finance.Data.TaxReconciliation.Report.DataList</t>
+  </si>
+  <si>
+    <t>Tax Reconciliation Summary</t>
+  </si>
+  <si>
+    <t>Module.Accounting.MasterData.AssetCategory.Transaction</t>
+  </si>
+  <si>
+    <t>Asset Category</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.Bank.Transaction</t>
+  </si>
+  <si>
+    <t>Bank</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.BankAccount.Transaction</t>
+  </si>
+  <si>
+    <t>Bank Account</t>
+  </si>
+  <si>
+    <t>Module.Budgeting.MasterData.Budget.Transaction</t>
+  </si>
+  <si>
+    <t>Module.Accounting.MasterData.ChartOfAccount.Transaction</t>
+  </si>
+  <si>
+    <t>Chart of Account</t>
+  </si>
+  <si>
+    <t>Depreciation Method</t>
+  </si>
+  <si>
+    <t>Module.Accounting.MasterData.DepreciationMethod.Transaction</t>
+  </si>
+  <si>
+    <t>Depreciation Rate Years</t>
+  </si>
+  <si>
+    <t>Module.Accounting.MasterData.DepreciationRateYears.Transaction</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.PaymentTerm.Transaction</t>
+  </si>
+  <si>
+    <t>Payment Term</t>
+  </si>
+  <si>
+    <t>Sub Budget</t>
+  </si>
+  <si>
+    <t>Module.Budgeting.MasterData.BudgetSection.Transaction</t>
+  </si>
+  <si>
+    <t>Module.Taxation.MasterData.ValueAddedTax.Transaction</t>
+  </si>
+  <si>
+    <t>Value Added Tax</t>
+  </si>
+  <si>
+    <t>Module.HumanResource.Data.SallaryAllocation.Transaction</t>
+  </si>
+  <si>
+    <t>Sallary Allocation</t>
+  </si>
+  <si>
+    <t>Module.HumanResource.Data.SallaryAllocation.Report.DataList</t>
+  </si>
+  <si>
+    <t>Sallary Allocation Summary</t>
+  </si>
+  <si>
+    <t>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</t>
+  </si>
+  <si>
+    <t>Person Work Time Sheet Summary</t>
+  </si>
+  <si>
+    <t>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.Person.Transaction</t>
+  </si>
+  <si>
+    <t>Person</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.UserRole.Transaction</t>
+  </si>
+  <si>
+    <t>Module.SupplyChain.Data.MaterialReceive.Report.DataList</t>
+  </si>
+  <si>
+    <t>Report DO to Material Receive</t>
+  </si>
+  <si>
+    <t>Report Material Receive to Material Return</t>
+  </si>
+  <si>
+    <t>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</t>
+  </si>
+  <si>
+    <t>Report Advance to Advance Settlement</t>
+  </si>
+  <si>
+    <t>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</t>
+  </si>
+  <si>
+    <t>Report BusinessTrip to BusinessTrip Settlement</t>
+  </si>
+  <si>
+    <t>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</t>
+  </si>
+  <si>
+    <t>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</t>
+  </si>
+  <si>
+    <t>Cash &amp; Bank Summary</t>
+  </si>
+  <si>
+    <t>Module.CustomerRelation.MasterData.Customer.Transaction</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Report Material Receive Summary</t>
   </si>
 </sst>
 </file>
@@ -12455,10 +12659,10 @@
     </row>
     <row r="311" spans="2:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B311" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="C311" s="13" t="s">
         <v>172</v>
-      </c>
-      <c r="C311" s="13" t="s">
-        <v>173</v>
       </c>
       <c r="D311" s="13" t="s">
         <v>96</v>
@@ -12819,7 +13023,7 @@
     </row>
     <row r="321" spans="2:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B321" s="13" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C321" s="13"/>
       <c r="D321" s="13"/>
@@ -12856,10 +13060,10 @@
     </row>
     <row r="322" spans="2:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B322" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C322" s="13" t="s">
         <v>175</v>
-      </c>
-      <c r="C322" s="13" t="s">
-        <v>176</v>
       </c>
       <c r="D322" s="13" t="s">
         <v>62</v>
@@ -13212,7 +13416,7 @@
     </row>
     <row r="332" spans="2:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B332" s="13" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C332" s="13"/>
       <c r="D332" s="13"/>
@@ -15791,7 +15995,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I64"/>
+  <dimension ref="B1:I98"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
@@ -15847,7 +16051,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="8">
-        <f t="shared" ref="E3:E64" si="0">IF(ISNUMBER($E2), $E2+1, 97000000000001)</f>
+        <f t="shared" ref="E3:E94" si="0">IF(ISNUMBER($E2), $E2+1, 97000000000001)</f>
         <v>97000000000002</v>
       </c>
       <c r="F3" s="3" t="str">
@@ -15855,11 +16059,11 @@
         <v>System.Logout</v>
       </c>
       <c r="G3" s="3" t="str">
-        <f t="shared" ref="G3:G4" si="2">IF(EXACT(C3, ""), "", C3)</f>
+        <f t="shared" ref="G3:G5" si="2">IF(EXACT(C3, ""), "", C3)</f>
         <v>Logout</v>
       </c>
       <c r="I3" s="9" t="str">
-        <f t="shared" ref="I3:I64" si="3">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B3, ""),"null", CONCATENATE("'", $F3, "'")), ", ", IF(EXACT($B3, ""), "null", CONCATENATE("'", $G3, "'")), ");")</f>
+        <f t="shared" ref="I3:I98" si="3">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B3, ""),"null", CONCATENATE("'", $F3, "'")), ", ", IF(EXACT($B3, ""), "null", CONCATENATE("'", $G3, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'System.Logout', 'Logout');</v>
       </c>
     </row>
@@ -15889,34 +16093,34 @@
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>92</v>
+        <v>235</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>91</v>
+        <v>236</v>
       </c>
       <c r="E5" s="8">
         <f t="shared" si="0"/>
         <v>97000000000004</v>
       </c>
       <c r="F5" s="3" t="str">
-        <f t="shared" ref="F5:F64" si="4">IF(EXACT(B5, ""), "", B5)</f>
-        <v>Dashboard.DocumentTracking</v>
+        <f t="shared" ref="F5:F8" si="4">IF(EXACT(B5, ""), "", B5)</f>
+        <v>Dashboard.Home</v>
       </c>
       <c r="G5" s="3" t="str">
-        <f t="shared" ref="G5:G64" si="5">IF(EXACT(C5, ""), "", C5)</f>
-        <v>Document Tracking</v>
+        <f t="shared" si="2"/>
+        <v>Dashboard</v>
       </c>
       <c r="I5" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.DocumentTracking', 'Document Tracking');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.Home', 'Dashboard');</v>
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
-        <v>151</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>149</v>
+        <v>91</v>
       </c>
       <c r="E6" s="8">
         <f t="shared" si="0"/>
@@ -15924,23 +16128,23 @@
       </c>
       <c r="F6" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Dashboard.MyDocumentTracking</v>
+        <v>Dashboard.DocumentTracking</v>
       </c>
       <c r="G6" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>My Document Tracking</v>
+        <f t="shared" ref="G6:G8" si="5">IF(EXACT(C6, ""), "", C6)</f>
+        <v>Document Tracking</v>
       </c>
       <c r="I6" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.MyDocumentTracking', 'My Document Tracking');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.DocumentTracking', 'Document Tracking');</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B7" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>150</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" si="0"/>
@@ -15948,23 +16152,23 @@
       </c>
       <c r="F7" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Dashboard.MyDocumentDisposition</v>
+        <v>Dashboard.MyDocumentTracking</v>
       </c>
       <c r="G7" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>My Document Disposition</v>
+        <v>My Document Tracking</v>
       </c>
       <c r="I7" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.MyDocumentDisposition', 'My Document Disposition');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.MyDocumentTracking', 'My Document Tracking');</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B8" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>131</v>
+      <c r="B8" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>149</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="0"/>
@@ -15972,1359 +16176,2175 @@
       </c>
       <c r="F8" s="3" t="str">
         <f t="shared" si="4"/>
-        <v>Module.General.MasterData.Country.Transaction</v>
+        <v>Dashboard.MyDocumentDisposition</v>
       </c>
       <c r="G8" s="3" t="str">
         <f t="shared" si="5"/>
-        <v>Country</v>
+        <v>My Document Disposition</v>
       </c>
       <c r="I8" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Country.Transaction', 'Country');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.MyDocumentDisposition', 'My Document Disposition');</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="0"/>
         <v>97000000000008</v>
       </c>
       <c r="F9" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
+        <f t="shared" ref="F9:F18" si="6">IF(EXACT(B9, ""), "", B9)</f>
+        <v>Module.General.MasterData.Country.Transaction</v>
       </c>
       <c r="G9" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Province / State</v>
+        <f t="shared" ref="G9:G18" si="7">IF(EXACT(C9, ""), "", C9)</f>
+        <v>Country</v>
       </c>
       <c r="I9" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction', 'Province / State');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Country.Transaction', 'Country');</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E10" s="8">
         <f t="shared" si="0"/>
         <v>97000000000009</v>
       </c>
       <c r="F10" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
+        <f t="shared" si="6"/>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
       </c>
       <c r="G10" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Municipality / Regency</v>
+        <f t="shared" si="7"/>
+        <v>Province / State</v>
       </c>
       <c r="I10" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction', 'Municipality / Regency');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction', 'Province / State');</v>
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
         <v>97000000000010</v>
       </c>
       <c r="F11" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
+        <f t="shared" si="6"/>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
       </c>
       <c r="G11" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>District</v>
+        <f t="shared" si="7"/>
+        <v>Municipality / Regency</v>
       </c>
       <c r="I11" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction', 'District');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction', 'Municipality / Regency');</v>
       </c>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B12" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>178</v>
+      <c r="B12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>179</v>
       </c>
       <c r="E12" s="8">
         <f t="shared" si="0"/>
         <v>97000000000011</v>
       </c>
       <c r="F12" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
+        <f t="shared" si="6"/>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
       </c>
       <c r="G12" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Urban Village / Village</v>
+        <f t="shared" si="7"/>
+        <v>District</v>
       </c>
       <c r="I12" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction', 'Urban Village / Village');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction', 'District');</v>
       </c>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B13" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>130</v>
+      <c r="B13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>177</v>
       </c>
       <c r="E13" s="8">
         <f t="shared" si="0"/>
         <v>97000000000012</v>
       </c>
       <c r="F13" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
+        <f t="shared" si="6"/>
+        <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
       </c>
       <c r="G13" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Business Document Type</v>
+        <f t="shared" si="7"/>
+        <v>Urban Village / Village</v>
       </c>
       <c r="I13" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BusinessDocumentType.Transaction', 'Business Document Type');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction', 'Urban Village / Village');</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B14" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>182</v>
+      <c r="B14" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="E14" s="8">
         <f t="shared" si="0"/>
         <v>97000000000013</v>
       </c>
       <c r="F14" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.BusinessDocument.Transaction</v>
+        <f t="shared" si="6"/>
+        <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
       </c>
       <c r="G14" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Business Document</v>
+        <f t="shared" si="7"/>
+        <v>Business Document Type</v>
       </c>
       <c r="I14" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BusinessDocument.Transaction', 'Business Document');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BusinessDocumentType.Transaction', 'Business Document Type');</v>
       </c>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E15" s="8">
         <f t="shared" si="0"/>
         <v>97000000000014</v>
       </c>
       <c r="F15" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
+        <f t="shared" si="6"/>
+        <v>Module.General.MasterData.BusinessDocument.Transaction</v>
       </c>
       <c r="G15" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Business Document Version</v>
+        <f t="shared" si="7"/>
+        <v>Business Document</v>
       </c>
       <c r="I15" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BusinessDocumentVersion.Transaction', 'Business Document Version');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BusinessDocument.Transaction', 'Business Document');</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>226</v>
+        <v>182</v>
       </c>
       <c r="E16" s="8">
         <f t="shared" si="0"/>
         <v>97000000000015</v>
       </c>
       <c r="F16" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.MenuManagement.Transaction</v>
+        <f t="shared" si="6"/>
+        <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
       </c>
       <c r="G16" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Menu Management</v>
+        <f t="shared" si="7"/>
+        <v>Business Document Version</v>
       </c>
       <c r="I16" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.MenuManagement.Transaction', 'Menu Management');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BusinessDocumentVersion.Transaction', 'Business Document Version');</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B17" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>228</v>
+      <c r="B17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="E17" s="8">
         <f t="shared" si="0"/>
         <v>97000000000016</v>
       </c>
       <c r="F17" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.WorkflowRoute.Transaction</v>
+        <f t="shared" si="6"/>
+        <v>Module.General.MasterData.MenuManagement.Transaction</v>
       </c>
       <c r="G17" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Workflow Route</v>
+        <f t="shared" si="7"/>
+        <v>Menu Management</v>
       </c>
       <c r="I17" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.WorkflowRoute.Transaction', 'Workflow Route');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.MenuManagement.Transaction', 'Menu Management');</v>
       </c>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
-        <v>119</v>
+        <v>237</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>117</v>
+        <v>238</v>
       </c>
       <c r="E18" s="8">
         <f t="shared" si="0"/>
         <v>97000000000017</v>
       </c>
       <c r="F18" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Budgeting.Data.Budget.Transaction</v>
+        <f t="shared" si="6"/>
+        <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
       </c>
       <c r="G18" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Budget</v>
+        <f t="shared" si="7"/>
+        <v>Privilege Menu</v>
       </c>
       <c r="I18" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.Budget.Transaction', 'Budget');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.PrivilegeMenu.Transaction', 'Privilege Menu');</v>
       </c>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B19" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>186</v>
+      <c r="B19" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>240</v>
       </c>
       <c r="E19" s="8">
         <f t="shared" si="0"/>
         <v>97000000000018</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
+        <f t="shared" ref="F19:F33" si="8">IF(EXACT(B19, ""), "", B19)</f>
+        <v>Module.General.MasterData.Workflow.Transaction</v>
       </c>
       <c r="G19" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report Modify Budget Summary</v>
+        <f t="shared" ref="G19:G33" si="9">IF(EXACT(C19, ""), "", C19)</f>
+        <v>Workflow</v>
       </c>
       <c r="I19" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.ModifyBudget.Report.Resume', 'Report Modify Budget Summary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Workflow.Transaction', 'Workflow');</v>
       </c>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B20" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>187</v>
+      <c r="B20" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="E20" s="8">
         <f t="shared" si="0"/>
         <v>97000000000019</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+        <f t="shared" si="8"/>
+        <v>Module.Budgeting.MasterData.Budget.Transaction</v>
       </c>
       <c r="G20" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report Cost Financial Structure</v>
+        <f t="shared" si="9"/>
+        <v>Budget</v>
       </c>
       <c r="I20" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.CFS.Report.Resume', 'Report Cost Financial Structure');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.MasterData.Budget.Transaction', 'Budget');</v>
       </c>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>147</v>
+        <v>279</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>148</v>
+        <v>278</v>
       </c>
       <c r="E21" s="8">
         <f t="shared" si="0"/>
         <v>97000000000020</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.Religion.Transaction</v>
+        <f t="shared" ref="F21:F84" si="10">IF(EXACT(B21, ""), "", B21)</f>
+        <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
       </c>
       <c r="G21" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Religion</v>
+        <f t="shared" ref="G21:G84" si="11">IF(EXACT(C21, ""), "", C21)</f>
+        <v>Sub Budget</v>
       </c>
       <c r="I21" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Religion.Transaction', 'Religion');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.MasterData.BudgetSection.Transaction', 'Sub Budget');</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>133</v>
+        <v>241</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>188</v>
+        <v>242</v>
       </c>
       <c r="E22" s="8">
         <f t="shared" si="0"/>
         <v>97000000000021</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Budgeting.Data.ModifyBudget.Transaction</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Blood Aglutinogen Type</v>
+        <f t="shared" si="11"/>
+        <v>Modify Budget</v>
       </c>
       <c r="I22" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BloodAglutinogenType.Transaction', 'Blood Aglutinogen Type');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.ModifyBudget.Transaction', 'Modify Budget');</v>
       </c>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B23" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>129</v>
+      <c r="B23" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="E23" s="8">
         <f t="shared" si="0"/>
         <v>97000000000022</v>
       </c>
       <c r="F23" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
       </c>
       <c r="G23" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Person Work Time Sheet</v>
+        <f t="shared" si="11"/>
+        <v>Report Modify Budget Summary</v>
       </c>
       <c r="I23" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction', 'Person Work Time Sheet');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.ModifyBudget.Report.Resume', 'Report Modify Budget Summary');</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>189</v>
+        <v>243</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>162</v>
+        <v>244</v>
       </c>
       <c r="E24" s="8">
         <f t="shared" si="0"/>
         <v>97000000000023</v>
       </c>
       <c r="F24" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.Warehouse.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Budgeting.Data.Work.Transaction</v>
       </c>
       <c r="G24" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Warehouse</v>
+        <f t="shared" si="11"/>
+        <v>Work</v>
       </c>
       <c r="I24" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Warehouse.Transaction', 'Warehouse');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.Work.Transaction', 'Work');</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B25" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>146</v>
+      <c r="B25" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="E25" s="8">
         <f t="shared" si="0"/>
         <v>97000000000024</v>
       </c>
       <c r="F25" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.ProductType.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
       </c>
       <c r="G25" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Product Type</v>
+        <f t="shared" si="11"/>
+        <v>Report Cost Financial Structure</v>
       </c>
       <c r="I25" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.ProductType.Transaction', 'Product Type');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.CFS.Report.Resume', 'Report Cost Financial Structure');</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="E26" s="8">
         <f t="shared" si="0"/>
         <v>97000000000025</v>
       </c>
       <c r="F26" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.Product.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
       </c>
       <c r="G26" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Product</v>
+        <f t="shared" si="11"/>
+        <v>Blood Aglutinogen Type</v>
       </c>
       <c r="I26" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Product.Transaction', 'Product');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BloodAglutinogenType.Transaction', 'Blood Aglutinogen Type');</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>154</v>
+        <v>290</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>191</v>
+        <v>291</v>
       </c>
       <c r="E27" s="8">
         <f t="shared" si="0"/>
         <v>97000000000026</v>
       </c>
       <c r="F27" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.Person.Transaction</v>
       </c>
       <c r="G27" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report DO Summary</v>
+        <f t="shared" si="11"/>
+        <v>Person</v>
       </c>
       <c r="I27" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Report.DataList', 'Report DO Summary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Person.Transaction', 'Person');</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E28" s="8">
         <f t="shared" si="0"/>
         <v>97000000000027</v>
       </c>
       <c r="F28" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.Religion.Transaction</v>
       </c>
       <c r="G28" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Delivery Order</v>
+        <f t="shared" si="11"/>
+        <v>Religion</v>
       </c>
       <c r="I28" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Transaction', 'Delivery Order');</v>
+        <f t="shared" ref="I28:I91" si="12">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B28, ""),"null", CONCATENATE("'", $F28, "'")), ", ", IF(EXACT($B28, ""), "null", CONCATENATE("'", $G28, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Religion.Transaction', 'Religion');</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>293</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>190</v>
+        <v>292</v>
       </c>
       <c r="E29" s="8">
         <f t="shared" si="0"/>
         <v>97000000000028</v>
       </c>
       <c r="F29" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.UserRole.Transaction</v>
       </c>
       <c r="G29" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Material Receive</v>
+        <f t="shared" si="11"/>
+        <v>Role</v>
       </c>
       <c r="I29" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceive.Transaction', 'Material Receive');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.UserRole.Transaction', 'Role');</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>193</v>
+        <v>288</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>196</v>
+        <v>289</v>
       </c>
       <c r="E30" s="8">
         <f t="shared" si="0"/>
         <v>97000000000029</v>
       </c>
       <c r="F30" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
       </c>
       <c r="G30" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report Material Return Summary</v>
+        <f t="shared" si="11"/>
+        <v>Department</v>
       </c>
       <c r="I30" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Report.DataList', 'Report Material Return Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.MasterData.OrganizationalDepartment.Transaction', 'Department');</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B31" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>195</v>
+      <c r="B31" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="E31" s="8">
         <f t="shared" si="0"/>
         <v>97000000000030</v>
       </c>
       <c r="F31" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
       </c>
       <c r="G31" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Material Return</v>
+        <f t="shared" si="11"/>
+        <v>Person Work Time Sheet</v>
       </c>
       <c r="I31" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Transaction', 'Material Return');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction', 'Person Work Time Sheet');</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>121</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>230</v>
+        <v>287</v>
       </c>
       <c r="E32" s="8">
         <f t="shared" si="0"/>
         <v>97000000000031</v>
       </c>
       <c r="F32" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.Advance.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
       </c>
       <c r="G32" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report Advance Summary</v>
+        <f t="shared" si="11"/>
+        <v>Person Work Time Sheet Summary</v>
       </c>
       <c r="I32" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Report.DataList', 'Report Advance Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList', 'Person Work Time Sheet Summary');</v>
       </c>
     </row>
     <row r="33" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>120</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>231</v>
+        <v>283</v>
       </c>
       <c r="E33" s="8">
         <f t="shared" si="0"/>
         <v>97000000000032</v>
       </c>
       <c r="F33" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.Advance.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
       </c>
       <c r="G33" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Advance Request</v>
+        <f t="shared" si="11"/>
+        <v>Sallary Allocation</v>
       </c>
       <c r="I33" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Transaction', 'Advance Request');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.SallaryAllocation.Transaction', 'Sallary Allocation');</v>
       </c>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B34" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>232</v>
+      <c r="B34" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>285</v>
       </c>
       <c r="E34" s="8">
         <f t="shared" si="0"/>
         <v>97000000000033</v>
       </c>
       <c r="F34" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
       </c>
       <c r="G34" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report Advance Settlement Summary</v>
+        <f t="shared" si="11"/>
+        <v>Sallary Allocation Summary</v>
       </c>
       <c r="I34" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Report.DataList', 'Report Advance Settlement Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.SallaryAllocation.Report.DataList', 'Sallary Allocation Summary');</v>
       </c>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>122</v>
+        <v>188</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="E35" s="8">
         <f t="shared" si="0"/>
         <v>97000000000034</v>
       </c>
       <c r="F35" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.Warehouse.Transaction</v>
       </c>
       <c r="G35" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>AdvanceSettlement</v>
+        <f t="shared" si="11"/>
+        <v>Warehouse</v>
       </c>
       <c r="I35" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Transaction', 'AdvanceSettlement');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Warehouse.Transaction', 'Warehouse');</v>
       </c>
     </row>
     <row r="36" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>233</v>
+        <v>145</v>
       </c>
       <c r="E36" s="8">
         <f t="shared" si="0"/>
         <v>97000000000035</v>
       </c>
       <c r="F36" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.ProductType.Transaction</v>
       </c>
       <c r="G36" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report BusinessTrip Settlement Summary</v>
+        <f t="shared" si="11"/>
+        <v>Product Type</v>
       </c>
       <c r="I36" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList', 'Report BusinessTrip Settlement Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.ProductType.Transaction', 'Product Type');</v>
       </c>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>201</v>
+        <v>142</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>234</v>
+        <v>143</v>
       </c>
       <c r="E37" s="8">
         <f t="shared" si="0"/>
         <v>97000000000036</v>
       </c>
       <c r="F37" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.Product.Transaction</v>
       </c>
       <c r="G37" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>BusinessTrip Settlement</v>
+        <f t="shared" si="11"/>
+        <v>Product</v>
       </c>
       <c r="I37" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Transaction', 'BusinessTrip Settlement');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Product.Transaction', 'Product');</v>
       </c>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>235</v>
+        <v>154</v>
       </c>
       <c r="E38" s="8">
         <f t="shared" si="0"/>
         <v>97000000000037</v>
       </c>
       <c r="F38" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
       </c>
       <c r="G38" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report BusinessTrip Request Summary</v>
+        <f t="shared" si="11"/>
+        <v>Delivery Order</v>
       </c>
       <c r="I38" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Report.DataList', 'Report BusinessTrip Request Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Transaction', 'Delivery Order');</v>
       </c>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B39" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>236</v>
+      <c r="B39" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>190</v>
       </c>
       <c r="E39" s="8">
         <f t="shared" si="0"/>
         <v>97000000000038</v>
       </c>
       <c r="F39" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
       </c>
       <c r="G39" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>BusinessTrip Request</v>
+        <f t="shared" si="11"/>
+        <v>Report DO Summary</v>
       </c>
       <c r="I39" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Transaction', 'BusinessTrip Request');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Report.DataList', 'Report DO Summary');</v>
       </c>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
-        <v>160</v>
+        <v>301</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>161</v>
+        <v>295</v>
       </c>
       <c r="E40" s="8">
         <f t="shared" si="0"/>
         <v>97000000000039</v>
       </c>
       <c r="F40" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
       </c>
       <c r="G40" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Supplier</v>
+        <f t="shared" si="11"/>
+        <v>Report DO to Material Receive</v>
       </c>
       <c r="I40" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.MasterData.Supplier.Transaction', 'Supplier');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList', 'Report DO to Material Receive');</v>
       </c>
     </row>
     <row r="41" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>159</v>
+        <v>191</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="E41" s="8">
         <f t="shared" si="0"/>
         <v>97000000000040</v>
       </c>
       <c r="F41" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
       </c>
       <c r="G41" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report Purchase Requisition Summary</v>
+        <f t="shared" si="11"/>
+        <v>Material Receive</v>
       </c>
       <c r="I41" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList', 'Report Purchase Requisition Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceive.Transaction', 'Material Receive');</v>
       </c>
     </row>
     <row r="42" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>205</v>
+        <v>306</v>
       </c>
       <c r="E42" s="8">
         <f t="shared" si="0"/>
         <v>97000000000041</v>
       </c>
       <c r="F42" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
       </c>
       <c r="G42" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report Purchase Requisition To Purchase Order</v>
+        <f t="shared" si="11"/>
+        <v>Report Material Receive Summary</v>
       </c>
       <c r="I42" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList', 'Report Purchase Requisition To Purchase Order');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceive.Report.DataList', 'Report Material Receive Summary');</v>
       </c>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>158</v>
+        <v>302</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>89</v>
+        <v>296</v>
       </c>
       <c r="E43" s="8">
         <f t="shared" si="0"/>
         <v>97000000000042</v>
       </c>
       <c r="F43" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
       </c>
       <c r="G43" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Purchase Requisition</v>
+        <f t="shared" si="11"/>
+        <v>Report Material Receive to Material Return</v>
       </c>
       <c r="I43" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Transaction', 'Purchase Requisition');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList', 'Report Material Receive to Material Return');</v>
       </c>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="E44" s="8">
         <f t="shared" si="0"/>
         <v>97000000000043</v>
       </c>
       <c r="F44" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
       </c>
       <c r="G44" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Report Purchase Order Summary</v>
+        <f t="shared" si="11"/>
+        <v>Material Return</v>
       </c>
       <c r="I44" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList', 'Report Purchase Order Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Transaction', 'Material Return');</v>
       </c>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B45" s="4" t="s">
-        <v>156</v>
+        <v>192</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>90</v>
+        <v>195</v>
       </c>
       <c r="E45" s="8">
         <f t="shared" si="0"/>
         <v>97000000000044</v>
       </c>
       <c r="F45" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
       </c>
       <c r="G45" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Purchase Order</v>
+        <f t="shared" si="11"/>
+        <v>Report Material Return Summary</v>
       </c>
       <c r="I45" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Transaction', 'Purchase Order');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Report.DataList', 'Report Material Return Summary');</v>
       </c>
     </row>
     <row r="46" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>142</v>
+        <v>228</v>
       </c>
       <c r="E46" s="8">
         <f t="shared" si="0"/>
         <v>97000000000045</v>
       </c>
       <c r="F46" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.Period.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.Advance.Transaction</v>
       </c>
       <c r="G46" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Period</v>
+        <f t="shared" si="11"/>
+        <v>Advance Request</v>
       </c>
       <c r="I46" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Period.Transaction', 'Period');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Transaction', 'Advance Request');</v>
       </c>
     </row>
     <row r="47" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>132</v>
+        <v>227</v>
       </c>
       <c r="E47" s="8">
         <f t="shared" si="0"/>
         <v>97000000000046</v>
       </c>
       <c r="F47" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.General.MasterData.Currency.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.Advance.Report.DataList</v>
       </c>
       <c r="G47" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Currency</v>
+        <f t="shared" si="11"/>
+        <v>Report Advance Summary</v>
       </c>
       <c r="I47" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Currency.Transaction', 'Currency');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Report.DataList', 'Report Advance Summary');</v>
       </c>
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
-        <v>218</v>
+        <v>297</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>208</v>
+        <v>298</v>
       </c>
       <c r="E48" s="8">
         <f t="shared" si="0"/>
         <v>97000000000047</v>
       </c>
       <c r="F48" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
       </c>
       <c r="G48" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Reimbursement</v>
+        <f t="shared" si="11"/>
+        <v>Report Advance to Advance Settlement</v>
       </c>
       <c r="I48" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Transaction', 'Reimbursement');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList', 'Report Advance to Advance Settlement');</v>
       </c>
     </row>
     <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>219</v>
+        <v>121</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="E49" s="8">
         <f t="shared" si="0"/>
         <v>97000000000048</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
       </c>
       <c r="G49" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Reimbursement Summary</v>
+        <f t="shared" si="11"/>
+        <v>AdvanceSettlement</v>
       </c>
       <c r="I49" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Report.DataList', 'Reimbursement Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Transaction', 'AdvanceSettlement');</v>
       </c>
     </row>
     <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>118</v>
+        <v>229</v>
       </c>
       <c r="E50" s="8">
         <f t="shared" si="0"/>
         <v>97000000000049</v>
       </c>
       <c r="F50" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.DebitNote.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
       </c>
       <c r="G50" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Debit Note</v>
+        <f t="shared" si="11"/>
+        <v>Report Advance Settlement Summary</v>
       </c>
       <c r="I50" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Transaction', 'Debit Note');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Report.DataList', 'Report Advance Settlement Summary');</v>
       </c>
     </row>
     <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
-        <v>125</v>
+        <v>202</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="E51" s="8">
         <f t="shared" si="0"/>
         <v>97000000000050</v>
       </c>
       <c r="F51" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
       </c>
       <c r="G51" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Debit Note Summary</v>
+        <f t="shared" si="11"/>
+        <v>BusinessTrip Request</v>
       </c>
       <c r="I51" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Report.DataList', 'Debit Note Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Transaction', 'BusinessTrip Request');</v>
       </c>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="E52" s="8">
         <f t="shared" si="0"/>
         <v>97000000000051</v>
       </c>
       <c r="F52" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
       </c>
       <c r="G52" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Reimbursement to Debit Note</v>
+        <f t="shared" si="11"/>
+        <v>Report BusinessTrip Request Summary</v>
       </c>
       <c r="I52" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList', 'Reimbursement to Debit Note');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Report.DataList', 'Report BusinessTrip Request Summary');</v>
       </c>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>163</v>
+        <v>299</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>165</v>
+        <v>300</v>
       </c>
       <c r="E53" s="8">
         <f t="shared" si="0"/>
         <v>97000000000052</v>
       </c>
       <c r="F53" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.CreditNote.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="G53" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Credit Note</v>
+        <f t="shared" si="11"/>
+        <v>Report BusinessTrip to BusinessTrip Settlement</v>
       </c>
       <c r="I53" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Transaction', 'Credit Note');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList', 'Report BusinessTrip to BusinessTrip Settlement');</v>
       </c>
     </row>
     <row r="54" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
-        <v>164</v>
+        <v>200</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>212</v>
+        <v>231</v>
       </c>
       <c r="E54" s="8">
         <f t="shared" si="0"/>
         <v>97000000000053</v>
       </c>
       <c r="F54" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
       </c>
       <c r="G54" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Credit Note Summary</v>
+        <f t="shared" si="11"/>
+        <v>BusinessTrip Settlement</v>
       </c>
       <c r="I54" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Report.DataList', 'Credit Note Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Transaction', 'BusinessTrip Settlement');</v>
       </c>
     </row>
     <row r="55" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B55" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>168</v>
+      <c r="B55" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>230</v>
       </c>
       <c r="E55" s="8">
         <f t="shared" si="0"/>
         <v>97000000000054</v>
       </c>
       <c r="F55" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.Loan.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="G55" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Loan</v>
+        <f t="shared" si="11"/>
+        <v>Report BusinessTrip Settlement Summary</v>
       </c>
       <c r="I55" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Transaction', 'Loan');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList', 'Report BusinessTrip Settlement Summary');</v>
       </c>
     </row>
     <row r="56" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>213</v>
+        <v>160</v>
       </c>
       <c r="E56" s="8">
         <f t="shared" si="0"/>
         <v>97000000000055</v>
       </c>
       <c r="F56" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.Loan.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
       </c>
       <c r="G56" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Loan Summary</v>
+        <f t="shared" si="11"/>
+        <v>Supplier</v>
       </c>
       <c r="I56" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Report.DataList', 'Loan Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.MasterData.Supplier.Transaction', 'Supplier');</v>
       </c>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>171</v>
+        <v>89</v>
       </c>
       <c r="E57" s="8">
         <f t="shared" si="0"/>
         <v>97000000000056</v>
       </c>
       <c r="F57" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
       </c>
       <c r="G57" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Loan Settlement</v>
+        <f t="shared" si="11"/>
+        <v>Purchase Requisition</v>
       </c>
       <c r="I57" s="9" t="str">
-        <f t="shared" ref="I57:I64" si="6">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B57, ""),"null", CONCATENATE("'", $F57, "'")), ", ", IF(EXACT($B57, ""), "null", CONCATENATE("'", $G57, "'")), ");")</f>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Transaction', 'Loan Settlement');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Transaction', 'Purchase Requisition');</v>
       </c>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="E58" s="8">
         <f t="shared" si="0"/>
         <v>97000000000057</v>
       </c>
       <c r="F58" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
       </c>
       <c r="G58" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Loan Settlement Summary</v>
+        <f t="shared" si="11"/>
+        <v>Report Purchase Requisition Summary</v>
       </c>
       <c r="I58" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Report.DataList', 'Loan Settlement Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList', 'Report Purchase Requisition Summary');</v>
       </c>
     </row>
     <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="E59" s="8">
         <f t="shared" si="0"/>
         <v>97000000000058</v>
       </c>
       <c r="F59" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
       </c>
       <c r="G59" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Loan to Loan Settlement</v>
+        <f t="shared" si="11"/>
+        <v>Report Purchase Requisition To Purchase Order</v>
       </c>
       <c r="I59" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList', 'Loan to Loan Settlement');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList', 'Report Purchase Requisition To Purchase Order');</v>
       </c>
     </row>
     <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
-        <v>222</v>
+        <v>155</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>237</v>
+        <v>90</v>
       </c>
       <c r="E60" s="8">
         <f t="shared" si="0"/>
         <v>97000000000059</v>
       </c>
       <c r="F60" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.CashBank.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
       </c>
       <c r="G60" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Cash &amp; Bank</v>
+        <f t="shared" si="11"/>
+        <v>Purchase Order</v>
       </c>
       <c r="I60" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Transaction', 'Cash &amp; Bank');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Transaction', 'Purchase Order');</v>
       </c>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>223</v>
+        <v>156</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>238</v>
+        <v>203</v>
       </c>
       <c r="E61" s="8">
         <f t="shared" si="0"/>
         <v>97000000000060</v>
       </c>
       <c r="F61" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.CashBank.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
       </c>
       <c r="G61" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Cash &amp; Bank Report</v>
+        <f t="shared" si="11"/>
+        <v>Report Purchase Order Summary</v>
       </c>
       <c r="I61" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Report.DataList', 'Cash &amp; Bank Report');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList', 'Report Purchase Order Summary');</v>
       </c>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B62" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>216</v>
+      <c r="B62" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>223</v>
       </c>
       <c r="E62" s="8">
         <f t="shared" si="0"/>
         <v>97000000000061</v>
       </c>
       <c r="F62" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+        <f t="shared" si="10"/>
+        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
       </c>
       <c r="G62" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Account Payable</v>
+        <f t="shared" si="11"/>
+        <v>Purchase Order to Account Payable</v>
       </c>
       <c r="I62" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Transaction', 'Account Payable');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList', 'Purchase Order to Account Payable');</v>
       </c>
     </row>
     <row r="63" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="B63" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>217</v>
+      <c r="B63" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>266</v>
       </c>
       <c r="E63" s="8">
         <f t="shared" si="0"/>
         <v>97000000000062</v>
       </c>
       <c r="F63" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.Bank.Transaction</v>
       </c>
       <c r="G63" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Account Payable Summary</v>
+        <f t="shared" si="11"/>
+        <v>Bank</v>
       </c>
       <c r="I63" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Report.DataList', 'Account Payable Summary');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Bank.Transaction', 'Bank');</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>224</v>
+        <v>268</v>
       </c>
       <c r="E64" s="8">
         <f t="shared" si="0"/>
         <v>97000000000063</v>
       </c>
       <c r="F64" s="3" t="str">
-        <f t="shared" si="4"/>
-        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.BankAccount.Transaction</v>
       </c>
       <c r="G64" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Purchase Order to Account Payable</v>
+        <f t="shared" si="11"/>
+        <v>Bank Account</v>
       </c>
       <c r="I64" s="9" t="str">
-        <f t="shared" si="6"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList', 'Purchase Order to Account Payable');</v>
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BankAccount.Transaction', 'Bank Account');</v>
+      </c>
+    </row>
+    <row r="65" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B65" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E65" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000064</v>
+      </c>
+      <c r="F65" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.Currency.Transaction</v>
+      </c>
+      <c r="G65" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Currency</v>
+      </c>
+      <c r="I65" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Currency.Transaction', 'Currency');</v>
+      </c>
+    </row>
+    <row r="66" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B66" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E66" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000065</v>
+      </c>
+      <c r="F66" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+      </c>
+      <c r="G66" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Exchange Rate</v>
+      </c>
+      <c r="I66" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Transaction', 'Exchange Rate');</v>
+      </c>
+    </row>
+    <row r="67" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B67" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E67" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000066</v>
+      </c>
+      <c r="F67" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+      </c>
+      <c r="G67" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Exchange Rate Summary</v>
+      </c>
+      <c r="I67" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Report.DataList', 'Exchange Rate Summary');</v>
+      </c>
+    </row>
+    <row r="68" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B68" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E68" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000067</v>
+      </c>
+      <c r="F68" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.PaymentTerm.Transaction</v>
+      </c>
+      <c r="G68" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Payment Term</v>
+      </c>
+      <c r="I68" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.PaymentTerm.Transaction', 'Payment Term');</v>
+      </c>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B69" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E69" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000068</v>
+      </c>
+      <c r="F69" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.General.MasterData.Period.Transaction</v>
+      </c>
+      <c r="G69" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Period</v>
+      </c>
+      <c r="I69" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Period.Transaction', 'Period');</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B70" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E70" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000069</v>
+      </c>
+      <c r="F70" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+      </c>
+      <c r="G70" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Asset Category</v>
+      </c>
+      <c r="I70" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.AssetCategory.Transaction', 'Asset Category');</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B71" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E71" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000070</v>
+      </c>
+      <c r="F71" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+      </c>
+      <c r="G71" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Chart of Account</v>
+      </c>
+      <c r="I71" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.ChartOfAccount.Transaction', 'Chart of Account');</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B72" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E72" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000071</v>
+      </c>
+      <c r="F72" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+      </c>
+      <c r="G72" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Depreciation Method</v>
+      </c>
+      <c r="I72" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationMethod.Transaction', 'Depreciation Method');</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B73" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E73" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000072</v>
+      </c>
+      <c r="F73" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+      </c>
+      <c r="G73" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Depreciation Rate Years</v>
+      </c>
+      <c r="I73" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationRateYears.Transaction', 'Depreciation Rate Years');</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B74" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E74" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000073</v>
+      </c>
+      <c r="F74" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+      </c>
+      <c r="G74" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Value Added Tax</v>
+      </c>
+      <c r="I74" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Taxation.MasterData.ValueAddedTax.Transaction', 'Value Added Tax');</v>
+      </c>
+    </row>
+    <row r="75" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B75" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E75" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000074</v>
+      </c>
+      <c r="F75" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+      </c>
+      <c r="G75" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>General Journal</v>
+      </c>
+      <c r="I75" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Transaction', 'General Journal');</v>
+      </c>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B76" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E76" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000075</v>
+      </c>
+      <c r="F76" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+      </c>
+      <c r="G76" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>General Journal Summary</v>
+      </c>
+      <c r="I76" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Report.DataList', 'General Journal Summary');</v>
+      </c>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B77" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E77" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000076</v>
+      </c>
+      <c r="F77" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+      </c>
+      <c r="G77" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Reimbursement</v>
+      </c>
+      <c r="I77" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Transaction', 'Reimbursement');</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B78" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E78" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000077</v>
+      </c>
+      <c r="F78" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+      </c>
+      <c r="G78" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Reimbursement Summary</v>
+      </c>
+      <c r="I78" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Report.DataList', 'Reimbursement Summary');</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B79" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E79" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000078</v>
+      </c>
+      <c r="F79" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+      </c>
+      <c r="G79" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Reimbursement to Debit Note</v>
+      </c>
+      <c r="I79" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList', 'Reimbursement to Debit Note');</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B80" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E80" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000079</v>
+      </c>
+      <c r="F80" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.DebitNote.Transaction</v>
+      </c>
+      <c r="G80" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Debit Note</v>
+      </c>
+      <c r="I80" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Transaction', 'Debit Note');</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B81" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E81" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000080</v>
+      </c>
+      <c r="F81" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+      </c>
+      <c r="G81" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Debit Note Summary</v>
+      </c>
+      <c r="I81" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Report.DataList', 'Debit Note Summary');</v>
+      </c>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B82" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E82" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000081</v>
+      </c>
+      <c r="F82" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.CreditNote.Transaction</v>
+      </c>
+      <c r="G82" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Credit Note</v>
+      </c>
+      <c r="I82" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Transaction', 'Credit Note');</v>
+      </c>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B83" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E83" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000082</v>
+      </c>
+      <c r="F83" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+      </c>
+      <c r="G83" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Credit Note Summary</v>
+      </c>
+      <c r="I83" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Report.DataList', 'Credit Note Summary');</v>
+      </c>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B84" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E84" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000083</v>
+      </c>
+      <c r="F84" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.Loan.Transaction</v>
+      </c>
+      <c r="G84" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Loan</v>
+      </c>
+      <c r="I84" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Transaction', 'Loan');</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B85" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E85" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000084</v>
+      </c>
+      <c r="F85" s="3" t="str">
+        <f t="shared" ref="F85:F98" si="13">IF(EXACT(B85, ""), "", B85)</f>
+        <v>Module.Finance.Data.Loan.Report.DataList</v>
+      </c>
+      <c r="G85" s="3" t="str">
+        <f t="shared" ref="G85:G98" si="14">IF(EXACT(C85, ""), "", C85)</f>
+        <v>Loan Summary</v>
+      </c>
+      <c r="I85" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Report.DataList', 'Loan Summary');</v>
+      </c>
+    </row>
+    <row r="86" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B86" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E86" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000085</v>
+      </c>
+      <c r="F86" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+      </c>
+      <c r="G86" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Loan to Loan Settlement</v>
+      </c>
+      <c r="I86" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList', 'Loan to Loan Settlement');</v>
+      </c>
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B87" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E87" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000086</v>
+      </c>
+      <c r="F87" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+      </c>
+      <c r="G87" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Loan Settlement</v>
+      </c>
+      <c r="I87" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Transaction', 'Loan Settlement');</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B88" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E88" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000087</v>
+      </c>
+      <c r="F88" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+      </c>
+      <c r="G88" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Loan Settlement Summary</v>
+      </c>
+      <c r="I88" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Report.DataList', 'Loan Settlement Summary');</v>
+      </c>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B89" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E89" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000088</v>
+      </c>
+      <c r="F89" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.CashBank.Transaction</v>
+      </c>
+      <c r="G89" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Cash &amp; Bank</v>
+      </c>
+      <c r="I89" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Transaction', 'Cash &amp; Bank');</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B90" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E90" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000089</v>
+      </c>
+      <c r="F90" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.CashBank.Report.DataList</v>
+      </c>
+      <c r="G90" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Cash &amp; Bank Summary</v>
+      </c>
+      <c r="I90" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Report.DataList', 'Cash &amp; Bank Summary');</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B91" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E91" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000090</v>
+      </c>
+      <c r="F91" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+      </c>
+      <c r="G91" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Account Payable</v>
+      </c>
+      <c r="I91" s="9" t="str">
+        <f t="shared" si="12"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Transaction', 'Account Payable');</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B92" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E92" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000091</v>
+      </c>
+      <c r="F92" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
+      </c>
+      <c r="G92" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Account Payable Summary</v>
+      </c>
+      <c r="I92" s="9" t="str">
+        <f t="shared" ref="I92:I98" si="15">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B92, ""),"null", CONCATENATE("'", $F92, "'")), ", ", IF(EXACT($B92, ""), "null", CONCATENATE("'", $G92, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Report.DataList', 'Account Payable Summary');</v>
+      </c>
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B93" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E93" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000092</v>
+      </c>
+      <c r="F93" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.SalesInvoice.Transaction</v>
+      </c>
+      <c r="G93" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Sales Invoice</v>
+      </c>
+      <c r="I93" s="9" t="str">
+        <f t="shared" si="15"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Transaction', 'Sales Invoice');</v>
+      </c>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B94" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E94" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000093</v>
+      </c>
+      <c r="F94" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
+      </c>
+      <c r="G94" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Sales Invoice Summary</v>
+      </c>
+      <c r="I94" s="9" t="str">
+        <f t="shared" si="15"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Report.DataList', 'Sales Invoice Summary');</v>
+      </c>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B95" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E95" s="8">
+        <f t="shared" ref="E95:E98" si="16">IF(ISNUMBER($E94), $E94+1, 97000000000001)</f>
+        <v>97000000000094</v>
+      </c>
+      <c r="F95" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
+      </c>
+      <c r="G95" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Sales Invoice to Credit Note</v>
+      </c>
+      <c r="I95" s="9" t="str">
+        <f t="shared" si="15"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList', 'Sales Invoice to Credit Note');</v>
+      </c>
+    </row>
+    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B96" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E96" s="8">
+        <f t="shared" si="16"/>
+        <v>97000000000095</v>
+      </c>
+      <c r="F96" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+      </c>
+      <c r="G96" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Tax Reconciliation</v>
+      </c>
+      <c r="I96" s="9" t="str">
+        <f t="shared" si="15"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Transaction', 'Tax Reconciliation');</v>
+      </c>
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B97" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="E97" s="8">
+        <f t="shared" si="16"/>
+        <v>97000000000096</v>
+      </c>
+      <c r="F97" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+      </c>
+      <c r="G97" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Tax Reconciliation Summary</v>
+      </c>
+      <c r="I97" s="9" t="str">
+        <f t="shared" si="15"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Report.DataList', 'Tax Reconciliation Summary');</v>
+      </c>
+    </row>
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B98" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E98" s="8">
+        <f t="shared" si="16"/>
+        <v>97000000000097</v>
+      </c>
+      <c r="F98" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
+      </c>
+      <c r="G98" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v>Customer</v>
+      </c>
+      <c r="I98" s="9" t="str">
+        <f t="shared" si="15"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.MasterData.Customer.Transaction', 'Customer');</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_Menu.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_Menu.xlsx
@@ -15995,7 +15995,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:I98"/>
+  <dimension ref="B1:K98"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
@@ -16008,7 +16008,7 @@
     <col min="8" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" s="6" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:11" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B1" s="6" t="s">
         <v>69</v>
       </c>
@@ -16019,7 +16019,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B2" s="2" t="s">
         <v>114</v>
       </c>
@@ -16042,8 +16042,25 @@
         <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B2, ""),"null", CONCATENATE("'", $F2, "'")), ", ", IF(EXACT($B2, ""), "null", CONCATENATE("'", $G2, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'System.Login', 'Login');</v>
       </c>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K2" s="1" t="str">
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B2, ""), "null", CONCATENATE("'", SUBSTITUTE($B2, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G2, ""), "null", CONCATENATE("'", SUBSTITUTE($G2, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'System.Login'::varchar,'caption', 'Login'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>115</v>
       </c>
@@ -16063,11 +16080,28 @@
         <v>Logout</v>
       </c>
       <c r="I3" s="9" t="str">
-        <f t="shared" ref="I3:I98" si="3">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B3, ""),"null", CONCATENATE("'", $F3, "'")), ", ", IF(EXACT($B3, ""), "null", CONCATENATE("'", $G3, "'")), ");")</f>
+        <f t="shared" ref="I3:I27" si="3">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B3, ""),"null", CONCATENATE("'", $F3, "'")), ", ", IF(EXACT($B3, ""), "null", CONCATENATE("'", $G3, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'System.Logout', 'Logout');</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K3" s="1" t="str">
+        <f t="shared" ref="K3:K66" si="4">CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B3, ""), "null", CONCATENATE("'", SUBSTITUTE($B3, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G3, ""), "null", CONCATENATE("'", SUBSTITUTE($G3, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'System.Logout'::varchar,'caption', 'Logout'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>116</v>
       </c>
@@ -16090,8 +16124,12 @@
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'System.Lock', 'Lock');</v>
       </c>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K4" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'System.Lock'::varchar,'caption', 'Lock'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>235</v>
       </c>
@@ -16103,7 +16141,7 @@
         <v>97000000000004</v>
       </c>
       <c r="F5" s="3" t="str">
-        <f t="shared" ref="F5:F8" si="4">IF(EXACT(B5, ""), "", B5)</f>
+        <f t="shared" ref="F5:F8" si="5">IF(EXACT(B5, ""), "", B5)</f>
         <v>Dashboard.Home</v>
       </c>
       <c r="G5" s="3" t="str">
@@ -16114,8 +16152,12 @@
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.Home', 'Dashboard');</v>
       </c>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K5" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Dashboard.Home'::varchar,'caption', 'Dashboard'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>92</v>
       </c>
@@ -16127,19 +16169,23 @@
         <v>97000000000005</v>
       </c>
       <c r="F6" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Dashboard.DocumentTracking</v>
       </c>
       <c r="G6" s="3" t="str">
-        <f t="shared" ref="G6:G8" si="5">IF(EXACT(C6, ""), "", C6)</f>
+        <f t="shared" ref="G6:G8" si="6">IF(EXACT(C6, ""), "", C6)</f>
         <v>Document Tracking</v>
       </c>
       <c r="I6" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.DocumentTracking', 'Document Tracking');</v>
       </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K6" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Dashboard.DocumentTracking'::varchar,'caption', 'Document Tracking'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>150</v>
       </c>
@@ -16151,19 +16197,23 @@
         <v>97000000000006</v>
       </c>
       <c r="F7" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Dashboard.MyDocumentTracking</v>
       </c>
       <c r="G7" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>My Document Tracking</v>
       </c>
       <c r="I7" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.MyDocumentTracking', 'My Document Tracking');</v>
       </c>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K7" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Dashboard.MyDocumentTracking'::varchar,'caption', 'My Document Tracking'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
         <v>151</v>
       </c>
@@ -16175,19 +16225,23 @@
         <v>97000000000007</v>
       </c>
       <c r="F8" s="3" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>Dashboard.MyDocumentDisposition</v>
       </c>
       <c r="G8" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>My Document Disposition</v>
       </c>
       <c r="I8" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Dashboard.MyDocumentDisposition', 'My Document Disposition');</v>
       </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K8" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Dashboard.MyDocumentDisposition'::varchar,'caption', 'My Document Disposition'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
         <v>134</v>
       </c>
@@ -16199,19 +16253,23 @@
         <v>97000000000008</v>
       </c>
       <c r="F9" s="3" t="str">
-        <f t="shared" ref="F9:F18" si="6">IF(EXACT(B9, ""), "", B9)</f>
+        <f t="shared" ref="F9:F18" si="7">IF(EXACT(B9, ""), "", B9)</f>
         <v>Module.General.MasterData.Country.Transaction</v>
       </c>
       <c r="G9" s="3" t="str">
-        <f t="shared" ref="G9:G18" si="7">IF(EXACT(C9, ""), "", C9)</f>
+        <f t="shared" ref="G9:G18" si="8">IF(EXACT(C9, ""), "", C9)</f>
         <v>Country</v>
       </c>
       <c r="I9" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Country.Transaction', 'Country');</v>
       </c>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K9" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Country.Transaction'::varchar,'caption', 'Country'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
         <v>135</v>
       </c>
@@ -16223,19 +16281,23 @@
         <v>97000000000009</v>
       </c>
       <c r="F10" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
       </c>
       <c r="G10" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Province / State</v>
       </c>
       <c r="I10" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction', 'Province / State');</v>
       </c>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K10" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction'::varchar,'caption', 'Province / State'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>136</v>
       </c>
@@ -16247,19 +16309,23 @@
         <v>97000000000010</v>
       </c>
       <c r="F11" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction</v>
       </c>
       <c r="G11" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Municipality / Regency</v>
       </c>
       <c r="I11" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction', 'Municipality / Regency');</v>
       </c>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K11" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CountryAdministrativeAreaLevel2.Transaction'::varchar,'caption', 'Municipality / Regency'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>137</v>
       </c>
@@ -16271,19 +16337,23 @@
         <v>97000000000011</v>
       </c>
       <c r="F12" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction</v>
       </c>
       <c r="G12" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>District</v>
       </c>
       <c r="I12" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction', 'District');</v>
       </c>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K12" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CountryAdministrativeAreaLevel3.Transaction'::varchar,'caption', 'District'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
         <v>138</v>
       </c>
@@ -16295,19 +16365,23 @@
         <v>97000000000012</v>
       </c>
       <c r="F13" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction</v>
       </c>
       <c r="G13" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Urban Village / Village</v>
       </c>
       <c r="I13" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction', 'Urban Village / Village');</v>
       </c>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K13" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CountryAdministrativeAreaLevel4.Transaction'::varchar,'caption', 'Urban Village / Village'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
         <v>133</v>
       </c>
@@ -16319,19 +16393,23 @@
         <v>97000000000013</v>
       </c>
       <c r="F14" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Module.General.MasterData.BusinessDocumentType.Transaction</v>
       </c>
       <c r="G14" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Business Document Type</v>
       </c>
       <c r="I14" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BusinessDocumentType.Transaction', 'Business Document Type');</v>
       </c>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K14" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BusinessDocumentType.Transaction'::varchar,'caption', 'Business Document Type'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>183</v>
       </c>
@@ -16343,19 +16421,23 @@
         <v>97000000000014</v>
       </c>
       <c r="F15" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Module.General.MasterData.BusinessDocument.Transaction</v>
       </c>
       <c r="G15" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Business Document</v>
       </c>
       <c r="I15" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BusinessDocument.Transaction', 'Business Document');</v>
       </c>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K15" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BusinessDocument.Transaction'::varchar,'caption', 'Business Document'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>184</v>
       </c>
@@ -16367,19 +16449,23 @@
         <v>97000000000015</v>
       </c>
       <c r="F16" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Module.General.MasterData.BusinessDocumentVersion.Transaction</v>
       </c>
       <c r="G16" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Business Document Version</v>
       </c>
       <c r="I16" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BusinessDocumentVersion.Transaction', 'Business Document Version');</v>
       </c>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K16" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BusinessDocumentVersion.Transaction'::varchar,'caption', 'Business Document Version'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>226</v>
       </c>
@@ -16391,19 +16477,23 @@
         <v>97000000000016</v>
       </c>
       <c r="F17" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Module.General.MasterData.MenuManagement.Transaction</v>
       </c>
       <c r="G17" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Menu Management</v>
       </c>
       <c r="I17" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.MenuManagement.Transaction', 'Menu Management');</v>
       </c>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K17" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.MenuManagement.Transaction'::varchar,'caption', 'Menu Management'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>237</v>
       </c>
@@ -16415,19 +16505,23 @@
         <v>97000000000017</v>
       </c>
       <c r="F18" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
       </c>
       <c r="G18" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Privilege Menu</v>
       </c>
       <c r="I18" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.PrivilegeMenu.Transaction', 'Privilege Menu');</v>
       </c>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K18" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.PrivilegeMenu.Transaction'::varchar,'caption', 'Privilege Menu'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
         <v>239</v>
       </c>
@@ -16439,19 +16533,23 @@
         <v>97000000000018</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f t="shared" ref="F19:F33" si="8">IF(EXACT(B19, ""), "", B19)</f>
+        <f t="shared" ref="F19:F20" si="9">IF(EXACT(B19, ""), "", B19)</f>
         <v>Module.General.MasterData.Workflow.Transaction</v>
       </c>
       <c r="G19" s="3" t="str">
-        <f t="shared" ref="G19:G33" si="9">IF(EXACT(C19, ""), "", C19)</f>
+        <f t="shared" ref="G19:G20" si="10">IF(EXACT(C19, ""), "", C19)</f>
         <v>Workflow</v>
       </c>
       <c r="I19" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Workflow.Transaction', 'Workflow');</v>
       </c>
-    </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K19" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Workflow.Transaction'::varchar,'caption', 'Workflow'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
         <v>269</v>
       </c>
@@ -16463,19 +16561,23 @@
         <v>97000000000019</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Module.Budgeting.MasterData.Budget.Transaction</v>
       </c>
       <c r="G20" s="3" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>Budget</v>
       </c>
       <c r="I20" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.MasterData.Budget.Transaction', 'Budget');</v>
       </c>
-    </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K20" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.MasterData.Budget.Transaction'::varchar,'caption', 'Budget'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>279</v>
       </c>
@@ -16487,19 +16589,23 @@
         <v>97000000000020</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f t="shared" ref="F21:F84" si="10">IF(EXACT(B21, ""), "", B21)</f>
+        <f t="shared" ref="F21:F84" si="11">IF(EXACT(B21, ""), "", B21)</f>
         <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
       </c>
       <c r="G21" s="3" t="str">
-        <f t="shared" ref="G21:G84" si="11">IF(EXACT(C21, ""), "", C21)</f>
+        <f t="shared" ref="G21:G84" si="12">IF(EXACT(C21, ""), "", C21)</f>
         <v>Sub Budget</v>
       </c>
       <c r="I21" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.MasterData.BudgetSection.Transaction', 'Sub Budget');</v>
       </c>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K21" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.MasterData.BudgetSection.Transaction'::varchar,'caption', 'Sub Budget'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>241</v>
       </c>
@@ -16511,19 +16617,23 @@
         <v>97000000000021</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Budgeting.Data.ModifyBudget.Transaction</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Modify Budget</v>
       </c>
       <c r="I22" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.ModifyBudget.Transaction', 'Modify Budget');</v>
       </c>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K22" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.ModifyBudget.Transaction'::varchar,'caption', 'Modify Budget'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>196</v>
       </c>
@@ -16535,19 +16645,23 @@
         <v>97000000000022</v>
       </c>
       <c r="F23" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
       </c>
       <c r="G23" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Modify Budget Summary</v>
       </c>
       <c r="I23" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.ModifyBudget.Report.Resume', 'Report Modify Budget Summary');</v>
       </c>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K23" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.ModifyBudget.Report.Resume'::varchar,'caption', 'Report Modify Budget Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>243</v>
       </c>
@@ -16559,19 +16673,23 @@
         <v>97000000000023</v>
       </c>
       <c r="F24" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Budgeting.Data.Work.Transaction</v>
       </c>
       <c r="G24" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Work</v>
       </c>
       <c r="I24" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.Work.Transaction', 'Work');</v>
       </c>
-    </row>
-    <row r="25" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K24" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.Work.Transaction'::varchar,'caption', 'Work'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
         <v>197</v>
       </c>
@@ -16583,19 +16701,23 @@
         <v>97000000000024</v>
       </c>
       <c r="F25" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Budgeting.Data.CFS.Report.Resume</v>
       </c>
       <c r="G25" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Cost Financial Structure</v>
       </c>
       <c r="I25" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.CFS.Report.Resume', 'Report Cost Financial Structure');</v>
       </c>
-    </row>
-    <row r="26" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K25" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.CFS.Report.Resume'::varchar,'caption', 'Report Cost Financial Structure'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>132</v>
       </c>
@@ -16607,19 +16729,23 @@
         <v>97000000000025</v>
       </c>
       <c r="F26" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
       </c>
       <c r="G26" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Blood Aglutinogen Type</v>
       </c>
       <c r="I26" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BloodAglutinogenType.Transaction', 'Blood Aglutinogen Type');</v>
       </c>
-    </row>
-    <row r="27" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K26" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BloodAglutinogenType.Transaction'::varchar,'caption', 'Blood Aglutinogen Type'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>290</v>
       </c>
@@ -16631,19 +16757,23 @@
         <v>97000000000026</v>
       </c>
       <c r="F27" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.Person.Transaction</v>
       </c>
       <c r="G27" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Person</v>
       </c>
       <c r="I27" s="9" t="str">
         <f t="shared" si="3"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Person.Transaction', 'Person');</v>
       </c>
-    </row>
-    <row r="28" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K27" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Person.Transaction'::varchar,'caption', 'Person'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>146</v>
       </c>
@@ -16655,19 +16785,23 @@
         <v>97000000000027</v>
       </c>
       <c r="F28" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.Religion.Transaction</v>
       </c>
       <c r="G28" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Religion</v>
       </c>
       <c r="I28" s="9" t="str">
-        <f t="shared" ref="I28:I91" si="12">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B28, ""),"null", CONCATENATE("'", $F28, "'")), ", ", IF(EXACT($B28, ""), "null", CONCATENATE("'", $G28, "'")), ");")</f>
+        <f t="shared" ref="I28:I91" si="13">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B28, ""),"null", CONCATENATE("'", $F28, "'")), ", ", IF(EXACT($B28, ""), "null", CONCATENATE("'", $G28, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Religion.Transaction', 'Religion');</v>
       </c>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K28" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Religion.Transaction'::varchar,'caption', 'Religion'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>293</v>
       </c>
@@ -16679,19 +16813,23 @@
         <v>97000000000028</v>
       </c>
       <c r="F29" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.UserRole.Transaction</v>
       </c>
       <c r="G29" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Role</v>
       </c>
       <c r="I29" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.UserRole.Transaction', 'Role');</v>
       </c>
-    </row>
-    <row r="30" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K29" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.UserRole.Transaction'::varchar,'caption', 'Role'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>288</v>
       </c>
@@ -16703,19 +16841,23 @@
         <v>97000000000029</v>
       </c>
       <c r="F30" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
       </c>
       <c r="G30" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Department</v>
       </c>
       <c r="I30" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.MasterData.OrganizationalDepartment.Transaction', 'Department');</v>
       </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K30" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.MasterData.OrganizationalDepartment.Transaction'::varchar,'caption', 'Department'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>127</v>
       </c>
@@ -16727,19 +16869,23 @@
         <v>97000000000030</v>
       </c>
       <c r="F31" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
       </c>
       <c r="G31" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Person Work Time Sheet</v>
       </c>
       <c r="I31" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction', 'Person Work Time Sheet');</v>
       </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K31" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction'::varchar,'caption', 'Person Work Time Sheet'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>286</v>
       </c>
@@ -16751,19 +16897,23 @@
         <v>97000000000031</v>
       </c>
       <c r="F32" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
       </c>
       <c r="G32" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Person Work Time Sheet Summary</v>
       </c>
       <c r="I32" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList', 'Person Work Time Sheet Summary');</v>
       </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K32" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList'::varchar,'caption', 'Person Work Time Sheet Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>282</v>
       </c>
@@ -16775,19 +16925,23 @@
         <v>97000000000032</v>
       </c>
       <c r="F33" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
       </c>
       <c r="G33" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Sallary Allocation</v>
       </c>
       <c r="I33" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.SallaryAllocation.Transaction', 'Sallary Allocation');</v>
       </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K33" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.SallaryAllocation.Transaction'::varchar,'caption', 'Sallary Allocation'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B34" s="4" t="s">
         <v>284</v>
       </c>
@@ -16799,19 +16953,23 @@
         <v>97000000000033</v>
       </c>
       <c r="F34" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
       </c>
       <c r="G34" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Sallary Allocation Summary</v>
       </c>
       <c r="I34" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.SallaryAllocation.Report.DataList', 'Sallary Allocation Summary');</v>
       </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K34" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.SallaryAllocation.Report.DataList'::varchar,'caption', 'Sallary Allocation Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
         <v>188</v>
       </c>
@@ -16823,19 +16981,23 @@
         <v>97000000000034</v>
       </c>
       <c r="F35" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.Warehouse.Transaction</v>
       </c>
       <c r="G35" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Warehouse</v>
       </c>
       <c r="I35" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Warehouse.Transaction', 'Warehouse');</v>
       </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K35" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Warehouse.Transaction'::varchar,'caption', 'Warehouse'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>144</v>
       </c>
@@ -16847,19 +17009,23 @@
         <v>97000000000035</v>
       </c>
       <c r="F36" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.ProductType.Transaction</v>
       </c>
       <c r="G36" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Product Type</v>
       </c>
       <c r="I36" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.ProductType.Transaction', 'Product Type');</v>
       </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K36" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.ProductType.Transaction'::varchar,'caption', 'Product Type'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>142</v>
       </c>
@@ -16871,19 +17037,23 @@
         <v>97000000000036</v>
       </c>
       <c r="F37" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.Product.Transaction</v>
       </c>
       <c r="G37" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Product</v>
       </c>
       <c r="I37" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Product.Transaction', 'Product');</v>
       </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K37" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Product.Transaction'::varchar,'caption', 'Product'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
         <v>152</v>
       </c>
@@ -16895,19 +17065,23 @@
         <v>97000000000037</v>
       </c>
       <c r="F38" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
       </c>
       <c r="G38" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Delivery Order</v>
       </c>
       <c r="I38" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Transaction', 'Delivery Order');</v>
       </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K38" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.DeliveryOrder.Transaction'::varchar,'caption', 'Delivery Order'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>153</v>
       </c>
@@ -16919,19 +17093,23 @@
         <v>97000000000038</v>
       </c>
       <c r="F39" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
       </c>
       <c r="G39" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report DO Summary</v>
       </c>
       <c r="I39" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Report.DataList', 'Report DO Summary');</v>
       </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K39" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.DeliveryOrder.Report.DataList'::varchar,'caption', 'Report DO Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>301</v>
       </c>
@@ -16943,19 +17121,23 @@
         <v>97000000000039</v>
       </c>
       <c r="F40" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
       </c>
       <c r="G40" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report DO to Material Receive</v>
       </c>
       <c r="I40" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList', 'Report DO to Material Receive');</v>
       </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K40" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList'::varchar,'caption', 'Report DO to Material Receive'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>191</v>
       </c>
@@ -16967,19 +17149,23 @@
         <v>97000000000040</v>
       </c>
       <c r="F41" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
       </c>
       <c r="G41" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Material Receive</v>
       </c>
       <c r="I41" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceive.Transaction', 'Material Receive');</v>
       </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K41" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReceive.Transaction'::varchar,'caption', 'Material Receive'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>294</v>
       </c>
@@ -16991,19 +17177,23 @@
         <v>97000000000041</v>
       </c>
       <c r="F42" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
       </c>
       <c r="G42" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Material Receive Summary</v>
       </c>
       <c r="I42" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceive.Report.DataList', 'Report Material Receive Summary');</v>
       </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K42" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReceive.Report.DataList'::varchar,'caption', 'Report Material Receive Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>302</v>
       </c>
@@ -17015,19 +17205,23 @@
         <v>97000000000042</v>
       </c>
       <c r="F43" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
       </c>
       <c r="G43" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Material Receive to Material Return</v>
       </c>
       <c r="I43" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList', 'Report Material Receive to Material Return');</v>
       </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K43" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList'::varchar,'caption', 'Report Material Receive to Material Return'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>193</v>
       </c>
@@ -17039,19 +17233,23 @@
         <v>97000000000043</v>
       </c>
       <c r="F44" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
       </c>
       <c r="G44" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Material Return</v>
       </c>
       <c r="I44" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Transaction', 'Material Return');</v>
       </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K44" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReturn.Transaction'::varchar,'caption', 'Material Return'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B45" s="4" t="s">
         <v>192</v>
       </c>
@@ -17063,19 +17261,23 @@
         <v>97000000000044</v>
       </c>
       <c r="F45" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
       </c>
       <c r="G45" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Material Return Summary</v>
       </c>
       <c r="I45" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Report.DataList', 'Report Material Return Summary');</v>
       </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K45" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReturn.Report.DataList'::varchar,'caption', 'Report Material Return Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>119</v>
       </c>
@@ -17087,19 +17289,23 @@
         <v>97000000000045</v>
       </c>
       <c r="F46" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.Advance.Transaction</v>
       </c>
       <c r="G46" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Advance Request</v>
       </c>
       <c r="I46" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Transaction', 'Advance Request');</v>
       </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K46" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Advance.Transaction'::varchar,'caption', 'Advance Request'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>120</v>
       </c>
@@ -17111,19 +17317,23 @@
         <v>97000000000046</v>
       </c>
       <c r="F47" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.Advance.Report.DataList</v>
       </c>
       <c r="G47" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Advance Summary</v>
       </c>
       <c r="I47" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Report.DataList', 'Report Advance Summary');</v>
       </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K47" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Advance.Report.DataList'::varchar,'caption', 'Report Advance Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>297</v>
       </c>
@@ -17135,19 +17345,23 @@
         <v>97000000000047</v>
       </c>
       <c r="F48" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
       </c>
       <c r="G48" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Advance to Advance Settlement</v>
       </c>
       <c r="I48" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList', 'Report Advance to Advance Settlement');</v>
       </c>
-    </row>
-    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K48" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList'::varchar,'caption', 'Report Advance to Advance Settlement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
         <v>121</v>
       </c>
@@ -17159,19 +17373,23 @@
         <v>97000000000048</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
       </c>
       <c r="G49" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>AdvanceSettlement</v>
       </c>
       <c r="I49" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Transaction', 'AdvanceSettlement');</v>
       </c>
-    </row>
-    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K49" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.AdvanceSettlement.Transaction'::varchar,'caption', 'AdvanceSettlement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>122</v>
       </c>
@@ -17183,19 +17401,23 @@
         <v>97000000000049</v>
       </c>
       <c r="F50" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
       </c>
       <c r="G50" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Advance Settlement Summary</v>
       </c>
       <c r="I50" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Report.DataList', 'Report Advance Settlement Summary');</v>
       </c>
-    </row>
-    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K50" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.AdvanceSettlement.Report.DataList'::varchar,'caption', 'Report Advance Settlement Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>202</v>
       </c>
@@ -17207,19 +17429,23 @@
         <v>97000000000050</v>
       </c>
       <c r="F51" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
       </c>
       <c r="G51" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>BusinessTrip Request</v>
       </c>
       <c r="I51" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Transaction', 'BusinessTrip Request');</v>
       </c>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K51" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTrip.Transaction'::varchar,'caption', 'BusinessTrip Request'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>201</v>
       </c>
@@ -17231,19 +17457,23 @@
         <v>97000000000051</v>
       </c>
       <c r="F52" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
       </c>
       <c r="G52" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report BusinessTrip Request Summary</v>
       </c>
       <c r="I52" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Report.DataList', 'Report BusinessTrip Request Summary');</v>
       </c>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K52" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTrip.Report.DataList'::varchar,'caption', 'Report BusinessTrip Request Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
         <v>299</v>
       </c>
@@ -17255,19 +17485,23 @@
         <v>97000000000052</v>
       </c>
       <c r="F53" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="G53" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report BusinessTrip to BusinessTrip Settlement</v>
       </c>
       <c r="I53" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList', 'Report BusinessTrip to BusinessTrip Settlement');</v>
       </c>
-    </row>
-    <row r="54" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K53" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList'::varchar,'caption', 'Report BusinessTrip to BusinessTrip Settlement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B54" s="2" t="s">
         <v>200</v>
       </c>
@@ -17279,19 +17513,23 @@
         <v>97000000000053</v>
       </c>
       <c r="F54" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
       </c>
       <c r="G54" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>BusinessTrip Settlement</v>
       </c>
       <c r="I54" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Transaction', 'BusinessTrip Settlement');</v>
       </c>
-    </row>
-    <row r="55" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K54" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTripSettlement.Transaction'::varchar,'caption', 'BusinessTrip Settlement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B55" s="4" t="s">
         <v>199</v>
       </c>
@@ -17303,19 +17541,23 @@
         <v>97000000000054</v>
       </c>
       <c r="F55" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="G55" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report BusinessTrip Settlement Summary</v>
       </c>
       <c r="I55" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList', 'Report BusinessTrip Settlement Summary');</v>
       </c>
-    </row>
-    <row r="56" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K55" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList'::varchar,'caption', 'Report BusinessTrip Settlement Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
         <v>159</v>
       </c>
@@ -17327,19 +17569,23 @@
         <v>97000000000055</v>
       </c>
       <c r="F56" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
       </c>
       <c r="G56" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Supplier</v>
       </c>
       <c r="I56" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.MasterData.Supplier.Transaction', 'Supplier');</v>
       </c>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K56" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.MasterData.Supplier.Transaction'::varchar,'caption', 'Supplier'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
         <v>157</v>
       </c>
@@ -17351,19 +17597,23 @@
         <v>97000000000056</v>
       </c>
       <c r="F57" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
       </c>
       <c r="G57" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Purchase Requisition</v>
       </c>
       <c r="I57" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Transaction', 'Purchase Requisition');</v>
       </c>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K57" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisition.Transaction'::varchar,'caption', 'Purchase Requisition'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
         <v>158</v>
       </c>
@@ -17375,19 +17625,23 @@
         <v>97000000000057</v>
       </c>
       <c r="F58" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
       </c>
       <c r="G58" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Purchase Requisition Summary</v>
       </c>
       <c r="I58" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList', 'Report Purchase Requisition Summary');</v>
       </c>
-    </row>
-    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K58" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList'::varchar,'caption', 'Report Purchase Requisition Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
         <v>206</v>
       </c>
@@ -17399,19 +17653,23 @@
         <v>97000000000058</v>
       </c>
       <c r="F59" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
       </c>
       <c r="G59" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Purchase Requisition To Purchase Order</v>
       </c>
       <c r="I59" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList', 'Report Purchase Requisition To Purchase Order');</v>
       </c>
-    </row>
-    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K59" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList'::varchar,'caption', 'Report Purchase Requisition To Purchase Order'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
         <v>155</v>
       </c>
@@ -17423,19 +17681,23 @@
         <v>97000000000059</v>
       </c>
       <c r="F60" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
       </c>
       <c r="G60" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Purchase Order</v>
       </c>
       <c r="I60" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Transaction', 'Purchase Order');</v>
       </c>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K60" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrder.Transaction'::varchar,'caption', 'Purchase Order'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
         <v>156</v>
       </c>
@@ -17447,19 +17709,23 @@
         <v>97000000000060</v>
       </c>
       <c r="F61" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
       </c>
       <c r="G61" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Report Purchase Order Summary</v>
       </c>
       <c r="I61" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList', 'Report Purchase Order Summary');</v>
       </c>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K61" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList'::varchar,'caption', 'Report Purchase Order Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>224</v>
       </c>
@@ -17471,19 +17737,23 @@
         <v>97000000000061</v>
       </c>
       <c r="F62" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
       </c>
       <c r="G62" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Purchase Order to Account Payable</v>
       </c>
       <c r="I62" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList', 'Purchase Order to Account Payable');</v>
       </c>
-    </row>
-    <row r="63" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K62" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList'::varchar,'caption', 'Purchase Order to Account Payable'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
         <v>265</v>
       </c>
@@ -17495,19 +17765,23 @@
         <v>97000000000062</v>
       </c>
       <c r="F63" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.Bank.Transaction</v>
       </c>
       <c r="G63" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Bank</v>
       </c>
       <c r="I63" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Bank.Transaction', 'Bank');</v>
       </c>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K63" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Bank.Transaction'::varchar,'caption', 'Bank'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B64" s="2" t="s">
         <v>267</v>
       </c>
@@ -17519,19 +17793,23 @@
         <v>97000000000063</v>
       </c>
       <c r="F64" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.BankAccount.Transaction</v>
       </c>
       <c r="G64" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Bank Account</v>
       </c>
       <c r="I64" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BankAccount.Transaction', 'Bank Account');</v>
       </c>
-    </row>
-    <row r="65" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K64" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BankAccount.Transaction'::varchar,'caption', 'Bank Account'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
         <v>139</v>
       </c>
@@ -17543,19 +17821,23 @@
         <v>97000000000064</v>
       </c>
       <c r="F65" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.Currency.Transaction</v>
       </c>
       <c r="G65" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Currency</v>
       </c>
       <c r="I65" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Currency.Transaction', 'Currency');</v>
       </c>
-    </row>
-    <row r="66" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K65" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Currency.Transaction'::varchar,'caption', 'Currency'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
         <v>245</v>
       </c>
@@ -17567,19 +17849,23 @@
         <v>97000000000065</v>
       </c>
       <c r="F66" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
       </c>
       <c r="G66" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Exchange Rate</v>
       </c>
       <c r="I66" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Transaction', 'Exchange Rate');</v>
       </c>
-    </row>
-    <row r="67" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K66" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CurrencyExchangeRate.Transaction'::varchar,'caption', 'Exchange Rate'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
         <v>253</v>
       </c>
@@ -17591,19 +17877,36 @@
         <v>97000000000066</v>
       </c>
       <c r="F67" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
       </c>
       <c r="G67" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Exchange Rate Summary</v>
       </c>
       <c r="I67" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Report.DataList', 'Exchange Rate Summary');</v>
       </c>
-    </row>
-    <row r="68" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K67" s="1" t="str">
+        <f t="shared" ref="K67:K98" si="14">CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B67, ""), "null", CONCATENATE("'", SUBSTITUTE($B67, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G67, ""), "null", CONCATENATE("'", SUBSTITUTE($G67, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CurrencyExchangeRate.Report.DataList'::varchar,'caption', 'Exchange Rate Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B68" s="2" t="s">
         <v>276</v>
       </c>
@@ -17615,19 +17918,23 @@
         <v>97000000000067</v>
       </c>
       <c r="F68" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.PaymentTerm.Transaction</v>
       </c>
       <c r="G68" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Payment Term</v>
       </c>
       <c r="I68" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.PaymentTerm.Transaction', 'Payment Term');</v>
       </c>
-    </row>
-    <row r="69" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K68" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.PaymentTerm.Transaction'::varchar,'caption', 'Payment Term'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B69" s="2" t="s">
         <v>140</v>
       </c>
@@ -17639,19 +17946,23 @@
         <v>97000000000068</v>
       </c>
       <c r="F69" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.General.MasterData.Period.Transaction</v>
       </c>
       <c r="G69" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Period</v>
       </c>
       <c r="I69" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Period.Transaction', 'Period');</v>
       </c>
-    </row>
-    <row r="70" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K69" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Period.Transaction'::varchar,'caption', 'Period'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
         <v>263</v>
       </c>
@@ -17663,19 +17974,23 @@
         <v>97000000000069</v>
       </c>
       <c r="F70" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
       </c>
       <c r="G70" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Asset Category</v>
       </c>
       <c r="I70" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.AssetCategory.Transaction', 'Asset Category');</v>
       </c>
-    </row>
-    <row r="71" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K70" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.AssetCategory.Transaction'::varchar,'caption', 'Asset Category'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
         <v>270</v>
       </c>
@@ -17687,19 +18002,23 @@
         <v>97000000000070</v>
       </c>
       <c r="F71" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
       </c>
       <c r="G71" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Chart of Account</v>
       </c>
       <c r="I71" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.ChartOfAccount.Transaction', 'Chart of Account');</v>
       </c>
-    </row>
-    <row r="72" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K71" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.ChartOfAccount.Transaction'::varchar,'caption', 'Chart of Account'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
         <v>273</v>
       </c>
@@ -17711,19 +18030,23 @@
         <v>97000000000071</v>
       </c>
       <c r="F72" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
       </c>
       <c r="G72" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Depreciation Method</v>
       </c>
       <c r="I72" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationMethod.Transaction', 'Depreciation Method');</v>
       </c>
-    </row>
-    <row r="73" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K72" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.DepreciationMethod.Transaction'::varchar,'caption', 'Depreciation Method'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B73" s="2" t="s">
         <v>275</v>
       </c>
@@ -17735,19 +18058,23 @@
         <v>97000000000072</v>
       </c>
       <c r="F73" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
       </c>
       <c r="G73" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Depreciation Rate Years</v>
       </c>
       <c r="I73" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationRateYears.Transaction', 'Depreciation Rate Years');</v>
       </c>
-    </row>
-    <row r="74" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K73" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.DepreciationRateYears.Transaction'::varchar,'caption', 'Depreciation Rate Years'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
         <v>280</v>
       </c>
@@ -17759,19 +18086,23 @@
         <v>97000000000073</v>
       </c>
       <c r="F74" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
       </c>
       <c r="G74" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Value Added Tax</v>
       </c>
       <c r="I74" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Taxation.MasterData.ValueAddedTax.Transaction', 'Value Added Tax');</v>
       </c>
-    </row>
-    <row r="75" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K74" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Taxation.MasterData.ValueAddedTax.Transaction'::varchar,'caption', 'Value Added Tax'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="75" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
         <v>247</v>
       </c>
@@ -17783,19 +18114,23 @@
         <v>97000000000074</v>
       </c>
       <c r="F75" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
       </c>
       <c r="G75" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>General Journal</v>
       </c>
       <c r="I75" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Transaction', 'General Journal');</v>
       </c>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K75" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralJournal.Transaction'::varchar,'caption', 'General Journal'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="76" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
         <v>255</v>
       </c>
@@ -17807,19 +18142,23 @@
         <v>97000000000075</v>
       </c>
       <c r="F76" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
       </c>
       <c r="G76" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>General Journal Summary</v>
       </c>
       <c r="I76" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Report.DataList', 'General Journal Summary');</v>
       </c>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K76" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralJournal.Report.DataList'::varchar,'caption', 'General Journal Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="77" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
         <v>217</v>
       </c>
@@ -17831,19 +18170,23 @@
         <v>97000000000076</v>
       </c>
       <c r="F77" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.Reimbursement.Transaction</v>
       </c>
       <c r="G77" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Reimbursement</v>
       </c>
       <c r="I77" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Transaction', 'Reimbursement');</v>
       </c>
-    </row>
-    <row r="78" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K77" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Reimbursement.Transaction'::varchar,'caption', 'Reimbursement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="78" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
         <v>218</v>
       </c>
@@ -17855,19 +18198,23 @@
         <v>97000000000077</v>
       </c>
       <c r="F78" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
       </c>
       <c r="G78" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Reimbursement Summary</v>
       </c>
       <c r="I78" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Report.DataList', 'Reimbursement Summary');</v>
       </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K78" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Reimbursement.Report.DataList'::varchar,'caption', 'Reimbursement Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="79" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B79" s="2" t="s">
         <v>219</v>
       </c>
@@ -17879,19 +18226,23 @@
         <v>97000000000078</v>
       </c>
       <c r="F79" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
       </c>
       <c r="G79" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Reimbursement to Debit Note</v>
       </c>
       <c r="I79" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList', 'Reimbursement to Debit Note');</v>
       </c>
-    </row>
-    <row r="80" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K79" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList'::varchar,'caption', 'Reimbursement to Debit Note'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="80" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B80" s="2" t="s">
         <v>123</v>
       </c>
@@ -17903,19 +18254,23 @@
         <v>97000000000079</v>
       </c>
       <c r="F80" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.DebitNote.Transaction</v>
       </c>
       <c r="G80" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Debit Note</v>
       </c>
       <c r="I80" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Transaction', 'Debit Note');</v>
       </c>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K80" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.DebitNote.Transaction'::varchar,'caption', 'Debit Note'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="81" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
         <v>124</v>
       </c>
@@ -17927,19 +18282,23 @@
         <v>97000000000080</v>
       </c>
       <c r="F81" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.DebitNote.Report.DataList</v>
       </c>
       <c r="G81" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Debit Note Summary</v>
       </c>
       <c r="I81" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Report.DataList', 'Debit Note Summary');</v>
       </c>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K81" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.DebitNote.Report.DataList'::varchar,'caption', 'Debit Note Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="82" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B82" s="2" t="s">
         <v>162</v>
       </c>
@@ -17951,19 +18310,23 @@
         <v>97000000000081</v>
       </c>
       <c r="F82" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.CreditNote.Transaction</v>
       </c>
       <c r="G82" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Credit Note</v>
       </c>
       <c r="I82" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Transaction', 'Credit Note');</v>
       </c>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K82" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CreditNote.Transaction'::varchar,'caption', 'Credit Note'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="83" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B83" s="2" t="s">
         <v>163</v>
       </c>
@@ -17975,19 +18338,23 @@
         <v>97000000000082</v>
       </c>
       <c r="F83" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.CreditNote.Report.DataList</v>
       </c>
       <c r="G83" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Credit Note Summary</v>
       </c>
       <c r="I83" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Report.DataList', 'Credit Note Summary');</v>
       </c>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K83" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CreditNote.Report.DataList'::varchar,'caption', 'Credit Note Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="84" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B84" s="2" t="s">
         <v>165</v>
       </c>
@@ -17999,19 +18366,23 @@
         <v>97000000000083</v>
       </c>
       <c r="F84" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>Module.Finance.Data.Loan.Transaction</v>
       </c>
       <c r="G84" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>Loan</v>
       </c>
       <c r="I84" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Transaction', 'Loan');</v>
       </c>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K84" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Loan.Transaction'::varchar,'caption', 'Loan'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B85" s="2" t="s">
         <v>166</v>
       </c>
@@ -18023,19 +18394,23 @@
         <v>97000000000084</v>
       </c>
       <c r="F85" s="3" t="str">
-        <f t="shared" ref="F85:F98" si="13">IF(EXACT(B85, ""), "", B85)</f>
+        <f t="shared" ref="F85:F98" si="15">IF(EXACT(B85, ""), "", B85)</f>
         <v>Module.Finance.Data.Loan.Report.DataList</v>
       </c>
       <c r="G85" s="3" t="str">
-        <f t="shared" ref="G85:G98" si="14">IF(EXACT(C85, ""), "", C85)</f>
+        <f t="shared" ref="G85:G98" si="16">IF(EXACT(C85, ""), "", C85)</f>
         <v>Loan Summary</v>
       </c>
       <c r="I85" s="9" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Report.DataList', 'Loan Summary');</v>
       </c>
-    </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="K85" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Loan.Report.DataList'::varchar,'caption', 'Loan Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
         <v>220</v>
       </c>
@@ -18047,19 +18422,23 @@
         <v>97000000000085</v>
       </c>
       <c r="F86" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
+      </c>
+      <c r="G86" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Loan to Loan Settlement</v>
+      </c>
+      <c r="I86" s="9" t="str">
         <f t="shared" si="13"/>
-        <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
-      </c>
-      <c r="G86" s="3" t="str">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList', 'Loan to Loan Settlement');</v>
+      </c>
+      <c r="K86" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Loan to Loan Settlement</v>
-      </c>
-      <c r="I86" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList', 'Loan to Loan Settlement');</v>
-      </c>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList'::varchar,'caption', 'Loan to Loan Settlement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B87" s="2" t="s">
         <v>168</v>
       </c>
@@ -18071,19 +18450,23 @@
         <v>97000000000086</v>
       </c>
       <c r="F87" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
+      </c>
+      <c r="G87" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Loan Settlement</v>
+      </c>
+      <c r="I87" s="9" t="str">
         <f t="shared" si="13"/>
-        <v>Module.Finance.Data.LoanSettlement.Transaction</v>
-      </c>
-      <c r="G87" s="3" t="str">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Transaction', 'Loan Settlement');</v>
+      </c>
+      <c r="K87" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Loan Settlement</v>
-      </c>
-      <c r="I87" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Transaction', 'Loan Settlement');</v>
-      </c>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanSettlement.Transaction'::varchar,'caption', 'Loan Settlement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B88" s="2" t="s">
         <v>169</v>
       </c>
@@ -18095,19 +18478,23 @@
         <v>97000000000087</v>
       </c>
       <c r="F88" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
+      </c>
+      <c r="G88" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Loan Settlement Summary</v>
+      </c>
+      <c r="I88" s="9" t="str">
         <f t="shared" si="13"/>
-        <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
-      </c>
-      <c r="G88" s="3" t="str">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Report.DataList', 'Loan Settlement Summary');</v>
+      </c>
+      <c r="K88" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Loan Settlement Summary</v>
-      </c>
-      <c r="I88" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Report.DataList', 'Loan Settlement Summary');</v>
-      </c>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanSettlement.Report.DataList'::varchar,'caption', 'Loan Settlement Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B89" s="2" t="s">
         <v>221</v>
       </c>
@@ -18119,19 +18506,23 @@
         <v>97000000000088</v>
       </c>
       <c r="F89" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>Module.Finance.Data.CashBank.Transaction</v>
+      </c>
+      <c r="G89" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Cash &amp; Bank</v>
+      </c>
+      <c r="I89" s="9" t="str">
         <f t="shared" si="13"/>
-        <v>Module.Finance.Data.CashBank.Transaction</v>
-      </c>
-      <c r="G89" s="3" t="str">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Transaction', 'Cash &amp; Bank');</v>
+      </c>
+      <c r="K89" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Cash &amp; Bank</v>
-      </c>
-      <c r="I89" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Transaction', 'Cash &amp; Bank');</v>
-      </c>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CashBank.Transaction'::varchar,'caption', 'Cash &amp; Bank'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B90" s="2" t="s">
         <v>222</v>
       </c>
@@ -18143,19 +18534,23 @@
         <v>97000000000089</v>
       </c>
       <c r="F90" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>Module.Finance.Data.CashBank.Report.DataList</v>
+      </c>
+      <c r="G90" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Cash &amp; Bank Summary</v>
+      </c>
+      <c r="I90" s="9" t="str">
         <f t="shared" si="13"/>
-        <v>Module.Finance.Data.CashBank.Report.DataList</v>
-      </c>
-      <c r="G90" s="3" t="str">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Report.DataList', 'Cash &amp; Bank Summary');</v>
+      </c>
+      <c r="K90" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Cash &amp; Bank Summary</v>
-      </c>
-      <c r="I90" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Report.DataList', 'Cash &amp; Bank Summary');</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CashBank.Report.DataList'::varchar,'caption', 'Cash &amp; Bank Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B91" s="2" t="s">
         <v>125</v>
       </c>
@@ -18167,19 +18562,23 @@
         <v>97000000000090</v>
       </c>
       <c r="F91" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
+      </c>
+      <c r="G91" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Account Payable</v>
+      </c>
+      <c r="I91" s="9" t="str">
         <f t="shared" si="13"/>
-        <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
-      </c>
-      <c r="G91" s="3" t="str">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Transaction', 'Account Payable');</v>
+      </c>
+      <c r="K91" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Account Payable</v>
-      </c>
-      <c r="I91" s="9" t="str">
-        <f t="shared" si="12"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Transaction', 'Account Payable');</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PaymentInstruction.Transaction'::varchar,'caption', 'Account Payable'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B92" s="2" t="s">
         <v>126</v>
       </c>
@@ -18191,19 +18590,23 @@
         <v>97000000000091</v>
       </c>
       <c r="F92" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
       </c>
       <c r="G92" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Account Payable Summary</v>
+      </c>
+      <c r="I92" s="9" t="str">
+        <f t="shared" ref="I92:I98" si="17">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B92, ""),"null", CONCATENATE("'", $F92, "'")), ", ", IF(EXACT($B92, ""), "null", CONCATENATE("'", $G92, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Report.DataList', 'Account Payable Summary');</v>
+      </c>
+      <c r="K92" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Account Payable Summary</v>
-      </c>
-      <c r="I92" s="9" t="str">
-        <f t="shared" ref="I92:I98" si="15">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B92, ""),"null", CONCATENATE("'", $F92, "'")), ", ", IF(EXACT($B92, ""), "null", CONCATENATE("'", $G92, "'")), ");")</f>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Report.DataList', 'Account Payable Summary');</v>
-      </c>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PaymentInstruction.Report.DataList'::varchar,'caption', 'Account Payable Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B93" s="2" t="s">
         <v>249</v>
       </c>
@@ -18215,19 +18618,23 @@
         <v>97000000000092</v>
       </c>
       <c r="F93" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Module.Finance.Data.SalesInvoice.Transaction</v>
       </c>
       <c r="G93" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Sales Invoice</v>
+      </c>
+      <c r="I93" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Transaction', 'Sales Invoice');</v>
+      </c>
+      <c r="K93" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Sales Invoice</v>
-      </c>
-      <c r="I93" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Transaction', 'Sales Invoice');</v>
-      </c>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.SalesInvoice.Transaction'::varchar,'caption', 'Sales Invoice'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B94" s="2" t="s">
         <v>257</v>
       </c>
@@ -18239,19 +18646,23 @@
         <v>97000000000093</v>
       </c>
       <c r="F94" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
       </c>
       <c r="G94" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Sales Invoice Summary</v>
+      </c>
+      <c r="I94" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Report.DataList', 'Sales Invoice Summary');</v>
+      </c>
+      <c r="K94" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Sales Invoice Summary</v>
-      </c>
-      <c r="I94" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Report.DataList', 'Sales Invoice Summary');</v>
-      </c>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.SalesInvoice.Report.DataList'::varchar,'caption', 'Sales Invoice Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B95" s="2" t="s">
         <v>259</v>
       </c>
@@ -18259,23 +18670,27 @@
         <v>260</v>
       </c>
       <c r="E95" s="8">
-        <f t="shared" ref="E95:E98" si="16">IF(ISNUMBER($E94), $E94+1, 97000000000001)</f>
+        <f t="shared" ref="E95:E98" si="18">IF(ISNUMBER($E94), $E94+1, 97000000000001)</f>
         <v>97000000000094</v>
       </c>
       <c r="F95" s="3" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="15"/>
         <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
       </c>
       <c r="G95" s="3" t="str">
+        <f t="shared" si="16"/>
+        <v>Sales Invoice to Credit Note</v>
+      </c>
+      <c r="I95" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList', 'Sales Invoice to Credit Note');</v>
+      </c>
+      <c r="K95" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Sales Invoice to Credit Note</v>
-      </c>
-      <c r="I95" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList', 'Sales Invoice to Credit Note');</v>
-      </c>
-    </row>
-    <row r="96" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList'::varchar,'caption', 'Sales Invoice to Credit Note'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B96" s="2" t="s">
         <v>251</v>
       </c>
@@ -18283,23 +18698,27 @@
         <v>252</v>
       </c>
       <c r="E96" s="8">
+        <f t="shared" si="18"/>
+        <v>97000000000095</v>
+      </c>
+      <c r="F96" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
+      </c>
+      <c r="G96" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>97000000000095</v>
-      </c>
-      <c r="F96" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
-      </c>
-      <c r="G96" s="3" t="str">
+        <v>Tax Reconciliation</v>
+      </c>
+      <c r="I96" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Transaction', 'Tax Reconciliation');</v>
+      </c>
+      <c r="K96" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Tax Reconciliation</v>
-      </c>
-      <c r="I96" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Transaction', 'Tax Reconciliation');</v>
-      </c>
-    </row>
-    <row r="97" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.TaxReconciliation.Transaction'::varchar,'caption', 'Tax Reconciliation'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B97" s="4" t="s">
         <v>261</v>
       </c>
@@ -18307,23 +18726,27 @@
         <v>262</v>
       </c>
       <c r="E97" s="8">
+        <f t="shared" si="18"/>
+        <v>97000000000096</v>
+      </c>
+      <c r="F97" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
+      </c>
+      <c r="G97" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>97000000000096</v>
-      </c>
-      <c r="F97" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
-      </c>
-      <c r="G97" s="3" t="str">
+        <v>Tax Reconciliation Summary</v>
+      </c>
+      <c r="I97" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Report.DataList', 'Tax Reconciliation Summary');</v>
+      </c>
+      <c r="K97" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Tax Reconciliation Summary</v>
-      </c>
-      <c r="I97" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Report.DataList', 'Tax Reconciliation Summary');</v>
-      </c>
-    </row>
-    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.TaxReconciliation.Report.DataList'::varchar,'caption', 'Tax Reconciliation Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B98" s="2" t="s">
         <v>304</v>
       </c>
@@ -18331,20 +18754,24 @@
         <v>305</v>
       </c>
       <c r="E98" s="8">
+        <f t="shared" si="18"/>
+        <v>97000000000097</v>
+      </c>
+      <c r="F98" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
+      </c>
+      <c r="G98" s="3" t="str">
         <f t="shared" si="16"/>
-        <v>97000000000097</v>
-      </c>
-      <c r="F98" s="3" t="str">
-        <f t="shared" si="13"/>
-        <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
-      </c>
-      <c r="G98" s="3" t="str">
+        <v>Customer</v>
+      </c>
+      <c r="I98" s="9" t="str">
+        <f t="shared" si="17"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.MasterData.Customer.Transaction', 'Customer');</v>
+      </c>
+      <c r="K98" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>Customer</v>
-      </c>
-      <c r="I98" s="9" t="str">
-        <f t="shared" si="15"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.MasterData.Customer.Transaction', 'Customer');</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.CustomerRelation.MasterData.Customer.Transaction'::varchar,'caption', 'Customer'::varchar)))::varchar;</v>
       </c>
     </row>
   </sheetData>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_Menu.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_Menu.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="MainOLD" sheetId="1" r:id="rId1"/>
     <sheet name="Main" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="307">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="340">
   <si>
     <t>System</t>
   </si>
@@ -647,9 +648,6 @@
     <t>Debit Note Summary</t>
   </si>
   <si>
-    <t>Reimbursement to Debit Note</t>
-  </si>
-  <si>
     <t>Credit Note Summary</t>
   </si>
   <si>
@@ -659,9 +657,6 @@
     <t>Loan Settlement Summary</t>
   </si>
   <si>
-    <t>Loan to Loan Settlement</t>
-  </si>
-  <si>
     <t>Account Payable</t>
   </si>
   <si>
@@ -686,9 +681,6 @@
     <t>Module.Finance.Data.CashBank.Report.DataList</t>
   </si>
   <si>
-    <t>Purchase Order to Account Payable</t>
-  </si>
-  <si>
     <t>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</t>
   </si>
   <si>
@@ -936,6 +928,114 @@
   </si>
   <si>
     <t>Report Material Receive Summary</t>
+  </si>
+  <si>
+    <t>Module.Budgeting.Data.ProgressBudget.Transaction</t>
+  </si>
+  <si>
+    <t>Progress Budget</t>
+  </si>
+  <si>
+    <t>Module.Budgeting.Data.Budget.Report.Resume</t>
+  </si>
+  <si>
+    <t>Module.Budgeting.Data.ProgressBudget.Report.Resume</t>
+  </si>
+  <si>
+    <t>Report Budget Summary</t>
+  </si>
+  <si>
+    <t>Report Progress Budget Summary</t>
+  </si>
+  <si>
+    <t>S-Curve Summary</t>
+  </si>
+  <si>
+    <t>Module.Budgeting.Data.SCurve.Report.Resume</t>
+  </si>
+  <si>
+    <t>Module.FixedAsset.Data.GoodsIdentity.Transaction</t>
+  </si>
+  <si>
+    <t>Fixed Asset</t>
+  </si>
+  <si>
+    <t>Module.FixedAsset.Data.GoodsIdentity.Report.DataList</t>
+  </si>
+  <si>
+    <t>Fixed Asset Summary</t>
+  </si>
+  <si>
+    <t>Module.Accounting.Data.GeneralLedger.Report.DataList</t>
+  </si>
+  <si>
+    <t>General Ledger Summary</t>
+  </si>
+  <si>
+    <t>Loan to Loan Settlement Summary</t>
+  </si>
+  <si>
+    <t>Module.Accounting.Data.ProfitLoss.Report.DataList</t>
+  </si>
+  <si>
+    <t>Module.Accounting.Data.BalanceSheet.Report.DataList</t>
+  </si>
+  <si>
+    <t>Profit Loss Summary</t>
+  </si>
+  <si>
+    <t>Balance Sheet</t>
+  </si>
+  <si>
+    <t>Reimbursement to Debit Note Summary</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.User.Transaction</t>
+  </si>
+  <si>
+    <t>Module.General.MasterData.Work.Transaction</t>
+  </si>
+  <si>
+    <t>Stock Opname</t>
+  </si>
+  <si>
+    <t>Module.SupplyChain.Data.PhysicalInventoryCount.Transaction</t>
+  </si>
+  <si>
+    <t>Module.SupplyChain.Data.PhysicalInventoryCount.Report.DataList</t>
+  </si>
+  <si>
+    <t>Report Stock Opname Summary</t>
+  </si>
+  <si>
+    <t>Module.SupplyChain.MasterData.SupplierCategory.Transaction</t>
+  </si>
+  <si>
+    <t>Supplier Category</t>
+  </si>
+  <si>
+    <t>Module.SupplyChain.MasterData.SupplierSubCategory.Transaction</t>
+  </si>
+  <si>
+    <t>Supplier Sub Category</t>
+  </si>
+  <si>
+    <t>Report Purchase Order to Account Payable Summary</t>
+  </si>
+  <si>
+    <t>Module.CustomerRelation.MasterData.CustomerOrder.Transaction</t>
+  </si>
+  <si>
+    <t>Customer Order</t>
+  </si>
+  <si>
+    <t>Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList</t>
+  </si>
+  <si>
+    <t>Customer Order Summary</t>
+  </si>
+  <si>
+    <t>Module.Budgeting.Data.Budget.Report.Transaction</t>
   </si>
 </sst>
 </file>
@@ -15995,7 +16095,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K98"/>
+  <dimension ref="B1:K116"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.140625" style="1" customWidth="1"/>
@@ -16068,7 +16168,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="8">
-        <f t="shared" ref="E3:E94" si="0">IF(ISNUMBER($E2), $E2+1, 97000000000001)</f>
+        <f t="shared" ref="E3:E84" si="0">IF(ISNUMBER($E2), $E2+1, 97000000000001)</f>
         <v>97000000000002</v>
       </c>
       <c r="F3" s="3" t="str">
@@ -16076,15 +16176,15 @@
         <v>System.Logout</v>
       </c>
       <c r="G3" s="3" t="str">
-        <f t="shared" ref="G3:G5" si="2">IF(EXACT(C3, ""), "", C3)</f>
+        <f t="shared" ref="G3:G4" si="2">IF(EXACT(C3, ""), "", C3)</f>
         <v>Logout</v>
       </c>
       <c r="I3" s="9" t="str">
-        <f t="shared" ref="I3:I27" si="3">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B3, ""),"null", CONCATENATE("'", $F3, "'")), ", ", IF(EXACT($B3, ""), "null", CONCATENATE("'", $G3, "'")), ");")</f>
+        <f t="shared" ref="I3:I67" si="3">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B3, ""),"null", CONCATENATE("'", $F3, "'")), ", ", IF(EXACT($B3, ""), "null", CONCATENATE("'", $G3, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'System.Logout', 'Logout');</v>
       </c>
       <c r="K3" s="1" t="str">
-        <f t="shared" ref="K3:K66" si="4">CONCATENATE(
+        <f t="shared" ref="K3:K67" si="4">CONCATENATE(
 "varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
 "'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
 "'sysLoginSession_RefID', varSystemLoginSession::bigint,",
@@ -16131,21 +16231,21 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E5" s="8">
         <f t="shared" si="0"/>
         <v>97000000000004</v>
       </c>
       <c r="F5" s="3" t="str">
-        <f t="shared" ref="F5:F8" si="5">IF(EXACT(B5, ""), "", B5)</f>
+        <f t="shared" ref="F5:F34" si="5">IF(EXACT(B5, ""), "", B5)</f>
         <v>Dashboard.Home</v>
       </c>
       <c r="G5" s="3" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="G5:G34" si="6">IF(EXACT(C5, ""), "", C5)</f>
         <v>Dashboard</v>
       </c>
       <c r="I5" s="9" t="str">
@@ -16173,7 +16273,7 @@
         <v>Dashboard.DocumentTracking</v>
       </c>
       <c r="G6" s="3" t="str">
-        <f t="shared" ref="G6:G8" si="6">IF(EXACT(C6, ""), "", C6)</f>
+        <f t="shared" si="6"/>
         <v>Document Tracking</v>
       </c>
       <c r="I6" s="9" t="str">
@@ -16253,11 +16353,11 @@
         <v>97000000000008</v>
       </c>
       <c r="F9" s="3" t="str">
-        <f t="shared" ref="F9:F18" si="7">IF(EXACT(B9, ""), "", B9)</f>
+        <f t="shared" si="5"/>
         <v>Module.General.MasterData.Country.Transaction</v>
       </c>
       <c r="G9" s="3" t="str">
-        <f t="shared" ref="G9:G18" si="8">IF(EXACT(C9, ""), "", C9)</f>
+        <f t="shared" si="6"/>
         <v>Country</v>
       </c>
       <c r="I9" s="9" t="str">
@@ -16281,11 +16381,11 @@
         <v>97000000000009</v>
       </c>
       <c r="F10" s="3" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="F10:F73" si="7">IF(EXACT(B10, ""), "", B10)</f>
         <v>Module.General.MasterData.CountryAdministrativeAreaLevel1.Transaction</v>
       </c>
       <c r="G10" s="3" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="G10:G73" si="8">IF(EXACT(C10, ""), "", C10)</f>
         <v>Province / State</v>
       </c>
       <c r="I10" s="9" t="str">
@@ -16467,10 +16567,10 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E17" s="8">
         <f t="shared" si="0"/>
@@ -16494,11 +16594,11 @@
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>238</v>
+      <c r="B18" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>117</v>
       </c>
       <c r="E18" s="8">
         <f t="shared" si="0"/>
@@ -16506,52 +16606,52 @@
       </c>
       <c r="F18" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
+        <v>Module.Budgeting.MasterData.Budget.Transaction</v>
       </c>
       <c r="G18" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>Privilege Menu</v>
+        <v>Budget</v>
       </c>
       <c r="I18" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.PrivilegeMenu.Transaction', 'Privilege Menu');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.MasterData.Budget.Transaction', 'Budget');</v>
       </c>
       <c r="K18" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.PrivilegeMenu.Transaction'::varchar,'caption', 'Privilege Menu'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.MasterData.Budget.Transaction'::varchar,'caption', 'Budget'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>240</v>
+      <c r="B19" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="E19" s="8">
         <f t="shared" si="0"/>
         <v>97000000000018</v>
       </c>
       <c r="F19" s="3" t="str">
-        <f t="shared" ref="F19:F20" si="9">IF(EXACT(B19, ""), "", B19)</f>
-        <v>Module.General.MasterData.Workflow.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
       </c>
       <c r="G19" s="3" t="str">
-        <f t="shared" ref="G19:G20" si="10">IF(EXACT(C19, ""), "", C19)</f>
-        <v>Workflow</v>
+        <f t="shared" si="8"/>
+        <v>Sub Budget</v>
       </c>
       <c r="I19" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Workflow.Transaction', 'Workflow');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.MasterData.BudgetSection.Transaction', 'Sub Budget');</v>
       </c>
       <c r="K19" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Workflow.Transaction'::varchar,'caption', 'Workflow'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.MasterData.BudgetSection.Transaction'::varchar,'caption', 'Sub Budget'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>269</v>
+        <v>339</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>117</v>
@@ -16561,67 +16661,67 @@
         <v>97000000000019</v>
       </c>
       <c r="F20" s="3" t="str">
-        <f t="shared" si="9"/>
-        <v>Module.Budgeting.MasterData.Budget.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Budgeting.Data.Budget.Report.Transaction</v>
       </c>
       <c r="G20" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v>Budget</v>
       </c>
       <c r="I20" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.MasterData.Budget.Transaction', 'Budget');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.Budget.Report.Transaction', 'Budget');</v>
       </c>
       <c r="K20" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.MasterData.Budget.Transaction'::varchar,'caption', 'Budget'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.Budget.Report.Transaction'::varchar,'caption', 'Budget'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>278</v>
+        <v>308</v>
       </c>
       <c r="E21" s="8">
         <f t="shared" si="0"/>
         <v>97000000000020</v>
       </c>
       <c r="F21" s="3" t="str">
-        <f t="shared" ref="F21:F84" si="11">IF(EXACT(B21, ""), "", B21)</f>
-        <v>Module.Budgeting.MasterData.BudgetSection.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Budgeting.Data.Budget.Report.Resume</v>
       </c>
       <c r="G21" s="3" t="str">
-        <f t="shared" ref="G21:G84" si="12">IF(EXACT(C21, ""), "", C21)</f>
-        <v>Sub Budget</v>
+        <f t="shared" si="8"/>
+        <v>Report Budget Summary</v>
       </c>
       <c r="I21" s="9" t="str">
-        <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.MasterData.BudgetSection.Transaction', 'Sub Budget');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B21, ""),"null", CONCATENATE("'", $F21, "'")), ", ", IF(EXACT($B21, ""), "null", CONCATENATE("'", $G21, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.Budget.Report.Resume', 'Report Budget Summary');</v>
       </c>
       <c r="K21" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.MasterData.BudgetSection.Transaction'::varchar,'caption', 'Sub Budget'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.Budget.Report.Resume'::varchar,'caption', 'Report Budget Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E22" s="8">
         <f t="shared" si="0"/>
         <v>97000000000021</v>
       </c>
       <c r="F22" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>Module.Budgeting.Data.ModifyBudget.Transaction</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>Modify Budget</v>
       </c>
       <c r="I22" s="9" t="str">
@@ -16645,11 +16745,11 @@
         <v>97000000000022</v>
       </c>
       <c r="F23" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>Module.Budgeting.Data.ModifyBudget.Report.Resume</v>
       </c>
       <c r="G23" s="3" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="8"/>
         <v>Report Modify Budget Summary</v>
       </c>
       <c r="I23" s="9" t="str">
@@ -16663,1233 +16763,1261 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>243</v>
+        <v>304</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>244</v>
+        <v>305</v>
       </c>
       <c r="E24" s="8">
         <f t="shared" si="0"/>
         <v>97000000000023</v>
       </c>
       <c r="F24" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Budgeting.Data.Work.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Budgeting.Data.ProgressBudget.Transaction</v>
       </c>
       <c r="G24" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Work</v>
+        <f t="shared" si="8"/>
+        <v>Progress Budget</v>
       </c>
       <c r="I24" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.Work.Transaction', 'Work');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.ProgressBudget.Transaction', 'Progress Budget');</v>
       </c>
       <c r="K24" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.Work.Transaction'::varchar,'caption', 'Work'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.ProgressBudget.Transaction'::varchar,'caption', 'Progress Budget'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B25" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>186</v>
+      <c r="B25" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>309</v>
       </c>
       <c r="E25" s="8">
         <f t="shared" si="0"/>
         <v>97000000000024</v>
       </c>
       <c r="F25" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
+        <f t="shared" si="7"/>
+        <v>Module.Budgeting.Data.ProgressBudget.Report.Resume</v>
       </c>
       <c r="G25" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Cost Financial Structure</v>
+        <f t="shared" si="8"/>
+        <v>Report Progress Budget Summary</v>
       </c>
       <c r="I25" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.CFS.Report.Resume', 'Report Cost Financial Structure');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.ProgressBudget.Report.Resume', 'Report Progress Budget Summary');</v>
       </c>
       <c r="K25" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.CFS.Report.Resume'::varchar,'caption', 'Report Cost Financial Structure'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.ProgressBudget.Report.Resume'::varchar,'caption', 'Report Progress Budget Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>132</v>
+        <v>311</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>187</v>
+        <v>310</v>
       </c>
       <c r="E26" s="8">
         <f t="shared" si="0"/>
         <v>97000000000025</v>
       </c>
       <c r="F26" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Budgeting.Data.SCurve.Report.Resume</v>
       </c>
       <c r="G26" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Blood Aglutinogen Type</v>
+        <f t="shared" si="8"/>
+        <v>S-Curve Summary</v>
       </c>
       <c r="I26" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BloodAglutinogenType.Transaction', 'Blood Aglutinogen Type');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.SCurve.Report.Resume', 'S-Curve Summary');</v>
       </c>
       <c r="K26" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BloodAglutinogenType.Transaction'::varchar,'caption', 'Blood Aglutinogen Type'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.SCurve.Report.Resume'::varchar,'caption', 'S-Curve Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
-        <v>290</v>
+        <v>240</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>291</v>
+        <v>241</v>
       </c>
       <c r="E27" s="8">
         <f t="shared" si="0"/>
         <v>97000000000026</v>
       </c>
       <c r="F27" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.Person.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Budgeting.Data.Work.Transaction</v>
       </c>
       <c r="G27" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Person</v>
+        <f t="shared" si="8"/>
+        <v>Work</v>
       </c>
       <c r="I27" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Person.Transaction', 'Person');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.Work.Transaction', 'Work');</v>
       </c>
       <c r="K27" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Person.Transaction'::varchar,'caption', 'Person'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.Work.Transaction'::varchar,'caption', 'Work'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B28" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>147</v>
+      <c r="B28" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>186</v>
       </c>
       <c r="E28" s="8">
         <f t="shared" si="0"/>
         <v>97000000000027</v>
       </c>
       <c r="F28" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.Religion.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Budgeting.Data.CFS.Report.Resume</v>
       </c>
       <c r="G28" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Religion</v>
+        <f t="shared" si="8"/>
+        <v>Report Cost Financial Structure</v>
       </c>
       <c r="I28" s="9" t="str">
-        <f t="shared" ref="I28:I91" si="13">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B28, ""),"null", CONCATENATE("'", $F28, "'")), ", ", IF(EXACT($B28, ""), "null", CONCATENATE("'", $G28, "'")), ");")</f>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Religion.Transaction', 'Religion');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.CFS.Report.Resume', 'Report Cost Financial Structure');</v>
       </c>
       <c r="K28" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Religion.Transaction'::varchar,'caption', 'Religion'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.CFS.Report.Resume'::varchar,'caption', 'Report Cost Financial Structure'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>293</v>
+        <v>132</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>292</v>
+        <v>187</v>
       </c>
       <c r="E29" s="8">
         <f t="shared" si="0"/>
         <v>97000000000028</v>
       </c>
       <c r="F29" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.UserRole.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.BloodAglutinogenType.Transaction</v>
       </c>
       <c r="G29" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Role</v>
+        <f t="shared" si="8"/>
+        <v>Blood Aglutinogen Type</v>
       </c>
       <c r="I29" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.UserRole.Transaction', 'Role');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B29, ""),"null", CONCATENATE("'", $F29, "'")), ", ", IF(EXACT($B29, ""), "null", CONCATENATE("'", $G29, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BloodAglutinogenType.Transaction', 'Blood Aglutinogen Type');</v>
       </c>
       <c r="K29" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.UserRole.Transaction'::varchar,'caption', 'Role'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BloodAglutinogenType.Transaction'::varchar,'caption', 'Blood Aglutinogen Type'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="E30" s="8">
         <f t="shared" si="0"/>
         <v>97000000000029</v>
       </c>
       <c r="F30" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.Person.Transaction</v>
       </c>
       <c r="G30" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Department</v>
+        <f t="shared" si="8"/>
+        <v>Person</v>
       </c>
       <c r="I30" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.MasterData.OrganizationalDepartment.Transaction', 'Department');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Person.Transaction', 'Person');</v>
       </c>
       <c r="K30" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.MasterData.OrganizationalDepartment.Transaction'::varchar,'caption', 'Department'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Person.Transaction'::varchar,'caption', 'Person'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
-        <v>127</v>
+        <v>234</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>128</v>
+        <v>235</v>
       </c>
       <c r="E31" s="8">
         <f t="shared" si="0"/>
         <v>97000000000030</v>
       </c>
       <c r="F31" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.PrivilegeMenu.Transaction</v>
       </c>
       <c r="G31" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Person Work Time Sheet</v>
+        <f t="shared" si="8"/>
+        <v>Privilege Menu</v>
       </c>
       <c r="I31" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction', 'Person Work Time Sheet');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.PrivilegeMenu.Transaction', 'Privilege Menu');</v>
       </c>
       <c r="K31" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction'::varchar,'caption', 'Person Work Time Sheet'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.PrivilegeMenu.Transaction'::varchar,'caption', 'Privilege Menu'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
-        <v>286</v>
+        <v>146</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>287</v>
+        <v>147</v>
       </c>
       <c r="E32" s="8">
         <f t="shared" si="0"/>
         <v>97000000000031</v>
       </c>
       <c r="F32" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.Religion.Transaction</v>
       </c>
       <c r="G32" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Person Work Time Sheet Summary</v>
+        <f t="shared" si="8"/>
+        <v>Religion</v>
       </c>
       <c r="I32" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList', 'Person Work Time Sheet Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Religion.Transaction', 'Religion');</v>
       </c>
       <c r="K32" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList'::varchar,'caption', 'Person Work Time Sheet Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Religion.Transaction'::varchar,'caption', 'Religion'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>282</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>283</v>
+        <v>72</v>
       </c>
       <c r="E33" s="8">
         <f t="shared" si="0"/>
         <v>97000000000032</v>
       </c>
       <c r="F33" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.User.Transaction</v>
       </c>
       <c r="G33" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sallary Allocation</v>
+        <f t="shared" si="8"/>
+        <v>User</v>
       </c>
       <c r="I33" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.SallaryAllocation.Transaction', 'Sallary Allocation');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B33, ""),"null", CONCATENATE("'", $F33, "'")), ", ", IF(EXACT($B33, ""), "null", CONCATENATE("'", $G33, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.User.Transaction', 'User');</v>
       </c>
       <c r="K33" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.SallaryAllocation.Transaction'::varchar,'caption', 'Sallary Allocation'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.User.Transaction'::varchar,'caption', 'User'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B34" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>285</v>
+      <c r="B34" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="E34" s="8">
         <f t="shared" si="0"/>
         <v>97000000000033</v>
       </c>
       <c r="F34" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.UserRole.Transaction</v>
       </c>
       <c r="G34" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Sallary Allocation Summary</v>
+        <f t="shared" si="8"/>
+        <v>Role</v>
       </c>
       <c r="I34" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.SallaryAllocation.Report.DataList', 'Sallary Allocation Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.UserRole.Transaction', 'Role');</v>
       </c>
       <c r="K34" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.SallaryAllocation.Report.DataList'::varchar,'caption', 'Sallary Allocation Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.UserRole.Transaction'::varchar,'caption', 'Role'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>161</v>
+        <v>237</v>
       </c>
       <c r="E35" s="8">
         <f t="shared" si="0"/>
         <v>97000000000034</v>
       </c>
       <c r="F35" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.Warehouse.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.Workflow.Transaction</v>
       </c>
       <c r="G35" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Warehouse</v>
+        <f t="shared" si="8"/>
+        <v>Workflow</v>
       </c>
       <c r="I35" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Warehouse.Transaction', 'Warehouse');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Workflow.Transaction', 'Workflow');</v>
       </c>
       <c r="K35" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Warehouse.Transaction'::varchar,'caption', 'Warehouse'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Workflow.Transaction'::varchar,'caption', 'Workflow'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>144</v>
+        <v>285</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>145</v>
+        <v>286</v>
       </c>
       <c r="E36" s="8">
         <f t="shared" si="0"/>
         <v>97000000000035</v>
       </c>
       <c r="F36" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.ProductType.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</v>
       </c>
       <c r="G36" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Product Type</v>
+        <f t="shared" si="8"/>
+        <v>Department</v>
       </c>
       <c r="I36" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.ProductType.Transaction', 'Product Type');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.MasterData.OrganizationalDepartment.Transaction', 'Department');</v>
       </c>
       <c r="K36" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.ProductType.Transaction'::varchar,'caption', 'Product Type'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.MasterData.OrganizationalDepartment.Transaction'::varchar,'caption', 'Department'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="37" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="E37" s="8">
         <f t="shared" si="0"/>
         <v>97000000000036</v>
       </c>
       <c r="F37" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.Product.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</v>
       </c>
       <c r="G37" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Product</v>
+        <f t="shared" si="8"/>
+        <v>Person Work Time Sheet</v>
       </c>
       <c r="I37" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Product.Transaction', 'Product');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B37, ""),"null", CONCATENATE("'", $F37, "'")), ", ", IF(EXACT($B37, ""), "null", CONCATENATE("'", $G37, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction', 'Person Work Time Sheet');</v>
       </c>
       <c r="K37" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Product.Transaction'::varchar,'caption', 'Product'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction'::varchar,'caption', 'Person Work Time Sheet'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>152</v>
+        <v>283</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>154</v>
+        <v>284</v>
       </c>
       <c r="E38" s="8">
         <f t="shared" si="0"/>
         <v>97000000000037</v>
       </c>
       <c r="F38" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</v>
       </c>
       <c r="G38" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Delivery Order</v>
+        <f t="shared" si="8"/>
+        <v>Person Work Time Sheet Summary</v>
       </c>
       <c r="I38" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Transaction', 'Delivery Order');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList', 'Person Work Time Sheet Summary');</v>
       </c>
       <c r="K38" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.DeliveryOrder.Transaction'::varchar,'caption', 'Delivery Order'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList'::varchar,'caption', 'Person Work Time Sheet Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
-        <v>153</v>
+        <v>279</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>190</v>
+        <v>280</v>
       </c>
       <c r="E39" s="8">
         <f t="shared" si="0"/>
         <v>97000000000038</v>
       </c>
       <c r="F39" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.HumanResource.Data.SallaryAllocation.Transaction</v>
       </c>
       <c r="G39" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report DO Summary</v>
+        <f t="shared" si="8"/>
+        <v>Sallary Allocation</v>
       </c>
       <c r="I39" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Report.DataList', 'Report DO Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.SallaryAllocation.Transaction', 'Sallary Allocation');</v>
       </c>
       <c r="K39" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.DeliveryOrder.Report.DataList'::varchar,'caption', 'Report DO Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.SallaryAllocation.Transaction'::varchar,'caption', 'Sallary Allocation'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B40" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>295</v>
+      <c r="B40" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>282</v>
       </c>
       <c r="E40" s="8">
         <f t="shared" si="0"/>
         <v>97000000000039</v>
       </c>
       <c r="F40" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.HumanResource.Data.SallaryAllocation.Report.DataList</v>
       </c>
       <c r="G40" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report DO to Material Receive</v>
+        <f t="shared" si="8"/>
+        <v>Sallary Allocation Summary</v>
       </c>
       <c r="I40" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList', 'Report DO to Material Receive');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.SallaryAllocation.Report.DataList', 'Sallary Allocation Summary');</v>
       </c>
       <c r="K40" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList'::varchar,'caption', 'Report DO to Material Receive'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.SallaryAllocation.Report.DataList'::varchar,'caption', 'Sallary Allocation Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
-        <v>191</v>
+        <v>142</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="E41" s="8">
         <f t="shared" si="0"/>
         <v>97000000000040</v>
       </c>
       <c r="F41" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.Product.Transaction</v>
       </c>
       <c r="G41" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Material Receive</v>
+        <f t="shared" si="8"/>
+        <v>Product</v>
       </c>
       <c r="I41" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceive.Transaction', 'Material Receive');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Product.Transaction', 'Product');</v>
       </c>
       <c r="K41" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReceive.Transaction'::varchar,'caption', 'Material Receive'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Product.Transaction'::varchar,'caption', 'Product'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
-        <v>294</v>
+        <v>144</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>306</v>
+        <v>145</v>
       </c>
       <c r="E42" s="8">
         <f t="shared" si="0"/>
         <v>97000000000041</v>
       </c>
       <c r="F42" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.ProductType.Transaction</v>
       </c>
       <c r="G42" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Material Receive Summary</v>
+        <f t="shared" si="8"/>
+        <v>Product Type</v>
       </c>
       <c r="I42" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceive.Report.DataList', 'Report Material Receive Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.ProductType.Transaction', 'Product Type');</v>
       </c>
       <c r="K42" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReceive.Report.DataList'::varchar,'caption', 'Report Material Receive Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.ProductType.Transaction'::varchar,'caption', 'Product Type'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>302</v>
+        <v>188</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>296</v>
+        <v>161</v>
       </c>
       <c r="E43" s="8">
         <f t="shared" si="0"/>
         <v>97000000000042</v>
       </c>
       <c r="F43" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.Warehouse.Transaction</v>
       </c>
       <c r="G43" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Material Receive to Material Return</v>
+        <f t="shared" si="8"/>
+        <v>Warehouse</v>
       </c>
       <c r="I43" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList', 'Report Material Receive to Material Return');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Warehouse.Transaction', 'Warehouse');</v>
       </c>
       <c r="K43" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList'::varchar,'caption', 'Report Material Receive to Material Return'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Warehouse.Transaction'::varchar,'caption', 'Warehouse'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>193</v>
+        <v>325</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>194</v>
+        <v>241</v>
       </c>
       <c r="E44" s="8">
         <f t="shared" si="0"/>
         <v>97000000000043</v>
       </c>
       <c r="F44" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.General.MasterData.Work.Transaction</v>
       </c>
       <c r="G44" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Material Return</v>
+        <f t="shared" si="8"/>
+        <v>Work</v>
       </c>
       <c r="I44" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Transaction', 'Material Return');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B44, ""),"null", CONCATENATE("'", $F44, "'")), ", ", IF(EXACT($B44, ""), "null", CONCATENATE("'", $G44, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Work.Transaction', 'Work');</v>
       </c>
       <c r="K44" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReturn.Transaction'::varchar,'caption', 'Material Return'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Work.Transaction'::varchar,'caption', 'Work'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B45" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>195</v>
+      <c r="B45" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="E45" s="8">
         <f t="shared" si="0"/>
         <v>97000000000044</v>
       </c>
       <c r="F45" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Transaction</v>
       </c>
       <c r="G45" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Material Return Summary</v>
+        <f t="shared" si="8"/>
+        <v>Delivery Order</v>
       </c>
       <c r="I45" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Report.DataList', 'Report Material Return Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Transaction', 'Delivery Order');</v>
       </c>
       <c r="K45" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReturn.Report.DataList'::varchar,'caption', 'Report Material Return Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.DeliveryOrder.Transaction'::varchar,'caption', 'Delivery Order'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>228</v>
+        <v>190</v>
       </c>
       <c r="E46" s="8">
         <f t="shared" si="0"/>
         <v>97000000000045</v>
       </c>
       <c r="F46" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.Advance.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.DeliveryOrder.Report.DataList</v>
       </c>
       <c r="G46" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Advance Request</v>
+        <f t="shared" si="8"/>
+        <v>Report DO Summary</v>
       </c>
       <c r="I46" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Transaction', 'Advance Request');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrder.Report.DataList', 'Report DO Summary');</v>
       </c>
       <c r="K46" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Advance.Transaction'::varchar,'caption', 'Advance Request'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.DeliveryOrder.Report.DataList'::varchar,'caption', 'Report DO Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>120</v>
+        <v>298</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>227</v>
+        <v>292</v>
       </c>
       <c r="E47" s="8">
         <f t="shared" si="0"/>
         <v>97000000000046</v>
       </c>
       <c r="F47" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.Advance.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList</v>
       </c>
       <c r="G47" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Advance Summary</v>
+        <f t="shared" si="8"/>
+        <v>Report DO to Material Receive</v>
       </c>
       <c r="I47" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Report.DataList', 'Report Advance Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList', 'Report DO to Material Receive');</v>
       </c>
       <c r="K47" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Advance.Report.DataList'::varchar,'caption', 'Report Advance Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.DeliveryOrderToMaterialReceive.Report.DataList'::varchar,'caption', 'Report DO to Material Receive'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
-        <v>297</v>
+        <v>191</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>298</v>
+        <v>189</v>
       </c>
       <c r="E48" s="8">
         <f t="shared" si="0"/>
         <v>97000000000047</v>
       </c>
       <c r="F48" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.MaterialReceive.Transaction</v>
       </c>
       <c r="G48" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Advance to Advance Settlement</v>
+        <f t="shared" si="8"/>
+        <v>Material Receive</v>
       </c>
       <c r="I48" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList', 'Report Advance to Advance Settlement');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B48, ""),"null", CONCATENATE("'", $F48, "'")), ", ", IF(EXACT($B48, ""), "null", CONCATENATE("'", $G48, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceive.Transaction', 'Material Receive');</v>
       </c>
       <c r="K48" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList'::varchar,'caption', 'Report Advance to Advance Settlement'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReceive.Transaction'::varchar,'caption', 'Material Receive'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>121</v>
+        <v>291</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>198</v>
+        <v>303</v>
       </c>
       <c r="E49" s="8">
         <f t="shared" si="0"/>
         <v>97000000000048</v>
       </c>
       <c r="F49" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.MaterialReceive.Report.DataList</v>
       </c>
       <c r="G49" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>AdvanceSettlement</v>
+        <f t="shared" si="8"/>
+        <v>Report Material Receive Summary</v>
       </c>
       <c r="I49" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Transaction', 'AdvanceSettlement');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceive.Report.DataList', 'Report Material Receive Summary');</v>
       </c>
       <c r="K49" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.AdvanceSettlement.Transaction'::varchar,'caption', 'AdvanceSettlement'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReceive.Report.DataList'::varchar,'caption', 'Report Material Receive Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>122</v>
+        <v>299</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="E50" s="8">
         <f t="shared" si="0"/>
         <v>97000000000049</v>
       </c>
       <c r="F50" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList</v>
       </c>
       <c r="G50" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Advance Settlement Summary</v>
+        <f t="shared" si="8"/>
+        <v>Report Material Receive to Material Return</v>
       </c>
       <c r="I50" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Report.DataList', 'Report Advance Settlement Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList', 'Report Material Receive to Material Return');</v>
       </c>
       <c r="K50" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.AdvanceSettlement.Report.DataList'::varchar,'caption', 'Report Advance Settlement Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReceiveToMaterialReturn.Report.DataList'::varchar,'caption', 'Report Material Receive to Material Return'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="E51" s="8">
         <f t="shared" si="0"/>
         <v>97000000000050</v>
       </c>
       <c r="F51" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.MaterialReturn.Transaction</v>
       </c>
       <c r="G51" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>BusinessTrip Request</v>
+        <f t="shared" si="8"/>
+        <v>Material Return</v>
       </c>
       <c r="I51" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Transaction', 'BusinessTrip Request');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Transaction', 'Material Return');</v>
       </c>
       <c r="K51" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTrip.Transaction'::varchar,'caption', 'BusinessTrip Request'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReturn.Transaction'::varchar,'caption', 'Material Return'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
       <c r="E52" s="8">
         <f t="shared" si="0"/>
         <v>97000000000051</v>
       </c>
       <c r="F52" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.MaterialReturn.Report.DataList</v>
       </c>
       <c r="G52" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report BusinessTrip Request Summary</v>
+        <f t="shared" si="8"/>
+        <v>Report Material Return Summary</v>
       </c>
       <c r="I52" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Report.DataList', 'Report BusinessTrip Request Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.MaterialReturn.Report.DataList', 'Report Material Return Summary');</v>
       </c>
       <c r="K52" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTrip.Report.DataList'::varchar,'caption', 'Report BusinessTrip Request Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.MaterialReturn.Report.DataList'::varchar,'caption', 'Report Material Return Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>299</v>
+        <v>327</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>300</v>
+        <v>326</v>
       </c>
       <c r="E53" s="8">
         <f t="shared" si="0"/>
         <v>97000000000052</v>
       </c>
       <c r="F53" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.PhysicalInventoryCount.Transaction</v>
       </c>
       <c r="G53" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report BusinessTrip to BusinessTrip Settlement</v>
+        <f t="shared" si="8"/>
+        <v>Stock Opname</v>
       </c>
       <c r="I53" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList', 'Report BusinessTrip to BusinessTrip Settlement');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B53, ""),"null", CONCATENATE("'", $F53, "'")), ", ", IF(EXACT($B53, ""), "null", CONCATENATE("'", $G53, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PhysicalInventoryCount.Transaction', 'Stock Opname');</v>
       </c>
       <c r="K53" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList'::varchar,'caption', 'Report BusinessTrip to BusinessTrip Settlement'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PhysicalInventoryCount.Transaction'::varchar,'caption', 'Stock Opname'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B54" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>231</v>
+      <c r="B54" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>329</v>
       </c>
       <c r="E54" s="8">
         <f t="shared" si="0"/>
         <v>97000000000053</v>
       </c>
       <c r="F54" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.PhysicalInventoryCount.Report.DataList</v>
       </c>
       <c r="G54" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>BusinessTrip Settlement</v>
+        <f t="shared" si="8"/>
+        <v>Report Stock Opname Summary</v>
       </c>
       <c r="I54" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Transaction', 'BusinessTrip Settlement');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PhysicalInventoryCount.Report.DataList', 'Report Stock Opname Summary');</v>
       </c>
       <c r="K54" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTripSettlement.Transaction'::varchar,'caption', 'BusinessTrip Settlement'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PhysicalInventoryCount.Report.DataList'::varchar,'caption', 'Report Stock Opname Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="55" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B55" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>230</v>
+      <c r="B55" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="E55" s="8">
         <f t="shared" si="0"/>
         <v>97000000000054</v>
       </c>
       <c r="F55" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.Advance.Transaction</v>
       </c>
       <c r="G55" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report BusinessTrip Settlement Summary</v>
+        <f t="shared" si="8"/>
+        <v>Advance Request</v>
       </c>
       <c r="I55" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList', 'Report BusinessTrip Settlement Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Transaction', 'Advance Request');</v>
       </c>
       <c r="K55" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList'::varchar,'caption', 'Report BusinessTrip Settlement Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Advance.Transaction'::varchar,'caption', 'Advance Request'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B56" s="2" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="E56" s="8">
         <f t="shared" si="0"/>
         <v>97000000000055</v>
       </c>
       <c r="F56" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.Advance.Report.DataList</v>
       </c>
       <c r="G56" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Supplier</v>
+        <f t="shared" si="8"/>
+        <v>Report Advance Summary</v>
       </c>
       <c r="I56" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.MasterData.Supplier.Transaction', 'Supplier');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Advance.Report.DataList', 'Report Advance Summary');</v>
       </c>
       <c r="K56" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.MasterData.Supplier.Transaction'::varchar,'caption', 'Supplier'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Advance.Report.DataList'::varchar,'caption', 'Report Advance Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>157</v>
+        <v>294</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>89</v>
+        <v>295</v>
       </c>
       <c r="E57" s="8">
         <f t="shared" si="0"/>
         <v>97000000000056</v>
       </c>
       <c r="F57" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList</v>
       </c>
       <c r="G57" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Purchase Requisition</v>
+        <f t="shared" si="8"/>
+        <v>Report Advance to Advance Settlement</v>
       </c>
       <c r="I57" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Transaction', 'Purchase Requisition');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B57, ""),"null", CONCATENATE("'", $F57, "'")), ", ", IF(EXACT($B57, ""), "null", CONCATENATE("'", $G57, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList', 'Report Advance to Advance Settlement');</v>
       </c>
       <c r="K57" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisition.Transaction'::varchar,'caption', 'Purchase Requisition'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.AdvanceToAdvanceSettlement.Report.DataList'::varchar,'caption', 'Report Advance to Advance Settlement'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B58" s="2" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E58" s="8">
         <f t="shared" si="0"/>
         <v>97000000000057</v>
       </c>
       <c r="F58" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.AdvanceSettlement.Transaction</v>
       </c>
       <c r="G58" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Purchase Requisition Summary</v>
+        <f t="shared" si="8"/>
+        <v>AdvanceSettlement</v>
       </c>
       <c r="I58" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList', 'Report Purchase Requisition Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Transaction', 'AdvanceSettlement');</v>
       </c>
       <c r="K58" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList'::varchar,'caption', 'Report Purchase Requisition Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.AdvanceSettlement.Transaction'::varchar,'caption', 'AdvanceSettlement'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B59" s="2" t="s">
-        <v>206</v>
+        <v>122</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="E59" s="8">
         <f t="shared" si="0"/>
         <v>97000000000058</v>
       </c>
       <c r="F59" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.AdvanceSettlement.Report.DataList</v>
       </c>
       <c r="G59" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Purchase Requisition To Purchase Order</v>
+        <f t="shared" si="8"/>
+        <v>Report Advance Settlement Summary</v>
       </c>
       <c r="I59" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList', 'Report Purchase Requisition To Purchase Order');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.AdvanceSettlement.Report.DataList', 'Report Advance Settlement Summary');</v>
       </c>
       <c r="K59" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList'::varchar,'caption', 'Report Purchase Requisition To Purchase Order'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.AdvanceSettlement.Report.DataList'::varchar,'caption', 'Report Advance Settlement Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
-        <v>155</v>
+        <v>202</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>90</v>
+        <v>230</v>
       </c>
       <c r="E60" s="8">
         <f t="shared" si="0"/>
         <v>97000000000059</v>
       </c>
       <c r="F60" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.PersonBusinessTrip.Transaction</v>
       </c>
       <c r="G60" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Purchase Order</v>
+        <f t="shared" si="8"/>
+        <v>BusinessTrip Request</v>
       </c>
       <c r="I60" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Transaction', 'Purchase Order');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Transaction', 'BusinessTrip Request');</v>
       </c>
       <c r="K60" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrder.Transaction'::varchar,'caption', 'Purchase Order'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTrip.Transaction'::varchar,'caption', 'BusinessTrip Request'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>203</v>
+        <v>229</v>
       </c>
       <c r="E61" s="8">
         <f t="shared" si="0"/>
         <v>97000000000060</v>
       </c>
       <c r="F61" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.PersonBusinessTrip.Report.DataList</v>
       </c>
       <c r="G61" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Report Purchase Order Summary</v>
+        <f t="shared" si="8"/>
+        <v>Report BusinessTrip Request Summary</v>
       </c>
       <c r="I61" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList', 'Report Purchase Order Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTrip.Report.DataList', 'Report BusinessTrip Request Summary');</v>
       </c>
       <c r="K61" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList'::varchar,'caption', 'Report Purchase Order Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTrip.Report.DataList'::varchar,'caption', 'Report BusinessTrip Request Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B62" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>223</v>
+      <c r="B62" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="E62" s="8">
         <f t="shared" si="0"/>
         <v>97000000000061</v>
       </c>
       <c r="F62" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="G62" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Purchase Order to Account Payable</v>
+        <f t="shared" si="8"/>
+        <v>Report BusinessTrip to BusinessTrip Settlement</v>
       </c>
       <c r="I62" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList', 'Purchase Order to Account Payable');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList', 'Report BusinessTrip to BusinessTrip Settlement');</v>
       </c>
       <c r="K62" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList'::varchar,'caption', 'Purchase Order to Account Payable'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTripToPersonBusinessTripSettlement.Report.DataList'::varchar,'caption', 'Report BusinessTrip to BusinessTrip Settlement'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
-        <v>265</v>
+        <v>200</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>266</v>
+        <v>228</v>
       </c>
       <c r="E63" s="8">
         <f t="shared" si="0"/>
         <v>97000000000062</v>
       </c>
       <c r="F63" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.Bank.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Transaction</v>
       </c>
       <c r="G63" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Bank</v>
+        <f t="shared" si="8"/>
+        <v>BusinessTrip Settlement</v>
       </c>
       <c r="I63" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Bank.Transaction', 'Bank');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Transaction', 'BusinessTrip Settlement');</v>
       </c>
       <c r="K63" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Bank.Transaction'::varchar,'caption', 'Bank'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTripSettlement.Transaction'::varchar,'caption', 'BusinessTrip Settlement'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B64" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>268</v>
+      <c r="B64" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>227</v>
       </c>
       <c r="E64" s="8">
         <f t="shared" si="0"/>
         <v>97000000000063</v>
       </c>
       <c r="F64" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.BankAccount.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList</v>
       </c>
       <c r="G64" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Bank Account</v>
+        <f t="shared" si="8"/>
+        <v>Report BusinessTrip Settlement Summary</v>
       </c>
       <c r="I64" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BankAccount.Transaction', 'Bank Account');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList', 'Report BusinessTrip Settlement Summary');</v>
       </c>
       <c r="K64" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BankAccount.Transaction'::varchar,'caption', 'Bank Account'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PersonBusinessTripSettlement.Report.DataList'::varchar,'caption', 'Report BusinessTrip Settlement Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="E65" s="8">
         <f t="shared" si="0"/>
         <v>97000000000064</v>
       </c>
       <c r="F65" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.Currency.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.MasterData.Supplier.Transaction</v>
       </c>
       <c r="G65" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Currency</v>
+        <f t="shared" si="8"/>
+        <v>Supplier</v>
       </c>
       <c r="I65" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Currency.Transaction', 'Currency');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.MasterData.Supplier.Transaction', 'Supplier');</v>
       </c>
       <c r="K65" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Currency.Transaction'::varchar,'caption', 'Currency'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.MasterData.Supplier.Transaction'::varchar,'caption', 'Supplier'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
-        <v>245</v>
+        <v>330</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>246</v>
+        <v>331</v>
       </c>
       <c r="E66" s="8">
         <f t="shared" si="0"/>
         <v>97000000000065</v>
       </c>
       <c r="F66" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.MasterData.SupplierCategory.Transaction</v>
       </c>
       <c r="G66" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Exchange Rate</v>
+        <f t="shared" si="8"/>
+        <v>Supplier Category</v>
       </c>
       <c r="I66" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Transaction', 'Exchange Rate');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B66, ""),"null", CONCATENATE("'", $F66, "'")), ", ", IF(EXACT($B66, ""), "null", CONCATENATE("'", $G66, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.MasterData.SupplierCategory.Transaction', 'Supplier Category');</v>
       </c>
       <c r="K66" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CurrencyExchangeRate.Transaction'::varchar,'caption', 'Exchange Rate'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.MasterData.SupplierCategory.Transaction'::varchar,'caption', 'Supplier Category'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="E67" s="8">
         <f t="shared" si="0"/>
         <v>97000000000066</v>
       </c>
       <c r="F67" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.MasterData.SupplierSubCategory.Transaction</v>
       </c>
       <c r="G67" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Exchange Rate Summary</v>
+        <f t="shared" si="8"/>
+        <v>Supplier Sub Category</v>
       </c>
       <c r="I67" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Report.DataList', 'Exchange Rate Summary');</v>
+        <f t="shared" si="3"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.MasterData.SupplierSubCategory.Transaction', 'Supplier Sub Category');</v>
       </c>
       <c r="K67" s="1" t="str">
-        <f t="shared" ref="K67:K98" si="14">CONCATENATE(
+        <f t="shared" si="4"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.MasterData.SupplierSubCategory.Transaction'::varchar,'caption', 'Supplier Sub Category'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B68" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E68" s="8">
+        <f t="shared" si="0"/>
+        <v>97000000000067</v>
+      </c>
+      <c r="F68" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Transaction</v>
+      </c>
+      <c r="G68" s="3" t="str">
+        <f t="shared" si="8"/>
+        <v>Purchase Requisition</v>
+      </c>
+      <c r="I68" s="9" t="str">
+        <f t="shared" ref="I68:I69" si="9">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B68, ""),"null", CONCATENATE("'", $F68, "'")), ", ", IF(EXACT($B68, ""), "null", CONCATENATE("'", $G68, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Transaction', 'Purchase Requisition');</v>
+      </c>
+      <c r="K68" s="1" t="str">
+        <f>CONCATENATE(
 "varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
 "'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
 "'sysLoginSession_RefID', varSystemLoginSession::bigint,",
@@ -17900,882 +18028,1588 @@
 "'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
 "'sysBranch_RefID', varInstitutionBranchID::bigint,",
 "'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B67, ""), "null", CONCATENATE("'", SUBSTITUTE($B67, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G67, ""), "null", CONCATENATE("'", SUBSTITUTE($G67, "'", "\'"), "'")), "::varchar",
+"'key', ", IF(EXACT($B68, ""), "null", CONCATENATE("'", SUBSTITUTE($B68, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G68, ""), "null", CONCATENATE("'", SUBSTITUTE($G68, "'", "\'"), "'")), "::varchar",
 ")))::varchar;")</f>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CurrencyExchangeRate.Report.DataList'::varchar,'caption', 'Exchange Rate Summary'::varchar)))::varchar;</v>
-      </c>
-    </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B68" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E68" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000067</v>
-      </c>
-      <c r="F68" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.PaymentTerm.Transaction</v>
-      </c>
-      <c r="G68" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Payment Term</v>
-      </c>
-      <c r="I68" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.PaymentTerm.Transaction', 'Payment Term');</v>
-      </c>
-      <c r="K68" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.PaymentTerm.Transaction'::varchar,'caption', 'Payment Term'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisition.Transaction'::varchar,'caption', 'Purchase Requisition'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B69" s="2" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>141</v>
+        <v>205</v>
       </c>
       <c r="E69" s="8">
         <f t="shared" si="0"/>
         <v>97000000000068</v>
       </c>
       <c r="F69" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.General.MasterData.Period.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.PurchaseRequisition.Report.DataList</v>
       </c>
       <c r="G69" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Period</v>
+        <f t="shared" si="8"/>
+        <v>Report Purchase Requisition Summary</v>
       </c>
       <c r="I69" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Period.Transaction', 'Period');</v>
+        <f t="shared" si="9"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList', 'Report Purchase Requisition Summary');</v>
       </c>
       <c r="K69" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Period.Transaction'::varchar,'caption', 'Period'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B69, ""), "null", CONCATENATE("'", SUBSTITUTE($B69, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G69, ""), "null", CONCATENATE("'", SUBSTITUTE($G69, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList'::varchar,'caption', 'Report Purchase Requisition Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
-        <v>263</v>
+        <v>206</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>264</v>
+        <v>204</v>
       </c>
       <c r="E70" s="8">
         <f t="shared" si="0"/>
         <v>97000000000069</v>
       </c>
       <c r="F70" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList</v>
       </c>
       <c r="G70" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Asset Category</v>
+        <f t="shared" si="8"/>
+        <v>Report Purchase Requisition To Purchase Order</v>
       </c>
       <c r="I70" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.AssetCategory.Transaction', 'Asset Category');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B70, ""),"null", CONCATENATE("'", $F70, "'")), ", ", IF(EXACT($B70, ""), "null", CONCATENATE("'", $G70, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList', 'Report Purchase Requisition To Purchase Order');</v>
       </c>
       <c r="K70" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.AssetCategory.Transaction'::varchar,'caption', 'Asset Category'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B70, ""), "null", CONCATENATE("'", SUBSTITUTE($B70, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G70, ""), "null", CONCATENATE("'", SUBSTITUTE($G70, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList'::varchar,'caption', 'Report Purchase Requisition To Purchase Order'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
-        <v>270</v>
+        <v>155</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>271</v>
+        <v>90</v>
       </c>
       <c r="E71" s="8">
         <f t="shared" si="0"/>
         <v>97000000000070</v>
       </c>
       <c r="F71" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Transaction</v>
       </c>
       <c r="G71" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Chart of Account</v>
+        <f t="shared" si="8"/>
+        <v>Purchase Order</v>
       </c>
       <c r="I71" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.ChartOfAccount.Transaction', 'Chart of Account');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B71, ""),"null", CONCATENATE("'", $F71, "'")), ", ", IF(EXACT($B71, ""), "null", CONCATENATE("'", $G71, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Transaction', 'Purchase Order');</v>
       </c>
       <c r="K71" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.ChartOfAccount.Transaction'::varchar,'caption', 'Chart of Account'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B71, ""), "null", CONCATENATE("'", SUBSTITUTE($B71, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G71, ""), "null", CONCATENATE("'", SUBSTITUTE($G71, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrder.Transaction'::varchar,'caption', 'Purchase Order'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
-        <v>273</v>
+        <v>156</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>272</v>
+        <v>203</v>
       </c>
       <c r="E72" s="8">
         <f t="shared" si="0"/>
         <v>97000000000071</v>
       </c>
       <c r="F72" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.PurchaseOrder.Report.DataList</v>
       </c>
       <c r="G72" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Depreciation Method</v>
+        <f t="shared" si="8"/>
+        <v>Report Purchase Order Summary</v>
       </c>
       <c r="I72" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationMethod.Transaction', 'Depreciation Method');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B72, ""),"null", CONCATENATE("'", $F72, "'")), ", ", IF(EXACT($B72, ""), "null", CONCATENATE("'", $G72, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList', 'Report Purchase Order Summary');</v>
       </c>
       <c r="K72" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.DepreciationMethod.Transaction'::varchar,'caption', 'Depreciation Method'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B72, ""), "null", CONCATENATE("'", SUBSTITUTE($B72, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G72, ""), "null", CONCATENATE("'", SUBSTITUTE($G72, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList'::varchar,'caption', 'Report Purchase Order Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B73" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>274</v>
+      <c r="B73" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>334</v>
       </c>
       <c r="E73" s="8">
         <f t="shared" si="0"/>
         <v>97000000000072</v>
       </c>
       <c r="F73" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+        <f t="shared" si="7"/>
+        <v>Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList</v>
       </c>
       <c r="G73" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Depreciation Rate Years</v>
+        <f t="shared" si="8"/>
+        <v>Report Purchase Order to Account Payable Summary</v>
       </c>
       <c r="I73" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationRateYears.Transaction', 'Depreciation Rate Years');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B73, ""),"null", CONCATENATE("'", $F73, "'")), ", ", IF(EXACT($B73, ""), "null", CONCATENATE("'", $G73, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList', 'Report Purchase Order to Account Payable Summary');</v>
       </c>
       <c r="K73" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.DepreciationRateYears.Transaction'::varchar,'caption', 'Depreciation Rate Years'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B73, ""), "null", CONCATENATE("'", SUBSTITUTE($B73, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G73, ""), "null", CONCATENATE("'", SUBSTITUTE($G73, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList'::varchar,'caption', 'Report Purchase Order to Account Payable Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="E74" s="8">
         <f t="shared" si="0"/>
         <v>97000000000073</v>
       </c>
       <c r="F74" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+        <f>IF(EXACT(B74, ""), "", B74)</f>
+        <v>Module.General.MasterData.Bank.Transaction</v>
       </c>
       <c r="G74" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Value Added Tax</v>
+        <f>IF(EXACT(C74, ""), "", C74)</f>
+        <v>Bank</v>
       </c>
       <c r="I74" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Taxation.MasterData.ValueAddedTax.Transaction', 'Value Added Tax');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B74, ""),"null", CONCATENATE("'", $F74, "'")), ", ", IF(EXACT($B74, ""), "null", CONCATENATE("'", $G74, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Bank.Transaction', 'Bank');</v>
       </c>
       <c r="K74" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Taxation.MasterData.ValueAddedTax.Transaction'::varchar,'caption', 'Value Added Tax'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B74, ""), "null", CONCATENATE("'", SUBSTITUTE($B74, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G74, ""), "null", CONCATENATE("'", SUBSTITUTE($G74, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Bank.Transaction'::varchar,'caption', 'Bank'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="E75" s="8">
         <f t="shared" si="0"/>
         <v>97000000000074</v>
       </c>
       <c r="F75" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+        <f>IF(EXACT(B75, ""), "", B75)</f>
+        <v>Module.General.MasterData.BankAccount.Transaction</v>
       </c>
       <c r="G75" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>General Journal</v>
+        <f>IF(EXACT(C75, ""), "", C75)</f>
+        <v>Bank Account</v>
       </c>
       <c r="I75" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Transaction', 'General Journal');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B75, ""),"null", CONCATENATE("'", $F75, "'")), ", ", IF(EXACT($B75, ""), "null", CONCATENATE("'", $G75, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BankAccount.Transaction', 'Bank Account');</v>
       </c>
       <c r="K75" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralJournal.Transaction'::varchar,'caption', 'General Journal'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B75, ""), "null", CONCATENATE("'", SUBSTITUTE($B75, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G75, ""), "null", CONCATENATE("'", SUBSTITUTE($G75, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BankAccount.Transaction'::varchar,'caption', 'Bank Account'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
-        <v>255</v>
+        <v>139</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>256</v>
+        <v>131</v>
       </c>
       <c r="E76" s="8">
         <f t="shared" si="0"/>
         <v>97000000000075</v>
       </c>
       <c r="F76" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+        <f>IF(EXACT(B76, ""), "", B76)</f>
+        <v>Module.General.MasterData.Currency.Transaction</v>
       </c>
       <c r="G76" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>General Journal Summary</v>
+        <f>IF(EXACT(C76, ""), "", C76)</f>
+        <v>Currency</v>
       </c>
       <c r="I76" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Report.DataList', 'General Journal Summary');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B76, ""),"null", CONCATENATE("'", $F76, "'")), ", ", IF(EXACT($B76, ""), "null", CONCATENATE("'", $G76, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Currency.Transaction', 'Currency');</v>
       </c>
       <c r="K76" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralJournal.Report.DataList'::varchar,'caption', 'General Journal Summary'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B76, ""), "null", CONCATENATE("'", SUBSTITUTE($B76, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G76, ""), "null", CONCATENATE("'", SUBSTITUTE($G76, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Currency.Transaction'::varchar,'caption', 'Currency'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>207</v>
+        <v>243</v>
       </c>
       <c r="E77" s="8">
         <f t="shared" si="0"/>
         <v>97000000000076</v>
       </c>
       <c r="F77" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+        <f>IF(EXACT(B77, ""), "", B77)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
       </c>
       <c r="G77" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Reimbursement</v>
+        <f>IF(EXACT(C77, ""), "", C77)</f>
+        <v>Exchange Rate</v>
       </c>
       <c r="I77" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Transaction', 'Reimbursement');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B77, ""),"null", CONCATENATE("'", $F77, "'")), ", ", IF(EXACT($B77, ""), "null", CONCATENATE("'", $G77, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Transaction', 'Exchange Rate');</v>
       </c>
       <c r="K77" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Reimbursement.Transaction'::varchar,'caption', 'Reimbursement'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B77, ""), "null", CONCATENATE("'", SUBSTITUTE($B77, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G77, ""), "null", CONCATENATE("'", SUBSTITUTE($G77, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CurrencyExchangeRate.Transaction'::varchar,'caption', 'Exchange Rate'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>208</v>
+        <v>251</v>
       </c>
       <c r="E78" s="8">
         <f t="shared" si="0"/>
         <v>97000000000077</v>
       </c>
       <c r="F78" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+        <f>IF(EXACT(B78, ""), "", B78)</f>
+        <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
       </c>
       <c r="G78" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Reimbursement Summary</v>
+        <f>IF(EXACT(C78, ""), "", C78)</f>
+        <v>Exchange Rate Summary</v>
       </c>
       <c r="I78" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Report.DataList', 'Reimbursement Summary');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B78, ""),"null", CONCATENATE("'", $F78, "'")), ", ", IF(EXACT($B78, ""), "null", CONCATENATE("'", $G78, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Report.DataList', 'Exchange Rate Summary');</v>
       </c>
       <c r="K78" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Reimbursement.Report.DataList'::varchar,'caption', 'Reimbursement Summary'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B78, ""), "null", CONCATENATE("'", SUBSTITUTE($B78, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G78, ""), "null", CONCATENATE("'", SUBSTITUTE($G78, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CurrencyExchangeRate.Report.DataList'::varchar,'caption', 'Exchange Rate Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B79" s="2" t="s">
-        <v>219</v>
+        <v>273</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="E79" s="8">
         <f t="shared" si="0"/>
         <v>97000000000078</v>
       </c>
       <c r="F79" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+        <f>IF(EXACT(B79, ""), "", B79)</f>
+        <v>Module.General.MasterData.PaymentTerm.Transaction</v>
       </c>
       <c r="G79" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Reimbursement to Debit Note</v>
+        <f>IF(EXACT(C79, ""), "", C79)</f>
+        <v>Payment Term</v>
       </c>
       <c r="I79" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList', 'Reimbursement to Debit Note');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B79, ""),"null", CONCATENATE("'", $F79, "'")), ", ", IF(EXACT($B79, ""), "null", CONCATENATE("'", $G79, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.PaymentTerm.Transaction', 'Payment Term');</v>
       </c>
       <c r="K79" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList'::varchar,'caption', 'Reimbursement to Debit Note'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B79, ""), "null", CONCATENATE("'", SUBSTITUTE($B79, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G79, ""), "null", CONCATENATE("'", SUBSTITUTE($G79, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.PaymentTerm.Transaction'::varchar,'caption', 'Payment Term'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B80" s="2" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E80" s="8">
         <f t="shared" si="0"/>
         <v>97000000000079</v>
       </c>
       <c r="F80" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.DebitNote.Transaction</v>
+        <f>IF(EXACT(B80, ""), "", B80)</f>
+        <v>Module.General.MasterData.Period.Transaction</v>
       </c>
       <c r="G80" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Debit Note</v>
+        <f>IF(EXACT(C80, ""), "", C80)</f>
+        <v>Period</v>
       </c>
       <c r="I80" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Transaction', 'Debit Note');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B80, ""),"null", CONCATENATE("'", $F80, "'")), ", ", IF(EXACT($B80, ""), "null", CONCATENATE("'", $G80, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Period.Transaction', 'Period');</v>
       </c>
       <c r="K80" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.DebitNote.Transaction'::varchar,'caption', 'Debit Note'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B80, ""), "null", CONCATENATE("'", SUBSTITUTE($B80, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G80, ""), "null", CONCATENATE("'", SUBSTITUTE($G80, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Period.Transaction'::varchar,'caption', 'Period'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
-        <v>124</v>
+        <v>260</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="E81" s="8">
         <f t="shared" si="0"/>
         <v>97000000000080</v>
       </c>
       <c r="F81" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+        <f>IF(EXACT(B81, ""), "", B81)</f>
+        <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
       </c>
       <c r="G81" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Debit Note Summary</v>
+        <f>IF(EXACT(C81, ""), "", C81)</f>
+        <v>Asset Category</v>
       </c>
       <c r="I81" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Report.DataList', 'Debit Note Summary');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B81, ""),"null", CONCATENATE("'", $F81, "'")), ", ", IF(EXACT($B81, ""), "null", CONCATENATE("'", $G81, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.AssetCategory.Transaction', 'Asset Category');</v>
       </c>
       <c r="K81" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.DebitNote.Report.DataList'::varchar,'caption', 'Debit Note Summary'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B81, ""), "null", CONCATENATE("'", SUBSTITUTE($B81, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G81, ""), "null", CONCATENATE("'", SUBSTITUTE($G81, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.AssetCategory.Transaction'::varchar,'caption', 'Asset Category'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B82" s="2" t="s">
-        <v>162</v>
+        <v>267</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>164</v>
+        <v>268</v>
       </c>
       <c r="E82" s="8">
         <f t="shared" si="0"/>
         <v>97000000000081</v>
       </c>
       <c r="F82" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.CreditNote.Transaction</v>
+        <f>IF(EXACT(B82, ""), "", B82)</f>
+        <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
       </c>
       <c r="G82" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Credit Note</v>
+        <f>IF(EXACT(C82, ""), "", C82)</f>
+        <v>Chart of Account</v>
       </c>
       <c r="I82" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Transaction', 'Credit Note');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B82, ""),"null", CONCATENATE("'", $F82, "'")), ", ", IF(EXACT($B82, ""), "null", CONCATENATE("'", $G82, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.ChartOfAccount.Transaction', 'Chart of Account');</v>
       </c>
       <c r="K82" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CreditNote.Transaction'::varchar,'caption', 'Credit Note'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B82, ""), "null", CONCATENATE("'", SUBSTITUTE($B82, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G82, ""), "null", CONCATENATE("'", SUBSTITUTE($G82, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.ChartOfAccount.Transaction'::varchar,'caption', 'Chart of Account'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B83" s="2" t="s">
-        <v>163</v>
+        <v>270</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>211</v>
+        <v>269</v>
       </c>
       <c r="E83" s="8">
         <f t="shared" si="0"/>
         <v>97000000000082</v>
       </c>
       <c r="F83" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+        <f>IF(EXACT(B83, ""), "", B83)</f>
+        <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
       </c>
       <c r="G83" s="3" t="str">
-        <f t="shared" si="12"/>
-        <v>Credit Note Summary</v>
+        <f>IF(EXACT(C83, ""), "", C83)</f>
+        <v>Depreciation Method</v>
       </c>
       <c r="I83" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Report.DataList', 'Credit Note Summary');</v>
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B83, ""),"null", CONCATENATE("'", $F83, "'")), ", ", IF(EXACT($B83, ""), "null", CONCATENATE("'", $G83, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationMethod.Transaction', 'Depreciation Method');</v>
       </c>
       <c r="K83" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CreditNote.Report.DataList'::varchar,'caption', 'Credit Note Summary'::varchar)))::varchar;</v>
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B83, ""), "null", CONCATENATE("'", SUBSTITUTE($B83, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G83, ""), "null", CONCATENATE("'", SUBSTITUTE($G83, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.DepreciationMethod.Transaction'::varchar,'caption', 'Depreciation Method'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B84" s="2" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>167</v>
+        <v>271</v>
       </c>
       <c r="E84" s="8">
         <f t="shared" si="0"/>
         <v>97000000000083</v>
       </c>
       <c r="F84" s="3" t="str">
+        <f t="shared" ref="F84:F116" si="10">IF(EXACT(B84, ""), "", B84)</f>
+        <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
+      </c>
+      <c r="G84" s="3" t="str">
+        <f t="shared" ref="G84:G116" si="11">IF(EXACT(C84, ""), "", C84)</f>
+        <v>Depreciation Rate Years</v>
+      </c>
+      <c r="I84" s="9" t="str">
+        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B84, ""),"null", CONCATENATE("'", $F84, "'")), ", ", IF(EXACT($B84, ""), "null", CONCATENATE("'", $G84, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationRateYears.Transaction', 'Depreciation Rate Years');</v>
+      </c>
+      <c r="K84" s="1" t="str">
+        <f>CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B84, ""), "null", CONCATENATE("'", SUBSTITUTE($B84, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G84, ""), "null", CONCATENATE("'", SUBSTITUTE($G84, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.DepreciationRateYears.Transaction'::varchar,'caption', 'Depreciation Rate Years'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B85" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E85" s="8">
+        <f t="shared" ref="E85:E116" si="12">IF(ISNUMBER($E84), $E84+1, 97000000000001)</f>
+        <v>97000000000084</v>
+      </c>
+      <c r="F85" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
+      </c>
+      <c r="G85" s="3" t="str">
         <f t="shared" si="11"/>
+        <v>Value Added Tax</v>
+      </c>
+      <c r="I85" s="9" t="str">
+        <f t="shared" ref="I85:I116" si="13">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B85, ""),"null", CONCATENATE("'", $F85, "'")), ", ", IF(EXACT($B85, ""), "null", CONCATENATE("'", $G85, "'")), ");")</f>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Taxation.MasterData.ValueAddedTax.Transaction', 'Value Added Tax');</v>
+      </c>
+      <c r="K85" s="1" t="str">
+        <f t="shared" ref="K85:K116" si="14">CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'key', ", IF(EXACT($B85, ""), "null", CONCATENATE("'", SUBSTITUTE($B85, "'", "\'"), "'")), "::varchar,",
+"'caption', ", IF(EXACT($G85, ""), "null", CONCATENATE("'", SUBSTITUTE($G85, "'", "\'"), "'")), "::varchar",
+")))::varchar;")</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Taxation.MasterData.ValueAddedTax.Transaction'::varchar,'caption', 'Value Added Tax'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B86" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E86" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000085</v>
+      </c>
+      <c r="F86" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.Data.BalanceSheet.Report.DataList</v>
+      </c>
+      <c r="G86" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Balance Sheet</v>
+      </c>
+      <c r="I86" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.BalanceSheet.Report.DataList', 'Balance Sheet');</v>
+      </c>
+      <c r="K86" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.BalanceSheet.Report.DataList'::varchar,'caption', 'Balance Sheet'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B87" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E87" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000086</v>
+      </c>
+      <c r="F87" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
+      </c>
+      <c r="G87" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>General Journal</v>
+      </c>
+      <c r="I87" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Transaction', 'General Journal');</v>
+      </c>
+      <c r="K87" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralJournal.Transaction'::varchar,'caption', 'General Journal'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B88" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E88" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000087</v>
+      </c>
+      <c r="F88" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
+      </c>
+      <c r="G88" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>General Journal Summary</v>
+      </c>
+      <c r="I88" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Report.DataList', 'General Journal Summary');</v>
+      </c>
+      <c r="K88" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralJournal.Report.DataList'::varchar,'caption', 'General Journal Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B89" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E89" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000088</v>
+      </c>
+      <c r="F89" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.Data.GeneralLedger.Report.DataList</v>
+      </c>
+      <c r="G89" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>General Ledger Summary</v>
+      </c>
+      <c r="I89" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralLedger.Report.DataList', 'General Ledger Summary');</v>
+      </c>
+      <c r="K89" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralLedger.Report.DataList'::varchar,'caption', 'General Ledger Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B90" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E90" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000089</v>
+      </c>
+      <c r="F90" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Accounting.Data.ProfitLoss.Report.DataList</v>
+      </c>
+      <c r="G90" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Profit Loss Summary</v>
+      </c>
+      <c r="I90" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.ProfitLoss.Report.DataList', 'Profit Loss Summary');</v>
+      </c>
+      <c r="K90" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.ProfitLoss.Report.DataList'::varchar,'caption', 'Profit Loss Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B91" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E91" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000090</v>
+      </c>
+      <c r="F91" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.CashBank.Transaction</v>
+      </c>
+      <c r="G91" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Cash &amp; Bank</v>
+      </c>
+      <c r="I91" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Transaction', 'Cash &amp; Bank');</v>
+      </c>
+      <c r="K91" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CashBank.Transaction'::varchar,'caption', 'Cash &amp; Bank'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B92" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E92" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000091</v>
+      </c>
+      <c r="F92" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.CashBank.Report.DataList</v>
+      </c>
+      <c r="G92" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Cash &amp; Bank Summary</v>
+      </c>
+      <c r="I92" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Report.DataList', 'Cash &amp; Bank Summary');</v>
+      </c>
+      <c r="K92" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CashBank.Report.DataList'::varchar,'caption', 'Cash &amp; Bank Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B93" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="E93" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000092</v>
+      </c>
+      <c r="F93" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.CreditNote.Transaction</v>
+      </c>
+      <c r="G93" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Credit Note</v>
+      </c>
+      <c r="I93" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Transaction', 'Credit Note');</v>
+      </c>
+      <c r="K93" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CreditNote.Transaction'::varchar,'caption', 'Credit Note'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B94" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E94" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000093</v>
+      </c>
+      <c r="F94" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.CreditNote.Report.DataList</v>
+      </c>
+      <c r="G94" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Credit Note Summary</v>
+      </c>
+      <c r="I94" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Report.DataList', 'Credit Note Summary');</v>
+      </c>
+      <c r="K94" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CreditNote.Report.DataList'::varchar,'caption', 'Credit Note Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B95" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E95" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000094</v>
+      </c>
+      <c r="F95" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.DebitNote.Transaction</v>
+      </c>
+      <c r="G95" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Debit Note</v>
+      </c>
+      <c r="I95" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Transaction', 'Debit Note');</v>
+      </c>
+      <c r="K95" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.DebitNote.Transaction'::varchar,'caption', 'Debit Note'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B96" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E96" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000095</v>
+      </c>
+      <c r="F96" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.DebitNote.Report.DataList</v>
+      </c>
+      <c r="G96" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Debit Note Summary</v>
+      </c>
+      <c r="I96" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Report.DataList', 'Debit Note Summary');</v>
+      </c>
+      <c r="K96" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.DebitNote.Report.DataList'::varchar,'caption', 'Debit Note Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B97" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E97" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000096</v>
+      </c>
+      <c r="F97" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.FixedAsset.Data.GoodsIdentity.Transaction</v>
+      </c>
+      <c r="G97" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Fixed Asset</v>
+      </c>
+      <c r="I97" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.FixedAsset.Data.GoodsIdentity.Transaction', 'Fixed Asset');</v>
+      </c>
+      <c r="K97" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.FixedAsset.Data.GoodsIdentity.Transaction'::varchar,'caption', 'Fixed Asset'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B98" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E98" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000097</v>
+      </c>
+      <c r="F98" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.FixedAsset.Data.GoodsIdentity.Report.DataList</v>
+      </c>
+      <c r="G98" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Fixed Asset Summary</v>
+      </c>
+      <c r="I98" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.FixedAsset.Data.GoodsIdentity.Report.DataList', 'Fixed Asset Summary');</v>
+      </c>
+      <c r="K98" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.FixedAsset.Data.GoodsIdentity.Report.DataList'::varchar,'caption', 'Fixed Asset Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="99" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B99" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E99" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000098</v>
+      </c>
+      <c r="F99" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.Loan.Transaction</v>
       </c>
-      <c r="G84" s="3" t="str">
-        <f t="shared" si="12"/>
+      <c r="G99" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Loan</v>
       </c>
-      <c r="I84" s="9" t="str">
+      <c r="I99" s="9" t="str">
         <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Transaction', 'Loan');</v>
       </c>
-      <c r="K84" s="1" t="str">
+      <c r="K99" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Loan.Transaction'::varchar,'caption', 'Loan'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="85" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B85" s="2" t="s">
+    <row r="100" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B100" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E85" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000084</v>
-      </c>
-      <c r="F85" s="3" t="str">
-        <f t="shared" ref="F85:F98" si="15">IF(EXACT(B85, ""), "", B85)</f>
+      <c r="C100" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E100" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000099</v>
+      </c>
+      <c r="F100" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.Loan.Report.DataList</v>
       </c>
-      <c r="G85" s="3" t="str">
-        <f t="shared" ref="G85:G98" si="16">IF(EXACT(C85, ""), "", C85)</f>
+      <c r="G100" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Loan Summary</v>
       </c>
-      <c r="I85" s="9" t="str">
+      <c r="I100" s="9" t="str">
         <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Report.DataList', 'Loan Summary');</v>
       </c>
-      <c r="K85" s="1" t="str">
+      <c r="K100" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Loan.Report.DataList'::varchar,'caption', 'Loan Summary'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="86" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B86" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E86" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000085</v>
-      </c>
-      <c r="F86" s="3" t="str">
-        <f t="shared" si="15"/>
+    <row r="101" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B101" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E101" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000100</v>
+      </c>
+      <c r="F101" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
       </c>
-      <c r="G86" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v>Loan to Loan Settlement</v>
-      </c>
-      <c r="I86" s="9" t="str">
+      <c r="G101" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Loan to Loan Settlement Summary</v>
+      </c>
+      <c r="I101" s="9" t="str">
         <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList', 'Loan to Loan Settlement');</v>
-      </c>
-      <c r="K86" s="1" t="str">
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList', 'Loan to Loan Settlement Summary');</v>
+      </c>
+      <c r="K101" s="1" t="str">
         <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList'::varchar,'caption', 'Loan to Loan Settlement'::varchar)))::varchar;</v>
-      </c>
-    </row>
-    <row r="87" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B87" s="2" t="s">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList'::varchar,'caption', 'Loan to Loan Settlement Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="102" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B102" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C87" s="2" t="s">
+      <c r="C102" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E87" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000086</v>
-      </c>
-      <c r="F87" s="3" t="str">
-        <f t="shared" si="15"/>
+      <c r="E102" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000101</v>
+      </c>
+      <c r="F102" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.LoanSettlement.Transaction</v>
       </c>
-      <c r="G87" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G102" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Loan Settlement</v>
       </c>
-      <c r="I87" s="9" t="str">
+      <c r="I102" s="9" t="str">
         <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Transaction', 'Loan Settlement');</v>
       </c>
-      <c r="K87" s="1" t="str">
+      <c r="K102" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanSettlement.Transaction'::varchar,'caption', 'Loan Settlement'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="88" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B88" s="2" t="s">
+    <row r="103" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B103" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E88" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000087</v>
-      </c>
-      <c r="F88" s="3" t="str">
-        <f t="shared" si="15"/>
+      <c r="C103" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E103" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000102</v>
+      </c>
+      <c r="F103" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
       </c>
-      <c r="G88" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G103" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Loan Settlement Summary</v>
       </c>
-      <c r="I88" s="9" t="str">
+      <c r="I103" s="9" t="str">
         <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Report.DataList', 'Loan Settlement Summary');</v>
       </c>
-      <c r="K88" s="1" t="str">
+      <c r="K103" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanSettlement.Report.DataList'::varchar,'caption', 'Loan Settlement Summary'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="89" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B89" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="E89" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000088</v>
-      </c>
-      <c r="F89" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>Module.Finance.Data.CashBank.Transaction</v>
-      </c>
-      <c r="G89" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v>Cash &amp; Bank</v>
-      </c>
-      <c r="I89" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Transaction', 'Cash &amp; Bank');</v>
-      </c>
-      <c r="K89" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CashBank.Transaction'::varchar,'caption', 'Cash &amp; Bank'::varchar)))::varchar;</v>
-      </c>
-    </row>
-    <row r="90" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B90" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E90" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000089</v>
-      </c>
-      <c r="F90" s="3" t="str">
-        <f t="shared" si="15"/>
-        <v>Module.Finance.Data.CashBank.Report.DataList</v>
-      </c>
-      <c r="G90" s="3" t="str">
-        <f t="shared" si="16"/>
-        <v>Cash &amp; Bank Summary</v>
-      </c>
-      <c r="I90" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Report.DataList', 'Cash &amp; Bank Summary');</v>
-      </c>
-      <c r="K90" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CashBank.Report.DataList'::varchar,'caption', 'Cash &amp; Bank Summary'::varchar)))::varchar;</v>
-      </c>
-    </row>
-    <row r="91" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B91" s="2" t="s">
+    <row r="104" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B104" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C91" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E91" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000090</v>
-      </c>
-      <c r="F91" s="3" t="str">
-        <f t="shared" si="15"/>
+      <c r="C104" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E104" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000103</v>
+      </c>
+      <c r="F104" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
       </c>
-      <c r="G91" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G104" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Account Payable</v>
       </c>
-      <c r="I91" s="9" t="str">
+      <c r="I104" s="9" t="str">
         <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Transaction', 'Account Payable');</v>
       </c>
-      <c r="K91" s="1" t="str">
+      <c r="K104" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PaymentInstruction.Transaction'::varchar,'caption', 'Account Payable'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="92" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B92" s="2" t="s">
+    <row r="105" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B105" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C92" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E92" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000091</v>
-      </c>
-      <c r="F92" s="3" t="str">
-        <f t="shared" si="15"/>
+      <c r="C105" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E105" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000104</v>
+      </c>
+      <c r="F105" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
       </c>
-      <c r="G92" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G105" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Account Payable Summary</v>
       </c>
-      <c r="I92" s="9" t="str">
-        <f t="shared" ref="I92:I98" si="17">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B92, ""),"null", CONCATENATE("'", $F92, "'")), ", ", IF(EXACT($B92, ""), "null", CONCATENATE("'", $G92, "'")), ");")</f>
+      <c r="I105" s="9" t="str">
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Report.DataList', 'Account Payable Summary');</v>
       </c>
-      <c r="K92" s="1" t="str">
+      <c r="K105" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PaymentInstruction.Report.DataList'::varchar,'caption', 'Account Payable Summary'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="93" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B93" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E93" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000092</v>
-      </c>
-      <c r="F93" s="3" t="str">
-        <f t="shared" si="15"/>
+    <row r="106" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B106" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E106" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000105</v>
+      </c>
+      <c r="F106" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.Reimbursement.Transaction</v>
+      </c>
+      <c r="G106" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Reimbursement</v>
+      </c>
+      <c r="I106" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Transaction', 'Reimbursement');</v>
+      </c>
+      <c r="K106" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Reimbursement.Transaction'::varchar,'caption', 'Reimbursement'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="107" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B107" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E107" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000106</v>
+      </c>
+      <c r="F107" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
+      </c>
+      <c r="G107" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Reimbursement Summary</v>
+      </c>
+      <c r="I107" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Report.DataList', 'Reimbursement Summary');</v>
+      </c>
+      <c r="K107" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Reimbursement.Report.DataList'::varchar,'caption', 'Reimbursement Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="108" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B108" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E108" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000107</v>
+      </c>
+      <c r="F108" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
+      </c>
+      <c r="G108" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Reimbursement to Debit Note Summary</v>
+      </c>
+      <c r="I108" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList', 'Reimbursement to Debit Note Summary');</v>
+      </c>
+      <c r="K108" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList'::varchar,'caption', 'Reimbursement to Debit Note Summary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="109" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B109" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E109" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000108</v>
+      </c>
+      <c r="F109" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.SalesInvoice.Transaction</v>
       </c>
-      <c r="G93" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G109" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Sales Invoice</v>
       </c>
-      <c r="I93" s="9" t="str">
-        <f t="shared" si="17"/>
+      <c r="I109" s="9" t="str">
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Transaction', 'Sales Invoice');</v>
       </c>
-      <c r="K93" s="1" t="str">
+      <c r="K109" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.SalesInvoice.Transaction'::varchar,'caption', 'Sales Invoice'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="94" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B94" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E94" s="8">
-        <f t="shared" si="0"/>
-        <v>97000000000093</v>
-      </c>
-      <c r="F94" s="3" t="str">
-        <f t="shared" si="15"/>
+    <row r="110" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B110" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E110" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000109</v>
+      </c>
+      <c r="F110" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
       </c>
-      <c r="G94" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G110" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Sales Invoice Summary</v>
       </c>
-      <c r="I94" s="9" t="str">
-        <f t="shared" si="17"/>
+      <c r="I110" s="9" t="str">
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Report.DataList', 'Sales Invoice Summary');</v>
       </c>
-      <c r="K94" s="1" t="str">
+      <c r="K110" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.SalesInvoice.Report.DataList'::varchar,'caption', 'Sales Invoice Summary'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="95" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B95" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E95" s="8">
-        <f t="shared" ref="E95:E98" si="18">IF(ISNUMBER($E94), $E94+1, 97000000000001)</f>
-        <v>97000000000094</v>
-      </c>
-      <c r="F95" s="3" t="str">
-        <f t="shared" si="15"/>
+    <row r="111" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B111" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E111" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000110</v>
+      </c>
+      <c r="F111" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
       </c>
-      <c r="G95" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G111" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Sales Invoice to Credit Note</v>
       </c>
-      <c r="I95" s="9" t="str">
-        <f t="shared" si="17"/>
+      <c r="I111" s="9" t="str">
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList', 'Sales Invoice to Credit Note');</v>
       </c>
-      <c r="K95" s="1" t="str">
+      <c r="K111" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList'::varchar,'caption', 'Sales Invoice to Credit Note'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="96" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B96" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E96" s="8">
-        <f t="shared" si="18"/>
-        <v>97000000000095</v>
-      </c>
-      <c r="F96" s="3" t="str">
-        <f t="shared" si="15"/>
+    <row r="112" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B112" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E112" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000111</v>
+      </c>
+      <c r="F112" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
       </c>
-      <c r="G96" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G112" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Tax Reconciliation</v>
       </c>
-      <c r="I96" s="9" t="str">
-        <f t="shared" si="17"/>
+      <c r="I112" s="9" t="str">
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Transaction', 'Tax Reconciliation');</v>
       </c>
-      <c r="K96" s="1" t="str">
+      <c r="K112" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.TaxReconciliation.Transaction'::varchar,'caption', 'Tax Reconciliation'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="97" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B97" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="E97" s="8">
-        <f t="shared" si="18"/>
-        <v>97000000000096</v>
-      </c>
-      <c r="F97" s="3" t="str">
-        <f t="shared" si="15"/>
+    <row r="113" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B113" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E113" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000112</v>
+      </c>
+      <c r="F113" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
       </c>
-      <c r="G97" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G113" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Tax Reconciliation Summary</v>
       </c>
-      <c r="I97" s="9" t="str">
-        <f t="shared" si="17"/>
+      <c r="I113" s="9" t="str">
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Report.DataList', 'Tax Reconciliation Summary');</v>
       </c>
-      <c r="K97" s="1" t="str">
+      <c r="K113" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.TaxReconciliation.Report.DataList'::varchar,'caption', 'Tax Reconciliation Summary'::varchar)))::varchar;</v>
       </c>
     </row>
-    <row r="98" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B98" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E98" s="8">
-        <f t="shared" si="18"/>
-        <v>97000000000097</v>
-      </c>
-      <c r="F98" s="3" t="str">
-        <f t="shared" si="15"/>
+    <row r="114" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B114" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="E114" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000113</v>
+      </c>
+      <c r="F114" s="3" t="str">
+        <f t="shared" si="10"/>
         <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
       </c>
-      <c r="G98" s="3" t="str">
-        <f t="shared" si="16"/>
+      <c r="G114" s="3" t="str">
+        <f t="shared" si="11"/>
         <v>Customer</v>
       </c>
-      <c r="I98" s="9" t="str">
-        <f t="shared" si="17"/>
+      <c r="I114" s="9" t="str">
+        <f t="shared" si="13"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.MasterData.Customer.Transaction', 'Customer');</v>
       </c>
-      <c r="K98" s="1" t="str">
+      <c r="K114" s="1" t="str">
         <f t="shared" si="14"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.CustomerRelation.MasterData.Customer.Transaction'::varchar,'caption', 'Customer'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="115" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B115" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E115" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000114</v>
+      </c>
+      <c r="F115" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.CustomerRelation.MasterData.CustomerOrder.Transaction</v>
+      </c>
+      <c r="G115" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Customer Order</v>
+      </c>
+      <c r="I115" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.MasterData.CustomerOrder.Transaction', 'Customer Order');</v>
+      </c>
+      <c r="K115" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.CustomerRelation.MasterData.CustomerOrder.Transaction'::varchar,'caption', 'Customer Order'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="116" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B116" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E116" s="8">
+        <f t="shared" si="12"/>
+        <v>97000000000115</v>
+      </c>
+      <c r="F116" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList</v>
+      </c>
+      <c r="G116" s="3" t="str">
+        <f t="shared" si="11"/>
+        <v>Customer Order Summary</v>
+      </c>
+      <c r="I116" s="9" t="str">
+        <f t="shared" si="13"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList', 'Customer Order Summary');</v>
+      </c>
+      <c r="K116" s="1" t="str">
+        <f t="shared" si="14"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList'::varchar,'caption', 'Customer Order Summary'::varchar)))::varchar;</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_Menu.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_Menu.xlsx
@@ -402,9 +402,6 @@
     <t>Module.HumanResource.Data.PersonWorkTimeSheet.Transaction</t>
   </si>
   <si>
-    <t>Person Work Time Sheet</t>
-  </si>
-  <si>
     <t>Business Document Type</t>
   </si>
   <si>
@@ -870,9 +867,6 @@
     <t>Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList</t>
   </si>
   <si>
-    <t>Person Work Time Sheet Summary</t>
-  </si>
-  <si>
     <t>Module.HumanResource.MasterData.OrganizationalDepartment.Transaction</t>
   </si>
   <si>
@@ -948,9 +942,6 @@
     <t>Report Progress Budget Summary</t>
   </si>
   <si>
-    <t>S-Curve Summary</t>
-  </si>
-  <si>
     <t>Module.Budgeting.Data.SCurve.Report.Resume</t>
   </si>
   <si>
@@ -981,9 +972,6 @@
     <t>Module.Accounting.Data.BalanceSheet.Report.DataList</t>
   </si>
   <si>
-    <t>Profit Loss Summary</t>
-  </si>
-  <si>
     <t>Balance Sheet</t>
   </si>
   <si>
@@ -1023,19 +1011,31 @@
     <t>Report Purchase Order to Account Payable Summary</t>
   </si>
   <si>
-    <t>Module.CustomerRelation.MasterData.CustomerOrder.Transaction</t>
-  </si>
-  <si>
     <t>Customer Order</t>
   </si>
   <si>
-    <t>Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList</t>
-  </si>
-  <si>
     <t>Customer Order Summary</t>
   </si>
   <si>
     <t>Module.Budgeting.Data.Budget.Report.Transaction</t>
+  </si>
+  <si>
+    <t>S-Curve</t>
+  </si>
+  <si>
+    <t>Profit Loss</t>
+  </si>
+  <si>
+    <t>Time Sheet</t>
+  </si>
+  <si>
+    <t>Time Sheet Summary</t>
+  </si>
+  <si>
+    <t>Module.CustomerRelation.Data.CustomerOrder.Transaction</t>
+  </si>
+  <si>
+    <t>Module.CustomerRelation.Data.CustomerOrder.Report.DataList</t>
   </si>
 </sst>
 </file>
@@ -12759,10 +12759,10 @@
     </row>
     <row r="311" spans="2:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B311" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C311" s="13" t="s">
         <v>171</v>
-      </c>
-      <c r="C311" s="13" t="s">
-        <v>172</v>
       </c>
       <c r="D311" s="13" t="s">
         <v>96</v>
@@ -13123,7 +13123,7 @@
     </row>
     <row r="321" spans="2:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B321" s="13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C321" s="13"/>
       <c r="D321" s="13"/>
@@ -13160,10 +13160,10 @@
     </row>
     <row r="322" spans="2:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B322" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="C322" s="13" t="s">
         <v>174</v>
-      </c>
-      <c r="C322" s="13" t="s">
-        <v>175</v>
       </c>
       <c r="D322" s="13" t="s">
         <v>62</v>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="332" spans="2:13" ht="25.5" x14ac:dyDescent="0.25">
       <c r="B332" s="13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C332" s="13"/>
       <c r="D332" s="13"/>
@@ -16231,21 +16231,21 @@
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="E5" s="8">
         <f t="shared" si="0"/>
         <v>97000000000004</v>
       </c>
       <c r="F5" s="3" t="str">
-        <f t="shared" ref="F5:F34" si="5">IF(EXACT(B5, ""), "", B5)</f>
+        <f t="shared" ref="F5:F9" si="5">IF(EXACT(B5, ""), "", B5)</f>
         <v>Dashboard.Home</v>
       </c>
       <c r="G5" s="3" t="str">
-        <f t="shared" ref="G5:G34" si="6">IF(EXACT(C5, ""), "", C5)</f>
+        <f t="shared" ref="G5:G9" si="6">IF(EXACT(C5, ""), "", C5)</f>
         <v>Dashboard</v>
       </c>
       <c r="I5" s="9" t="str">
@@ -16287,10 +16287,10 @@
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" si="0"/>
@@ -16315,10 +16315,10 @@
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B8" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="0"/>
@@ -16343,10 +16343,10 @@
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B9" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="0"/>
@@ -16371,10 +16371,10 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B10" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E10" s="8">
         <f t="shared" si="0"/>
@@ -16399,10 +16399,10 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E11" s="8">
         <f t="shared" si="0"/>
@@ -16427,10 +16427,10 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E12" s="8">
         <f t="shared" si="0"/>
@@ -16455,10 +16455,10 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B13" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E13" s="8">
         <f t="shared" si="0"/>
@@ -16483,10 +16483,10 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B14" s="7" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E14" s="8">
         <f t="shared" si="0"/>
@@ -16511,10 +16511,10 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E15" s="8">
         <f t="shared" si="0"/>
@@ -16539,10 +16539,10 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E16" s="8">
         <f t="shared" si="0"/>
@@ -16567,10 +16567,10 @@
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E17" s="8">
         <f t="shared" si="0"/>
@@ -16595,7 +16595,7 @@
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B18" s="7" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>117</v>
@@ -16623,10 +16623,10 @@
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E19" s="8">
         <f t="shared" si="0"/>
@@ -16651,7 +16651,7 @@
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B20" s="2" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>117</v>
@@ -16679,10 +16679,10 @@
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="E21" s="8">
         <f t="shared" si="0"/>
@@ -16707,10 +16707,10 @@
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="E22" s="8">
         <f t="shared" si="0"/>
@@ -16735,10 +16735,10 @@
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E23" s="8">
         <f t="shared" si="0"/>
@@ -16763,10 +16763,10 @@
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E24" s="8">
         <f t="shared" si="0"/>
@@ -16791,10 +16791,10 @@
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="E25" s="8">
         <f t="shared" si="0"/>
@@ -16819,10 +16819,10 @@
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>310</v>
+        <v>334</v>
       </c>
       <c r="E26" s="8">
         <f t="shared" si="0"/>
@@ -16834,23 +16834,23 @@
       </c>
       <c r="G26" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>S-Curve Summary</v>
+        <v>S-Curve</v>
       </c>
       <c r="I26" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.SCurve.Report.Resume', 'S-Curve Summary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Budgeting.Data.SCurve.Report.Resume', 'S-Curve');</v>
       </c>
       <c r="K26" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.SCurve.Report.Resume'::varchar,'caption', 'S-Curve Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Budgeting.Data.SCurve.Report.Resume'::varchar,'caption', 'S-Curve'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="E27" s="8">
         <f t="shared" si="0"/>
@@ -16875,10 +16875,10 @@
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E28" s="8">
         <f t="shared" si="0"/>
@@ -16903,10 +16903,10 @@
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E29" s="8">
         <f t="shared" si="0"/>
@@ -16931,10 +16931,10 @@
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E30" s="8">
         <f t="shared" si="0"/>
@@ -16959,10 +16959,10 @@
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="E31" s="8">
         <f t="shared" si="0"/>
@@ -16987,10 +16987,10 @@
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="E32" s="8">
         <f t="shared" si="0"/>
@@ -17015,7 +17015,7 @@
     </row>
     <row r="33" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>72</v>
@@ -17043,10 +17043,10 @@
     </row>
     <row r="34" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E34" s="8">
         <f t="shared" si="0"/>
@@ -17071,10 +17071,10 @@
     </row>
     <row r="35" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B35" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="E35" s="8">
         <f t="shared" si="0"/>
@@ -17099,10 +17099,10 @@
     </row>
     <row r="36" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E36" s="8">
         <f t="shared" si="0"/>
@@ -17130,7 +17130,7 @@
         <v>127</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>128</v>
+        <v>336</v>
       </c>
       <c r="E37" s="8">
         <f t="shared" si="0"/>
@@ -17142,23 +17142,23 @@
       </c>
       <c r="G37" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>Person Work Time Sheet</v>
+        <v>Time Sheet</v>
       </c>
       <c r="I37" s="9" t="str">
         <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B37, ""),"null", CONCATENATE("'", $F37, "'")), ", ", IF(EXACT($B37, ""), "null", CONCATENATE("'", $G37, "'")), ");")</f>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction', 'Person Work Time Sheet');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction', 'Time Sheet');</v>
       </c>
       <c r="K37" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction'::varchar,'caption', 'Person Work Time Sheet'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Transaction'::varchar,'caption', 'Time Sheet'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="38" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B38" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="E38" s="8">
         <f t="shared" si="0"/>
@@ -17170,23 +17170,23 @@
       </c>
       <c r="G38" s="3" t="str">
         <f t="shared" si="8"/>
-        <v>Person Work Time Sheet Summary</v>
+        <v>Time Sheet Summary</v>
       </c>
       <c r="I38" s="9" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList', 'Person Work Time Sheet Summary');</v>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList', 'Time Sheet Summary');</v>
       </c>
       <c r="K38" s="1" t="str">
         <f t="shared" si="4"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList'::varchar,'caption', 'Person Work Time Sheet Summary'::varchar)))::varchar;</v>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.HumanResource.Data.PersonWorkTimeSheet.Report.DataList'::varchar,'caption', 'Time Sheet Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="39" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="E39" s="8">
         <f t="shared" si="0"/>
@@ -17211,10 +17211,10 @@
     </row>
     <row r="40" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B40" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>281</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>282</v>
       </c>
       <c r="E40" s="8">
         <f t="shared" si="0"/>
@@ -17239,10 +17239,10 @@
     </row>
     <row r="41" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="E41" s="8">
         <f t="shared" si="0"/>
@@ -17267,10 +17267,10 @@
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="E42" s="8">
         <f t="shared" si="0"/>
@@ -17295,10 +17295,10 @@
     </row>
     <row r="43" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="E43" s="8">
         <f t="shared" si="0"/>
@@ -17323,10 +17323,10 @@
     </row>
     <row r="44" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E44" s="8">
         <f t="shared" si="0"/>
@@ -17351,10 +17351,10 @@
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E45" s="8">
         <f t="shared" si="0"/>
@@ -17379,10 +17379,10 @@
     </row>
     <row r="46" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E46" s="8">
         <f t="shared" si="0"/>
@@ -17407,10 +17407,10 @@
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E47" s="8">
         <f t="shared" si="0"/>
@@ -17435,10 +17435,10 @@
     </row>
     <row r="48" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E48" s="8">
         <f t="shared" si="0"/>
@@ -17463,10 +17463,10 @@
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B49" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E49" s="8">
         <f t="shared" si="0"/>
@@ -17491,10 +17491,10 @@
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E50" s="8">
         <f t="shared" si="0"/>
@@ -17519,10 +17519,10 @@
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="E51" s="8">
         <f t="shared" si="0"/>
@@ -17547,10 +17547,10 @@
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E52" s="8">
         <f t="shared" si="0"/>
@@ -17575,10 +17575,10 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B53" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E53" s="8">
         <f t="shared" si="0"/>
@@ -17603,10 +17603,10 @@
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B54" s="4" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E54" s="8">
         <f t="shared" si="0"/>
@@ -17634,7 +17634,7 @@
         <v>119</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E55" s="8">
         <f t="shared" si="0"/>
@@ -17662,7 +17662,7 @@
         <v>120</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E56" s="8">
         <f t="shared" si="0"/>
@@ -17687,10 +17687,10 @@
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B57" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E57" s="8">
         <f t="shared" si="0"/>
@@ -17718,7 +17718,7 @@
         <v>121</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E58" s="8">
         <f t="shared" si="0"/>
@@ -17746,7 +17746,7 @@
         <v>122</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E59" s="8">
         <f t="shared" si="0"/>
@@ -17771,10 +17771,10 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B60" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E60" s="8">
         <f t="shared" si="0"/>
@@ -17799,10 +17799,10 @@
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B61" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E61" s="8">
         <f t="shared" si="0"/>
@@ -17827,10 +17827,10 @@
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B62" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E62" s="8">
         <f t="shared" si="0"/>
@@ -17855,10 +17855,10 @@
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B63" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E63" s="8">
         <f t="shared" si="0"/>
@@ -17883,10 +17883,10 @@
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B64" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="E64" s="8">
         <f t="shared" si="0"/>
@@ -17911,10 +17911,10 @@
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B65" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="E65" s="8">
         <f t="shared" si="0"/>
@@ -17939,10 +17939,10 @@
     </row>
     <row r="66" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B66" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E66" s="8">
         <f t="shared" si="0"/>
@@ -17967,10 +17967,10 @@
     </row>
     <row r="67" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B67" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E67" s="8">
         <f t="shared" si="0"/>
@@ -17995,7 +17995,7 @@
     </row>
     <row r="68" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B68" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>89</v>
@@ -18017,7 +18017,7 @@
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Transaction', 'Purchase Requisition');</v>
       </c>
       <c r="K68" s="1" t="str">
-        <f>CONCATENATE(
+        <f t="shared" ref="K68:K84" si="10">CONCATENATE(
 "varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
 "'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
 "'sysLoginSession_RefID', varSystemLoginSession::bigint,",
@@ -18036,10 +18036,10 @@
     </row>
     <row r="69" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B69" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E69" s="8">
         <f t="shared" si="0"/>
@@ -18058,29 +18058,16 @@
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList', 'Report Purchase Requisition Summary');</v>
       </c>
       <c r="K69" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B69, ""), "null", CONCATENATE("'", SUBSTITUTE($B69, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G69, ""), "null", CONCATENATE("'", SUBSTITUTE($G69, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisition.Report.DataList'::varchar,'caption', 'Report Purchase Requisition Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="70" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B70" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E70" s="8">
         <f t="shared" si="0"/>
@@ -18095,30 +18082,17 @@
         <v>Report Purchase Requisition To Purchase Order</v>
       </c>
       <c r="I70" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B70, ""),"null", CONCATENATE("'", $F70, "'")), ", ", IF(EXACT($B70, ""), "null", CONCATENATE("'", $G70, "'")), ");")</f>
+        <f t="shared" ref="I70:I84" si="11">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B70, ""),"null", CONCATENATE("'", $F70, "'")), ", ", IF(EXACT($B70, ""), "null", CONCATENATE("'", $G70, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList', 'Report Purchase Requisition To Purchase Order');</v>
       </c>
       <c r="K70" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B70, ""), "null", CONCATENATE("'", SUBSTITUTE($B70, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G70, ""), "null", CONCATENATE("'", SUBSTITUTE($G70, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseRequisitionToPurchaseOrder.Report.DataList'::varchar,'caption', 'Report Purchase Requisition To Purchase Order'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B71" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>90</v>
@@ -18136,33 +18110,20 @@
         <v>Purchase Order</v>
       </c>
       <c r="I71" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B71, ""),"null", CONCATENATE("'", $F71, "'")), ", ", IF(EXACT($B71, ""), "null", CONCATENATE("'", $G71, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Transaction', 'Purchase Order');</v>
       </c>
       <c r="K71" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B71, ""), "null", CONCATENATE("'", SUBSTITUTE($B71, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G71, ""), "null", CONCATENATE("'", SUBSTITUTE($G71, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrder.Transaction'::varchar,'caption', 'Purchase Order'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B72" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E72" s="8">
         <f t="shared" si="0"/>
@@ -18177,33 +18138,20 @@
         <v>Report Purchase Order Summary</v>
       </c>
       <c r="I72" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B72, ""),"null", CONCATENATE("'", $F72, "'")), ", ", IF(EXACT($B72, ""), "null", CONCATENATE("'", $G72, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList', 'Report Purchase Order Summary');</v>
       </c>
       <c r="K72" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B72, ""), "null", CONCATENATE("'", SUBSTITUTE($B72, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G72, ""), "null", CONCATENATE("'", SUBSTITUTE($G72, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrder.Report.DataList'::varchar,'caption', 'Report Purchase Order Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B73" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="E73" s="8">
         <f t="shared" si="0"/>
@@ -18218,503 +18166,347 @@
         <v>Report Purchase Order to Account Payable Summary</v>
       </c>
       <c r="I73" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B73, ""),"null", CONCATENATE("'", $F73, "'")), ", ", IF(EXACT($B73, ""), "null", CONCATENATE("'", $G73, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList', 'Report Purchase Order to Account Payable Summary');</v>
       </c>
       <c r="K73" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B73, ""), "null", CONCATENATE("'", SUBSTITUTE($B73, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G73, ""), "null", CONCATENATE("'", SUBSTITUTE($G73, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.SupplyChain.Data.PurchaseOrderToPaymentInstruction.Report.DataList'::varchar,'caption', 'Report Purchase Order to Account Payable Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="74" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B74" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="E74" s="8">
         <f t="shared" si="0"/>
         <v>97000000000073</v>
       </c>
       <c r="F74" s="3" t="str">
-        <f>IF(EXACT(B74, ""), "", B74)</f>
+        <f t="shared" ref="F74:F83" si="12">IF(EXACT(B74, ""), "", B74)</f>
         <v>Module.General.MasterData.Bank.Transaction</v>
       </c>
       <c r="G74" s="3" t="str">
-        <f>IF(EXACT(C74, ""), "", C74)</f>
+        <f t="shared" ref="G74:G83" si="13">IF(EXACT(C74, ""), "", C74)</f>
         <v>Bank</v>
       </c>
       <c r="I74" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B74, ""),"null", CONCATENATE("'", $F74, "'")), ", ", IF(EXACT($B74, ""), "null", CONCATENATE("'", $G74, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Bank.Transaction', 'Bank');</v>
       </c>
       <c r="K74" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B74, ""), "null", CONCATENATE("'", SUBSTITUTE($B74, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G74, ""), "null", CONCATENATE("'", SUBSTITUTE($G74, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Bank.Transaction'::varchar,'caption', 'Bank'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="75" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B75" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C75" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="E75" s="8">
         <f t="shared" si="0"/>
         <v>97000000000074</v>
       </c>
       <c r="F75" s="3" t="str">
-        <f>IF(EXACT(B75, ""), "", B75)</f>
+        <f t="shared" si="12"/>
         <v>Module.General.MasterData.BankAccount.Transaction</v>
       </c>
       <c r="G75" s="3" t="str">
-        <f>IF(EXACT(C75, ""), "", C75)</f>
+        <f t="shared" si="13"/>
         <v>Bank Account</v>
       </c>
       <c r="I75" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B75, ""),"null", CONCATENATE("'", $F75, "'")), ", ", IF(EXACT($B75, ""), "null", CONCATENATE("'", $G75, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.BankAccount.Transaction', 'Bank Account');</v>
       </c>
       <c r="K75" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B75, ""), "null", CONCATENATE("'", SUBSTITUTE($B75, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G75, ""), "null", CONCATENATE("'", SUBSTITUTE($G75, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.BankAccount.Transaction'::varchar,'caption', 'Bank Account'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="76" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B76" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E76" s="8">
         <f t="shared" si="0"/>
         <v>97000000000075</v>
       </c>
       <c r="F76" s="3" t="str">
-        <f>IF(EXACT(B76, ""), "", B76)</f>
+        <f t="shared" si="12"/>
         <v>Module.General.MasterData.Currency.Transaction</v>
       </c>
       <c r="G76" s="3" t="str">
-        <f>IF(EXACT(C76, ""), "", C76)</f>
+        <f t="shared" si="13"/>
         <v>Currency</v>
       </c>
       <c r="I76" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B76, ""),"null", CONCATENATE("'", $F76, "'")), ", ", IF(EXACT($B76, ""), "null", CONCATENATE("'", $G76, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Currency.Transaction', 'Currency');</v>
       </c>
       <c r="K76" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B76, ""), "null", CONCATENATE("'", SUBSTITUTE($B76, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G76, ""), "null", CONCATENATE("'", SUBSTITUTE($G76, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Currency.Transaction'::varchar,'caption', 'Currency'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="77" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B77" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="E77" s="8">
         <f t="shared" si="0"/>
         <v>97000000000076</v>
       </c>
       <c r="F77" s="3" t="str">
-        <f>IF(EXACT(B77, ""), "", B77)</f>
+        <f t="shared" si="12"/>
         <v>Module.General.MasterData.CurrencyExchangeRate.Transaction</v>
       </c>
       <c r="G77" s="3" t="str">
-        <f>IF(EXACT(C77, ""), "", C77)</f>
+        <f t="shared" si="13"/>
         <v>Exchange Rate</v>
       </c>
       <c r="I77" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B77, ""),"null", CONCATENATE("'", $F77, "'")), ", ", IF(EXACT($B77, ""), "null", CONCATENATE("'", $G77, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Transaction', 'Exchange Rate');</v>
       </c>
       <c r="K77" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B77, ""), "null", CONCATENATE("'", SUBSTITUTE($B77, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G77, ""), "null", CONCATENATE("'", SUBSTITUTE($G77, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CurrencyExchangeRate.Transaction'::varchar,'caption', 'Exchange Rate'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="78" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B78" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="E78" s="8">
         <f t="shared" si="0"/>
         <v>97000000000077</v>
       </c>
       <c r="F78" s="3" t="str">
-        <f>IF(EXACT(B78, ""), "", B78)</f>
+        <f t="shared" si="12"/>
         <v>Module.General.MasterData.CurrencyExchangeRate.Report.DataList</v>
       </c>
       <c r="G78" s="3" t="str">
-        <f>IF(EXACT(C78, ""), "", C78)</f>
+        <f t="shared" si="13"/>
         <v>Exchange Rate Summary</v>
       </c>
       <c r="I78" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B78, ""),"null", CONCATENATE("'", $F78, "'")), ", ", IF(EXACT($B78, ""), "null", CONCATENATE("'", $G78, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.CurrencyExchangeRate.Report.DataList', 'Exchange Rate Summary');</v>
       </c>
       <c r="K78" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B78, ""), "null", CONCATENATE("'", SUBSTITUTE($B78, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G78, ""), "null", CONCATENATE("'", SUBSTITUTE($G78, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.CurrencyExchangeRate.Report.DataList'::varchar,'caption', 'Exchange Rate Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="79" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B79" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>274</v>
       </c>
       <c r="E79" s="8">
         <f t="shared" si="0"/>
         <v>97000000000078</v>
       </c>
       <c r="F79" s="3" t="str">
-        <f>IF(EXACT(B79, ""), "", B79)</f>
+        <f t="shared" si="12"/>
         <v>Module.General.MasterData.PaymentTerm.Transaction</v>
       </c>
       <c r="G79" s="3" t="str">
-        <f>IF(EXACT(C79, ""), "", C79)</f>
+        <f t="shared" si="13"/>
         <v>Payment Term</v>
       </c>
       <c r="I79" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B79, ""),"null", CONCATENATE("'", $F79, "'")), ", ", IF(EXACT($B79, ""), "null", CONCATENATE("'", $G79, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.PaymentTerm.Transaction', 'Payment Term');</v>
       </c>
       <c r="K79" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B79, ""), "null", CONCATENATE("'", SUBSTITUTE($B79, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G79, ""), "null", CONCATENATE("'", SUBSTITUTE($G79, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.PaymentTerm.Transaction'::varchar,'caption', 'Payment Term'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="80" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B80" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="E80" s="8">
         <f t="shared" si="0"/>
         <v>97000000000079</v>
       </c>
       <c r="F80" s="3" t="str">
-        <f>IF(EXACT(B80, ""), "", B80)</f>
+        <f t="shared" si="12"/>
         <v>Module.General.MasterData.Period.Transaction</v>
       </c>
       <c r="G80" s="3" t="str">
-        <f>IF(EXACT(C80, ""), "", C80)</f>
+        <f t="shared" si="13"/>
         <v>Period</v>
       </c>
       <c r="I80" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B80, ""),"null", CONCATENATE("'", $F80, "'")), ", ", IF(EXACT($B80, ""), "null", CONCATENATE("'", $G80, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.General.MasterData.Period.Transaction', 'Period');</v>
       </c>
       <c r="K80" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B80, ""), "null", CONCATENATE("'", SUBSTITUTE($B80, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G80, ""), "null", CONCATENATE("'", SUBSTITUTE($G80, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.General.MasterData.Period.Transaction'::varchar,'caption', 'Period'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="81" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B81" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="E81" s="8">
         <f t="shared" si="0"/>
         <v>97000000000080</v>
       </c>
       <c r="F81" s="3" t="str">
-        <f>IF(EXACT(B81, ""), "", B81)</f>
+        <f t="shared" si="12"/>
         <v>Module.Accounting.MasterData.AssetCategory.Transaction</v>
       </c>
       <c r="G81" s="3" t="str">
-        <f>IF(EXACT(C81, ""), "", C81)</f>
+        <f t="shared" si="13"/>
         <v>Asset Category</v>
       </c>
       <c r="I81" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B81, ""),"null", CONCATENATE("'", $F81, "'")), ", ", IF(EXACT($B81, ""), "null", CONCATENATE("'", $G81, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.AssetCategory.Transaction', 'Asset Category');</v>
       </c>
       <c r="K81" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B81, ""), "null", CONCATENATE("'", SUBSTITUTE($B81, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G81, ""), "null", CONCATENATE("'", SUBSTITUTE($G81, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.AssetCategory.Transaction'::varchar,'caption', 'Asset Category'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="82" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B82" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="C82" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>268</v>
       </c>
       <c r="E82" s="8">
         <f t="shared" si="0"/>
         <v>97000000000081</v>
       </c>
       <c r="F82" s="3" t="str">
-        <f>IF(EXACT(B82, ""), "", B82)</f>
+        <f t="shared" si="12"/>
         <v>Module.Accounting.MasterData.ChartOfAccount.Transaction</v>
       </c>
       <c r="G82" s="3" t="str">
-        <f>IF(EXACT(C82, ""), "", C82)</f>
+        <f t="shared" si="13"/>
         <v>Chart of Account</v>
       </c>
       <c r="I82" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B82, ""),"null", CONCATENATE("'", $F82, "'")), ", ", IF(EXACT($B82, ""), "null", CONCATENATE("'", $G82, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.ChartOfAccount.Transaction', 'Chart of Account');</v>
       </c>
       <c r="K82" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B82, ""), "null", CONCATENATE("'", SUBSTITUTE($B82, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G82, ""), "null", CONCATENATE("'", SUBSTITUTE($G82, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.ChartOfAccount.Transaction'::varchar,'caption', 'Chart of Account'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="83" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B83" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="E83" s="8">
         <f t="shared" si="0"/>
         <v>97000000000082</v>
       </c>
       <c r="F83" s="3" t="str">
-        <f>IF(EXACT(B83, ""), "", B83)</f>
+        <f t="shared" si="12"/>
         <v>Module.Accounting.MasterData.DepreciationMethod.Transaction</v>
       </c>
       <c r="G83" s="3" t="str">
-        <f>IF(EXACT(C83, ""), "", C83)</f>
+        <f t="shared" si="13"/>
         <v>Depreciation Method</v>
       </c>
       <c r="I83" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B83, ""),"null", CONCATENATE("'", $F83, "'")), ", ", IF(EXACT($B83, ""), "null", CONCATENATE("'", $G83, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationMethod.Transaction', 'Depreciation Method');</v>
       </c>
       <c r="K83" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B83, ""), "null", CONCATENATE("'", SUBSTITUTE($B83, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G83, ""), "null", CONCATENATE("'", SUBSTITUTE($G83, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.DepreciationMethod.Transaction'::varchar,'caption', 'Depreciation Method'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="84" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B84" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E84" s="8">
         <f t="shared" si="0"/>
         <v>97000000000083</v>
       </c>
       <c r="F84" s="3" t="str">
-        <f t="shared" ref="F84:F116" si="10">IF(EXACT(B84, ""), "", B84)</f>
+        <f t="shared" ref="F84:F116" si="14">IF(EXACT(B84, ""), "", B84)</f>
         <v>Module.Accounting.MasterData.DepreciationRateYears.Transaction</v>
       </c>
       <c r="G84" s="3" t="str">
-        <f t="shared" ref="G84:G116" si="11">IF(EXACT(C84, ""), "", C84)</f>
+        <f t="shared" ref="G84:G116" si="15">IF(EXACT(C84, ""), "", C84)</f>
         <v>Depreciation Rate Years</v>
       </c>
       <c r="I84" s="9" t="str">
-        <f>CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B84, ""),"null", CONCATENATE("'", $F84, "'")), ", ", IF(EXACT($B84, ""), "null", CONCATENATE("'", $G84, "'")), ");")</f>
+        <f t="shared" si="11"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.MasterData.DepreciationRateYears.Transaction', 'Depreciation Rate Years');</v>
       </c>
       <c r="K84" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'key', ", IF(EXACT($B84, ""), "null", CONCATENATE("'", SUBSTITUTE($B84, "'", "\'"), "'")), "::varchar,",
-"'caption', ", IF(EXACT($G84, ""), "null", CONCATENATE("'", SUBSTITUTE($G84, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
+        <f t="shared" si="10"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.MasterData.DepreciationRateYears.Transaction'::varchar,'caption', 'Depreciation Rate Years'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="85" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B85" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="C85" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C85" s="2" t="s">
-        <v>278</v>
-      </c>
       <c r="E85" s="8">
-        <f t="shared" ref="E85:E116" si="12">IF(ISNUMBER($E84), $E84+1, 97000000000001)</f>
+        <f t="shared" ref="E85:E116" si="16">IF(ISNUMBER($E84), $E84+1, 97000000000001)</f>
         <v>97000000000084</v>
       </c>
       <c r="F85" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Taxation.MasterData.ValueAddedTax.Transaction</v>
       </c>
       <c r="G85" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Value Added Tax</v>
       </c>
       <c r="I85" s="9" t="str">
-        <f t="shared" ref="I85:I116" si="13">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B85, ""),"null", CONCATENATE("'", $F85, "'")), ", ", IF(EXACT($B85, ""), "null", CONCATENATE("'", $G85, "'")), ");")</f>
+        <f t="shared" ref="I85:I116" si="17">CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_Menu_SET""(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, ", IF(EXACT($B85, ""),"null", CONCATENATE("'", $F85, "'")), ", ", IF(EXACT($B85, ""), "null", CONCATENATE("'", $G85, "'")), ");")</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Taxation.MasterData.ValueAddedTax.Transaction', 'Value Added Tax');</v>
       </c>
       <c r="K85" s="1" t="str">
-        <f t="shared" ref="K85:K116" si="14">CONCATENATE(
+        <f t="shared" ref="K85:K116" si="18">CONCATENATE(
 "varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
 "'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
 "'sysLoginSession_RefID', varSystemLoginSession::bigint,",
@@ -18733,253 +18525,253 @@
     </row>
     <row r="86" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B86" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E86" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000085</v>
       </c>
       <c r="F86" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Accounting.Data.BalanceSheet.Report.DataList</v>
       </c>
       <c r="G86" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Balance Sheet</v>
       </c>
       <c r="I86" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.BalanceSheet.Report.DataList', 'Balance Sheet');</v>
       </c>
       <c r="K86" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.BalanceSheet.Report.DataList'::varchar,'caption', 'Balance Sheet'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="87" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B87" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C87" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="C87" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="E87" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000086</v>
       </c>
       <c r="F87" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Accounting.Data.GeneralJournal.Transaction</v>
       </c>
       <c r="G87" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>General Journal</v>
       </c>
       <c r="I87" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Transaction', 'General Journal');</v>
       </c>
       <c r="K87" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralJournal.Transaction'::varchar,'caption', 'General Journal'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="88" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B88" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C88" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="C88" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="E88" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000087</v>
       </c>
       <c r="F88" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Accounting.Data.GeneralJournal.Report.DataList</v>
       </c>
       <c r="G88" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>General Journal Summary</v>
       </c>
       <c r="I88" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralJournal.Report.DataList', 'General Journal Summary');</v>
       </c>
       <c r="K88" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralJournal.Report.DataList'::varchar,'caption', 'General Journal Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="89" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B89" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E89" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000088</v>
       </c>
       <c r="F89" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Accounting.Data.GeneralLedger.Report.DataList</v>
       </c>
       <c r="G89" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>General Ledger Summary</v>
       </c>
       <c r="I89" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.GeneralLedger.Report.DataList', 'General Ledger Summary');</v>
       </c>
       <c r="K89" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.GeneralLedger.Report.DataList'::varchar,'caption', 'General Ledger Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="90" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B90" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>321</v>
+        <v>335</v>
       </c>
       <c r="E90" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000089</v>
       </c>
       <c r="F90" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Accounting.Data.ProfitLoss.Report.DataList</v>
       </c>
       <c r="G90" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>Profit Loss Summary</v>
+        <f t="shared" si="15"/>
+        <v>Profit Loss</v>
       </c>
       <c r="I90" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.ProfitLoss.Report.DataList', 'Profit Loss Summary');</v>
+        <f t="shared" si="17"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Accounting.Data.ProfitLoss.Report.DataList', 'Profit Loss');</v>
       </c>
       <c r="K90" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.ProfitLoss.Report.DataList'::varchar,'caption', 'Profit Loss Summary'::varchar)))::varchar;</v>
+        <f t="shared" si="18"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Accounting.Data.ProfitLoss.Report.DataList'::varchar,'caption', 'Profit Loss'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="91" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B91" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="E91" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000090</v>
       </c>
       <c r="F91" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.CashBank.Transaction</v>
       </c>
       <c r="G91" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Cash &amp; Bank</v>
       </c>
       <c r="I91" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Transaction', 'Cash &amp; Bank');</v>
       </c>
       <c r="K91" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CashBank.Transaction'::varchar,'caption', 'Cash &amp; Bank'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="92" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B92" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E92" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000091</v>
       </c>
       <c r="F92" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.CashBank.Report.DataList</v>
       </c>
       <c r="G92" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Cash &amp; Bank Summary</v>
       </c>
       <c r="I92" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CashBank.Report.DataList', 'Cash &amp; Bank Summary');</v>
       </c>
       <c r="K92" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CashBank.Report.DataList'::varchar,'caption', 'Cash &amp; Bank Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="93" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B93" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E93" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000092</v>
       </c>
       <c r="F93" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.CreditNote.Transaction</v>
       </c>
       <c r="G93" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Credit Note</v>
       </c>
       <c r="I93" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Transaction', 'Credit Note');</v>
       </c>
       <c r="K93" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CreditNote.Transaction'::varchar,'caption', 'Credit Note'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="94" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B94" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E94" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000093</v>
       </c>
       <c r="F94" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.CreditNote.Report.DataList</v>
       </c>
       <c r="G94" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Credit Note Summary</v>
       </c>
       <c r="I94" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.CreditNote.Report.DataList', 'Credit Note Summary');</v>
       </c>
       <c r="K94" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.CreditNote.Report.DataList'::varchar,'caption', 'Credit Note Summary'::varchar)))::varchar;</v>
       </c>
     </row>
@@ -18991,23 +18783,23 @@
         <v>118</v>
       </c>
       <c r="E95" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000094</v>
       </c>
       <c r="F95" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.DebitNote.Transaction</v>
       </c>
       <c r="G95" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Debit Note</v>
       </c>
       <c r="I95" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Transaction', 'Debit Note');</v>
       </c>
       <c r="K95" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.DebitNote.Transaction'::varchar,'caption', 'Debit Note'::varchar)))::varchar;</v>
       </c>
     </row>
@@ -19016,222 +18808,222 @@
         <v>124</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E96" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000095</v>
       </c>
       <c r="F96" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.DebitNote.Report.DataList</v>
       </c>
       <c r="G96" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Debit Note Summary</v>
       </c>
       <c r="I96" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.DebitNote.Report.DataList', 'Debit Note Summary');</v>
       </c>
       <c r="K96" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.DebitNote.Report.DataList'::varchar,'caption', 'Debit Note Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B97" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E97" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000096</v>
       </c>
       <c r="F97" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.FixedAsset.Data.GoodsIdentity.Transaction</v>
       </c>
       <c r="G97" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Fixed Asset</v>
       </c>
       <c r="I97" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.FixedAsset.Data.GoodsIdentity.Transaction', 'Fixed Asset');</v>
       </c>
       <c r="K97" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.FixedAsset.Data.GoodsIdentity.Transaction'::varchar,'caption', 'Fixed Asset'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="98" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B98" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="E98" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000097</v>
       </c>
       <c r="F98" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.FixedAsset.Data.GoodsIdentity.Report.DataList</v>
       </c>
       <c r="G98" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Fixed Asset Summary</v>
       </c>
       <c r="I98" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.FixedAsset.Data.GoodsIdentity.Report.DataList', 'Fixed Asset Summary');</v>
       </c>
       <c r="K98" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.FixedAsset.Data.GoodsIdentity.Report.DataList'::varchar,'caption', 'Fixed Asset Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="99" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B99" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E99" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000098</v>
       </c>
       <c r="F99" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.Loan.Transaction</v>
       </c>
       <c r="G99" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Loan</v>
       </c>
       <c r="I99" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Transaction', 'Loan');</v>
       </c>
       <c r="K99" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Loan.Transaction'::varchar,'caption', 'Loan'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="100" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B100" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E100" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000099</v>
       </c>
       <c r="F100" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.Loan.Report.DataList</v>
       </c>
       <c r="G100" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Loan Summary</v>
       </c>
       <c r="I100" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Loan.Report.DataList', 'Loan Summary');</v>
       </c>
       <c r="K100" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Loan.Report.DataList'::varchar,'caption', 'Loan Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="101" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B101" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E101" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000100</v>
       </c>
       <c r="F101" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.LoanToLoanSettlement.Report.DataList</v>
       </c>
       <c r="G101" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Loan to Loan Settlement Summary</v>
       </c>
       <c r="I101" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList', 'Loan to Loan Settlement Summary');</v>
       </c>
       <c r="K101" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanToLoanSettlement.Report.DataList'::varchar,'caption', 'Loan to Loan Settlement Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="102" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B102" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E102" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000101</v>
       </c>
       <c r="F102" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.LoanSettlement.Transaction</v>
       </c>
       <c r="G102" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Loan Settlement</v>
       </c>
       <c r="I102" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Transaction', 'Loan Settlement');</v>
       </c>
       <c r="K102" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanSettlement.Transaction'::varchar,'caption', 'Loan Settlement'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="103" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B103" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E103" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000102</v>
       </c>
       <c r="F103" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.LoanSettlement.Report.DataList</v>
       </c>
       <c r="G103" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Loan Settlement Summary</v>
       </c>
       <c r="I103" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.LoanSettlement.Report.DataList', 'Loan Settlement Summary');</v>
       </c>
       <c r="K103" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.LoanSettlement.Report.DataList'::varchar,'caption', 'Loan Settlement Summary'::varchar)))::varchar;</v>
       </c>
     </row>
@@ -19240,26 +19032,26 @@
         <v>125</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E104" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000103</v>
       </c>
       <c r="F104" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.PaymentInstruction.Transaction</v>
       </c>
       <c r="G104" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Account Payable</v>
       </c>
       <c r="I104" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Transaction', 'Account Payable');</v>
       </c>
       <c r="K104" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PaymentInstruction.Transaction'::varchar,'caption', 'Account Payable'::varchar)))::varchar;</v>
       </c>
     </row>
@@ -19268,335 +19060,335 @@
         <v>126</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E105" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000104</v>
       </c>
       <c r="F105" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.PaymentInstruction.Report.DataList</v>
       </c>
       <c r="G105" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Account Payable Summary</v>
       </c>
       <c r="I105" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.PaymentInstruction.Report.DataList', 'Account Payable Summary');</v>
       </c>
       <c r="K105" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.PaymentInstruction.Report.DataList'::varchar,'caption', 'Account Payable Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="106" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B106" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E106" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000105</v>
       </c>
       <c r="F106" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.Reimbursement.Transaction</v>
       </c>
       <c r="G106" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Reimbursement</v>
       </c>
       <c r="I106" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Transaction', 'Reimbursement');</v>
       </c>
       <c r="K106" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Reimbursement.Transaction'::varchar,'caption', 'Reimbursement'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="107" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B107" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="E107" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000106</v>
       </c>
       <c r="F107" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.Reimbursement.Report.DataList</v>
       </c>
       <c r="G107" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Reimbursement Summary</v>
       </c>
       <c r="I107" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.Reimbursement.Report.DataList', 'Reimbursement Summary');</v>
       </c>
       <c r="K107" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.Reimbursement.Report.DataList'::varchar,'caption', 'Reimbursement Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="108" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B108" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E108" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000107</v>
       </c>
       <c r="F108" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.ReimbursementToDebitNote.Report.DataList</v>
       </c>
       <c r="G108" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Reimbursement to Debit Note Summary</v>
       </c>
       <c r="I108" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList', 'Reimbursement to Debit Note Summary');</v>
       </c>
       <c r="K108" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.ReimbursementToDebitNote.Report.DataList'::varchar,'caption', 'Reimbursement to Debit Note Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="109" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B109" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="C109" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="E109" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000108</v>
       </c>
       <c r="F109" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.SalesInvoice.Transaction</v>
       </c>
       <c r="G109" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Sales Invoice</v>
       </c>
       <c r="I109" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Transaction', 'Sales Invoice');</v>
       </c>
       <c r="K109" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.SalesInvoice.Transaction'::varchar,'caption', 'Sales Invoice'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="110" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B110" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="C110" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="E110" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000109</v>
       </c>
       <c r="F110" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.SalesInvoice.Report.DataList</v>
       </c>
       <c r="G110" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Sales Invoice Summary</v>
       </c>
       <c r="I110" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoice.Report.DataList', 'Sales Invoice Summary');</v>
       </c>
       <c r="K110" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.SalesInvoice.Report.DataList'::varchar,'caption', 'Sales Invoice Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="111" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B111" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C111" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="C111" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="E111" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000110</v>
       </c>
       <c r="F111" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList</v>
       </c>
       <c r="G111" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Sales Invoice to Credit Note</v>
       </c>
       <c r="I111" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList', 'Sales Invoice to Credit Note');</v>
       </c>
       <c r="K111" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.SalesInvoiceToCreditNote.Report.DataList'::varchar,'caption', 'Sales Invoice to Credit Note'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="112" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B112" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C112" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="C112" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="E112" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000111</v>
       </c>
       <c r="F112" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.TaxReconciliation.Transaction</v>
       </c>
       <c r="G112" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Tax Reconciliation</v>
       </c>
       <c r="I112" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Transaction', 'Tax Reconciliation');</v>
       </c>
       <c r="K112" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.TaxReconciliation.Transaction'::varchar,'caption', 'Tax Reconciliation'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="113" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B113" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C113" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="E113" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000112</v>
       </c>
       <c r="F113" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.Finance.Data.TaxReconciliation.Report.DataList</v>
       </c>
       <c r="G113" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Tax Reconciliation Summary</v>
       </c>
       <c r="I113" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.Finance.Data.TaxReconciliation.Report.DataList', 'Tax Reconciliation Summary');</v>
       </c>
       <c r="K113" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.Finance.Data.TaxReconciliation.Report.DataList'::varchar,'caption', 'Tax Reconciliation Summary'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="114" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B114" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E114" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000113</v>
       </c>
       <c r="F114" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="14"/>
         <v>Module.CustomerRelation.MasterData.Customer.Transaction</v>
       </c>
       <c r="G114" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Customer</v>
       </c>
       <c r="I114" s="9" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.MasterData.Customer.Transaction', 'Customer');</v>
       </c>
       <c r="K114" s="1" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.CustomerRelation.MasterData.Customer.Transaction'::varchar,'caption', 'Customer'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="115" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B115" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="E115" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000114</v>
       </c>
       <c r="F115" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>Module.CustomerRelation.MasterData.CustomerOrder.Transaction</v>
+        <f t="shared" si="14"/>
+        <v>Module.CustomerRelation.Data.CustomerOrder.Transaction</v>
       </c>
       <c r="G115" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Customer Order</v>
       </c>
       <c r="I115" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.MasterData.CustomerOrder.Transaction', 'Customer Order');</v>
+        <f t="shared" si="17"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.Data.CustomerOrder.Transaction', 'Customer Order');</v>
       </c>
       <c r="K115" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.CustomerRelation.MasterData.CustomerOrder.Transaction'::varchar,'caption', 'Customer Order'::varchar)))::varchar;</v>
+        <f t="shared" si="18"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.CustomerRelation.Data.CustomerOrder.Transaction'::varchar,'caption', 'Customer Order'::varchar)))::varchar;</v>
       </c>
     </row>
     <row r="116" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B116" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="E116" s="8">
-        <f t="shared" si="12"/>
+        <f t="shared" si="16"/>
         <v>97000000000115</v>
       </c>
       <c r="F116" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList</v>
+        <f t="shared" si="14"/>
+        <v>Module.CustomerRelation.Data.CustomerOrder.Report.DataList</v>
       </c>
       <c r="G116" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="15"/>
         <v>Customer Order Summary</v>
       </c>
       <c r="I116" s="9" t="str">
-        <f t="shared" si="13"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList', 'Customer Order Summary');</v>
+        <f t="shared" si="17"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_Menu_SET"(varSystemLoginSession, null, null, null, varInstitutionBranchID, varBaseCurrencyID, 'Module.CustomerRelation.Data.CustomerOrder.Report.DataList', 'Customer Order Summary');</v>
       </c>
       <c r="K116" s="1" t="str">
-        <f t="shared" si="14"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.CustomerRelation.MasterData.CustomerOrder.Report.DataList'::varchar,'caption', 'Customer Order Summary'::varchar)))::varchar;</v>
+        <f t="shared" si="18"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'key', 'Module.CustomerRelation.Data.CustomerOrder.Report.DataList'::varchar,'caption', 'Customer Order Summary'::varchar)))::varchar;</v>
       </c>
     </row>
   </sheetData>
